--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B5226A-6AC3-410F-881F-E2649E769C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BC992F-EE1E-47C0-8977-407185790E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Test" sheetId="4" r:id="rId3"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Registration!$A$1:$I$92</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="151">
   <si>
     <t>S No</t>
   </si>
@@ -460,6 +463,36 @@
   </si>
   <si>
     <t>Result</t>
+  </si>
+  <si>
+    <t>Muhammad Nabi</t>
+  </si>
+  <si>
+    <t>Irshad Ali Tanwar</t>
+  </si>
+  <si>
+    <t>452027323651-3</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Dua</t>
+  </si>
+  <si>
+    <t>Muneer Ahmed</t>
+  </si>
+  <si>
+    <t>Rameesha Fatima</t>
+  </si>
+  <si>
+    <t>Muhammad Bilawal</t>
+  </si>
+  <si>
+    <t>42201-6718737-5</t>
+  </si>
+  <si>
+    <t>Pending</t>
   </si>
 </sst>
 </file>
@@ -699,6 +732,26 @@
     <xf numFmtId="18" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -708,37 +761,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1048,17 +1092,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}">
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1141,7 +1186,9 @@
       <c r="G3" s="5">
         <v>45755</v>
       </c>
-      <c r="H3" s="5"/>
+      <c r="H3" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1166,8 +1213,12 @@
       <c r="G4" s="5">
         <v>45755</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="6"/>
+      <c r="H4" s="5">
+        <v>45766</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.4375</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -1191,8 +1242,12 @@
       <c r="G5" s="5">
         <v>45755</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6"/>
+      <c r="H5" s="5">
+        <v>45766</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0.4375</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -1216,7 +1271,9 @@
       <c r="G6" s="5">
         <v>45755</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1239,8 +1296,12 @@
       <c r="G7" s="5">
         <v>45755</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6"/>
+      <c r="H7" s="5">
+        <v>45766</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.4375</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -1264,7 +1325,9 @@
       <c r="G8" s="5">
         <v>45755</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1289,7 +1352,9 @@
       <c r="G9" s="5">
         <v>45755</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1312,7 +1377,9 @@
       <c r="G10" s="5">
         <v>45755</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1362,7 +1429,9 @@
       <c r="G12" s="5">
         <v>45755</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1416,7 +1485,9 @@
       <c r="G14" s="5">
         <v>45755</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1439,7 +1510,9 @@
       <c r="G15" s="5">
         <v>45755</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1462,7 +1535,9 @@
       <c r="G16" s="5">
         <v>45755</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1514,7 +1589,9 @@
       <c r="G18" s="5">
         <v>45755</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="H18" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1537,7 +1614,9 @@
       <c r="G19" s="5">
         <v>45755</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1560,7 +1639,9 @@
       <c r="G20" s="5">
         <v>45755</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I20" s="6"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1583,7 +1664,9 @@
       <c r="G21" s="5">
         <v>45755</v>
       </c>
-      <c r="H21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I21" s="6"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1637,7 +1720,9 @@
       <c r="G23" s="5">
         <v>45755</v>
       </c>
-      <c r="H23" s="5"/>
+      <c r="H23" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I23" s="6"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1660,7 +1745,9 @@
       <c r="G24" s="5">
         <v>45755</v>
       </c>
-      <c r="H24" s="5"/>
+      <c r="H24" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I24" s="6"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1683,7 +1770,9 @@
       <c r="G25" s="5">
         <v>45755</v>
       </c>
-      <c r="H25" s="5"/>
+      <c r="H25" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I25" s="6"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1737,7 +1826,9 @@
       <c r="G27" s="5">
         <v>45755</v>
       </c>
-      <c r="H27" s="5"/>
+      <c r="H27" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I27" s="6"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1760,7 +1851,9 @@
       <c r="G28" s="5">
         <v>45755</v>
       </c>
-      <c r="H28" s="5"/>
+      <c r="H28" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I28" s="6"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1785,7 +1878,9 @@
       <c r="G29" s="5">
         <v>45755</v>
       </c>
-      <c r="H29" s="5"/>
+      <c r="H29" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I29" s="6"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1810,7 +1905,9 @@
       <c r="G30" s="5">
         <v>45755</v>
       </c>
-      <c r="H30" s="5"/>
+      <c r="H30" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I30" s="6"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1833,7 +1930,9 @@
       <c r="G31" s="5">
         <v>45755</v>
       </c>
-      <c r="H31" s="5"/>
+      <c r="H31" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I31" s="6"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1858,7 +1957,9 @@
       <c r="G32" s="5">
         <v>45755</v>
       </c>
-      <c r="H32" s="5"/>
+      <c r="H32" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I32" s="6"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1912,7 +2013,9 @@
       <c r="G34" s="5">
         <v>45755</v>
       </c>
-      <c r="H34" s="5"/>
+      <c r="H34" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I34" s="6"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -1935,7 +2038,9 @@
       <c r="G35" s="5">
         <v>45755</v>
       </c>
-      <c r="H35" s="5"/>
+      <c r="H35" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I35" s="6"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1956,7 +2061,9 @@
       <c r="G36" s="5">
         <v>45755</v>
       </c>
-      <c r="H36" s="5"/>
+      <c r="H36" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I36" s="6"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -1979,7 +2086,9 @@
       <c r="G37" s="5">
         <v>45755</v>
       </c>
-      <c r="H37" s="5"/>
+      <c r="H37" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I37" s="6"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2029,7 +2138,9 @@
       <c r="G39" s="5">
         <v>45755</v>
       </c>
-      <c r="H39" s="5"/>
+      <c r="H39" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I39" s="6"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2081,7 +2192,9 @@
       <c r="G41" s="5">
         <v>45761</v>
       </c>
-      <c r="H41" s="5"/>
+      <c r="H41" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I41" s="6"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2104,7 +2217,9 @@
       <c r="G42" s="5">
         <v>45761</v>
       </c>
-      <c r="H42" s="5"/>
+      <c r="H42" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I42" s="6"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -2127,7 +2242,9 @@
       <c r="G43" s="5">
         <v>45761</v>
       </c>
-      <c r="H43" s="5"/>
+      <c r="H43" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I43" s="6"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2235,7 +2352,9 @@
       <c r="G47" s="5">
         <v>45761</v>
       </c>
-      <c r="H47" s="5"/>
+      <c r="H47" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I47" s="6"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2256,10 +2375,12 @@
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
+      <c r="H48" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I48" s="6"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2277,10 +2398,12 @@
         <v>3350336312</v>
       </c>
       <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
+      <c r="H49" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2299,7 +2422,9 @@
       <c r="F50" s="4">
         <v>3008912581</v>
       </c>
-      <c r="G50" s="5"/>
+      <c r="G50" s="5">
+        <v>45757</v>
+      </c>
       <c r="H50" s="5">
         <v>45764</v>
       </c>
@@ -2307,7 +2432,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2324,7 +2449,9 @@
       <c r="F51" s="3">
         <v>3122609898</v>
       </c>
-      <c r="G51" s="5"/>
+      <c r="G51" s="5">
+        <v>45757</v>
+      </c>
       <c r="H51" s="5">
         <v>45764</v>
       </c>
@@ -2332,46 +2459,95 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="6"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B52" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F52" s="4">
+        <v>3029250772</v>
+      </c>
+      <c r="G52" s="5">
+        <v>45764</v>
+      </c>
+      <c r="H52" s="5">
+        <v>45775</v>
+      </c>
+      <c r="I52" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="J52" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
+      <c r="B53" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="E53" s="3"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="6"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F53" s="4">
+        <v>3700321721</v>
+      </c>
+      <c r="G53" s="5">
+        <v>45764</v>
+      </c>
+      <c r="H53" s="5">
+        <v>45766</v>
+      </c>
+      <c r="I53" s="6">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="6"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B54" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F54" s="4">
+        <v>3152761492</v>
+      </c>
+      <c r="G54" s="5">
+        <v>45764</v>
+      </c>
+      <c r="H54" s="5">
+        <v>45766</v>
+      </c>
+      <c r="I54" s="6">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2381,10 +2557,12 @@
       <c r="E55" s="3"/>
       <c r="F55" s="4"/>
       <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
+      <c r="H55" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -2394,10 +2572,12 @@
       <c r="E56" s="3"/>
       <c r="F56" s="4"/>
       <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
+      <c r="H56" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I56" s="6"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2407,10 +2587,12 @@
       <c r="E57" s="3"/>
       <c r="F57" s="4"/>
       <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
+      <c r="H57" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2420,10 +2602,12 @@
       <c r="E58" s="3"/>
       <c r="F58" s="4"/>
       <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
+      <c r="H58" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2433,10 +2617,12 @@
       <c r="E59" s="3"/>
       <c r="F59" s="4"/>
       <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
+      <c r="H59" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2446,10 +2632,12 @@
       <c r="E60" s="3"/>
       <c r="F60" s="4"/>
       <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
+      <c r="H60" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2459,10 +2647,12 @@
       <c r="E61" s="3"/>
       <c r="F61" s="4"/>
       <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
+      <c r="H61" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -2472,10 +2662,12 @@
       <c r="E62" s="3"/>
       <c r="F62" s="4"/>
       <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
+      <c r="H62" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2485,10 +2677,12 @@
       <c r="E63" s="3"/>
       <c r="F63" s="4"/>
       <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
+      <c r="H63" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -2498,7 +2692,9 @@
       <c r="E64" s="3"/>
       <c r="F64" s="4"/>
       <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
+      <c r="H64" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I64" s="6"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -2511,7 +2707,9 @@
       <c r="E65" s="3"/>
       <c r="F65" s="4"/>
       <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
+      <c r="H65" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I65" s="6"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -2524,7 +2722,9 @@
       <c r="E66" s="3"/>
       <c r="F66" s="4"/>
       <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
+      <c r="H66" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I66" s="6"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -2537,7 +2737,9 @@
       <c r="E67" s="3"/>
       <c r="F67" s="4"/>
       <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
+      <c r="H67" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I67" s="6"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -2550,7 +2752,9 @@
       <c r="E68" s="3"/>
       <c r="F68" s="4"/>
       <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
+      <c r="H68" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I68" s="6"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -2563,7 +2767,9 @@
       <c r="E69" s="3"/>
       <c r="F69" s="4"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
+      <c r="H69" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I69" s="6"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -2576,7 +2782,9 @@
       <c r="E70" s="3"/>
       <c r="F70" s="4"/>
       <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
+      <c r="H70" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I70" s="6"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -2589,7 +2797,9 @@
       <c r="E71" s="3"/>
       <c r="F71" s="4"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
+      <c r="H71" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I71" s="6"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -2602,7 +2812,9 @@
       <c r="E72" s="3"/>
       <c r="F72" s="4"/>
       <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
+      <c r="H72" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I72" s="6"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -2615,7 +2827,9 @@
       <c r="E73" s="3"/>
       <c r="F73" s="4"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
+      <c r="H73" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I73" s="6"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -2628,7 +2842,9 @@
       <c r="E74" s="3"/>
       <c r="F74" s="4"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
+      <c r="H74" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I74" s="6"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -2641,7 +2857,9 @@
       <c r="E75" s="3"/>
       <c r="F75" s="4"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
+      <c r="H75" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I75" s="6"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -2654,7 +2872,9 @@
       <c r="E76" s="3"/>
       <c r="F76" s="4"/>
       <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
+      <c r="H76" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I76" s="6"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -2667,7 +2887,9 @@
       <c r="E77" s="3"/>
       <c r="F77" s="4"/>
       <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
+      <c r="H77" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I77" s="6"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -2680,7 +2902,9 @@
       <c r="E78" s="3"/>
       <c r="F78" s="4"/>
       <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
+      <c r="H78" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I78" s="6"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -2693,7 +2917,9 @@
       <c r="E79" s="3"/>
       <c r="F79" s="4"/>
       <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
+      <c r="H79" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I79" s="6"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -2706,7 +2932,9 @@
       <c r="E80" s="3"/>
       <c r="F80" s="4"/>
       <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
+      <c r="H80" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I80" s="6"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -2719,7 +2947,9 @@
       <c r="E81" s="3"/>
       <c r="F81" s="4"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
+      <c r="H81" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I81" s="6"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -2732,7 +2962,9 @@
       <c r="E82" s="3"/>
       <c r="F82" s="4"/>
       <c r="G82" s="5"/>
-      <c r="H82" s="5"/>
+      <c r="H82" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I82" s="6"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -2745,7 +2977,9 @@
       <c r="E83" s="3"/>
       <c r="F83" s="4"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="5"/>
+      <c r="H83" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I83" s="6"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -2758,7 +2992,9 @@
       <c r="E84" s="3"/>
       <c r="F84" s="4"/>
       <c r="G84" s="5"/>
-      <c r="H84" s="5"/>
+      <c r="H84" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I84" s="6"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -2771,7 +3007,9 @@
       <c r="E85" s="3"/>
       <c r="F85" s="4"/>
       <c r="G85" s="5"/>
-      <c r="H85" s="5"/>
+      <c r="H85" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I85" s="6"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -2784,7 +3022,9 @@
       <c r="E86" s="3"/>
       <c r="F86" s="4"/>
       <c r="G86" s="5"/>
-      <c r="H86" s="5"/>
+      <c r="H86" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I86" s="6"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -2797,7 +3037,9 @@
       <c r="E87" s="3"/>
       <c r="F87" s="4"/>
       <c r="G87" s="5"/>
-      <c r="H87" s="5"/>
+      <c r="H87" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I87" s="6"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -2810,7 +3052,9 @@
       <c r="E88" s="3"/>
       <c r="F88" s="4"/>
       <c r="G88" s="5"/>
-      <c r="H88" s="5"/>
+      <c r="H88" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I88" s="6"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -2823,7 +3067,9 @@
       <c r="E89" s="3"/>
       <c r="F89" s="4"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="5"/>
+      <c r="H89" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I89" s="6"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -2836,7 +3082,9 @@
       <c r="E90" s="3"/>
       <c r="F90" s="4"/>
       <c r="G90" s="5"/>
-      <c r="H90" s="5"/>
+      <c r="H90" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I90" s="6"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -2849,7 +3097,9 @@
       <c r="E91" s="3"/>
       <c r="F91" s="4"/>
       <c r="G91" s="5"/>
-      <c r="H91" s="5"/>
+      <c r="H91" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I91" s="6"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -2862,10 +3112,18 @@
       <c r="E92" s="3"/>
       <c r="F92" s="4"/>
       <c r="G92" s="5"/>
-      <c r="H92" s="5"/>
+      <c r="H92" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="I92" s="6"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}"/>
+  <conditionalFormatting sqref="A1:I92">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$H1&lt;TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3178,16 +3436,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B2" s="16"/>
@@ -3196,7 +3454,7 @@
       <c r="E2" s="17"/>
     </row>
     <row r="3" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="12" t="s">
         <v>136</v>
       </c>
       <c r="B3" s="16"/>
@@ -3205,7 +3463,7 @@
       <c r="E3" s="17"/>
     </row>
     <row r="4" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="16"/>
@@ -3214,7 +3472,7 @@
       <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="12" t="s">
         <v>137</v>
       </c>
       <c r="B5" s="16"/>
@@ -3223,7 +3481,7 @@
       <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>138</v>
       </c>
       <c r="B6" s="16"/>
@@ -3232,26 +3490,26 @@
       <c r="E6" s="17"/>
     </row>
     <row r="7" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="14"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B22" s="16"/>
@@ -3260,7 +3518,7 @@
       <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="12" t="s">
         <v>136</v>
       </c>
       <c r="B23" s="16"/>
@@ -3269,7 +3527,7 @@
       <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B24" s="16"/>
@@ -3278,7 +3536,7 @@
       <c r="E24" s="17"/>
     </row>
     <row r="25" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="12" t="s">
         <v>137</v>
       </c>
       <c r="B25" s="16"/>
@@ -3287,7 +3545,7 @@
       <c r="E25" s="17"/>
     </row>
     <row r="26" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="12" t="s">
         <v>138</v>
       </c>
       <c r="B26" s="16"/>
@@ -3296,16 +3554,22 @@
       <c r="E26" s="17"/>
     </row>
     <row r="27" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="20"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -3314,12 +3578,6 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3339,156 +3597,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="14" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="24"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BC992F-EE1E-47C0-8977-407185790E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD03E1F-D1EE-4043-8E2D-7597E37B91E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="153">
   <si>
     <t>S No</t>
   </si>
@@ -493,6 +493,12 @@
   </si>
   <si>
     <t>Pending</t>
+  </si>
+  <si>
+    <t>Ariyan Khan</t>
+  </si>
+  <si>
+    <t>Muhammad Ismail</t>
   </si>
 </sst>
 </file>
@@ -746,12 +752,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -760,6 +760,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1092,6 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1135,7 +1142,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1164,7 +1171,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1249,7 +1256,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1303,7 +1310,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1330,7 +1337,7 @@
       </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1357,7 +1364,7 @@
       </c>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1382,7 +1389,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1409,7 +1416,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1434,7 +1441,7 @@
       </c>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1463,7 +1470,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1490,7 +1497,7 @@
       </c>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1515,7 +1522,7 @@
       </c>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1540,7 +1547,7 @@
       </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1569,7 +1576,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1594,7 +1601,7 @@
       </c>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1619,7 +1626,7 @@
       </c>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1644,7 +1651,7 @@
       </c>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1669,7 +1676,7 @@
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1698,7 +1705,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1725,7 +1732,7 @@
       </c>
       <c r="I23" s="6"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1750,7 +1757,7 @@
       </c>
       <c r="I24" s="6"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1775,7 +1782,7 @@
       </c>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1804,7 +1811,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1831,7 +1838,7 @@
       </c>
       <c r="I27" s="6"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1856,7 +1863,7 @@
       </c>
       <c r="I28" s="6"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1883,7 +1890,7 @@
       </c>
       <c r="I29" s="6"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1910,7 +1917,7 @@
       </c>
       <c r="I30" s="6"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1935,7 +1942,7 @@
       </c>
       <c r="I31" s="6"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1962,7 +1969,7 @@
       </c>
       <c r="I32" s="6"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1991,7 +1998,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2018,7 +2025,7 @@
       </c>
       <c r="I34" s="6"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2043,7 +2050,7 @@
       </c>
       <c r="I35" s="6"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2066,7 +2073,7 @@
       </c>
       <c r="I36" s="6"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2091,7 +2098,7 @@
       </c>
       <c r="I37" s="6"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2118,7 +2125,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2143,7 +2150,7 @@
       </c>
       <c r="I39" s="6"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2172,7 +2179,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2197,7 +2204,7 @@
       </c>
       <c r="I41" s="6"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2222,7 +2229,7 @@
       </c>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2330,7 +2337,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2357,7 +2364,7 @@
       </c>
       <c r="I47" s="6"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2380,7 +2387,7 @@
       </c>
       <c r="I48" s="6"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2403,7 +2410,7 @@
       </c>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2432,7 +2439,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2459,7 +2466,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2551,18 +2558,30 @@
       <c r="A55" s="2">
         <v>54</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
+      <c r="B55" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="E55" s="3"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I55" s="6"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F55" s="4">
+        <v>3053196212</v>
+      </c>
+      <c r="G55" s="5">
+        <v>45764</v>
+      </c>
+      <c r="H55" s="5">
+        <v>45766</v>
+      </c>
+      <c r="I55" s="6">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -2577,7 +2596,7 @@
       </c>
       <c r="I56" s="6"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2592,7 +2611,7 @@
       </c>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2607,7 +2626,7 @@
       </c>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2622,7 +2641,7 @@
       </c>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2637,7 +2656,7 @@
       </c>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2652,7 +2671,7 @@
       </c>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -2667,7 +2686,7 @@
       </c>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2682,7 +2701,7 @@
       </c>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -2697,7 +2716,7 @@
       </c>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2712,7 +2731,7 @@
       </c>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -2727,7 +2746,7 @@
       </c>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -2742,7 +2761,7 @@
       </c>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -2757,7 +2776,7 @@
       </c>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -2772,7 +2791,7 @@
       </c>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -2787,7 +2806,7 @@
       </c>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2802,7 +2821,7 @@
       </c>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -2817,7 +2836,7 @@
       </c>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2832,7 +2851,7 @@
       </c>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -2847,7 +2866,7 @@
       </c>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2862,7 +2881,7 @@
       </c>
       <c r="I75" s="6"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -2877,7 +2896,7 @@
       </c>
       <c r="I76" s="6"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -2892,7 +2911,7 @@
       </c>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -2907,7 +2926,7 @@
       </c>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -2922,7 +2941,7 @@
       </c>
       <c r="I79" s="6"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -2937,7 +2956,7 @@
       </c>
       <c r="I80" s="6"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -2952,7 +2971,7 @@
       </c>
       <c r="I81" s="6"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -2967,7 +2986,7 @@
       </c>
       <c r="I82" s="6"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -2982,7 +3001,7 @@
       </c>
       <c r="I83" s="6"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -2997,7 +3016,7 @@
       </c>
       <c r="I84" s="6"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -3012,7 +3031,7 @@
       </c>
       <c r="I85" s="6"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -3027,7 +3046,7 @@
       </c>
       <c r="I86" s="6"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -3042,7 +3061,7 @@
       </c>
       <c r="I87" s="6"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -3057,7 +3076,7 @@
       </c>
       <c r="I88" s="6"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -3072,7 +3091,7 @@
       </c>
       <c r="I89" s="6"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -3087,7 +3106,7 @@
       </c>
       <c r="I90" s="6"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -3102,7 +3121,7 @@
       </c>
       <c r="I91" s="6"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -3118,7 +3137,13 @@
       <c r="I92" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}"/>
+  <autoFilter ref="A1:I92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}">
+    <filterColumn colId="7">
+      <filters>
+        <dateGroupItem year="2025" month="4" day="19" dateTimeGrouping="day"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A1:I92">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$H1&lt;TODAY()</formula>
@@ -3436,13 +3461,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -3493,20 +3518,20 @@
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="22"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="20"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -3557,19 +3582,13 @@
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -3578,6 +3597,12 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD03E1F-D1EE-4043-8E2D-7597E37B91E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B81F2E-6CDD-4282-B505-10E0DBE4273B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="155">
   <si>
     <t>S No</t>
   </si>
@@ -499,6 +499,12 @@
   </si>
   <si>
     <t>Muhammad Ismail</t>
+  </si>
+  <si>
+    <t>Anabiya</t>
+  </si>
+  <si>
+    <t>C/o D.O</t>
   </si>
 </sst>
 </file>
@@ -752,6 +758,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -760,12 +772,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1098,7 +1104,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1142,7 +1147,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1171,7 +1176,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1256,7 +1261,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1310,7 +1315,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1337,7 +1342,7 @@
       </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1364,7 +1369,7 @@
       </c>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1389,7 +1394,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1416,7 +1421,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1441,7 +1446,7 @@
       </c>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1470,7 +1475,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1497,7 +1502,7 @@
       </c>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1547,7 +1552,7 @@
       </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1576,7 +1581,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1601,7 +1606,7 @@
       </c>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1626,7 +1631,7 @@
       </c>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1651,7 +1656,7 @@
       </c>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1676,7 +1681,7 @@
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1705,7 +1710,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1732,7 +1737,7 @@
       </c>
       <c r="I23" s="6"/>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1757,7 +1762,7 @@
       </c>
       <c r="I24" s="6"/>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1782,7 +1787,7 @@
       </c>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1811,7 +1816,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1838,7 +1843,7 @@
       </c>
       <c r="I27" s="6"/>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1863,7 +1868,7 @@
       </c>
       <c r="I28" s="6"/>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1890,7 +1895,7 @@
       </c>
       <c r="I29" s="6"/>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1917,7 +1922,7 @@
       </c>
       <c r="I30" s="6"/>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1942,7 +1947,7 @@
       </c>
       <c r="I31" s="6"/>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1969,7 +1974,7 @@
       </c>
       <c r="I32" s="6"/>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1998,7 +2003,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2025,7 +2030,7 @@
       </c>
       <c r="I34" s="6"/>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2050,7 +2055,7 @@
       </c>
       <c r="I35" s="6"/>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2073,7 +2078,7 @@
       </c>
       <c r="I36" s="6"/>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2098,7 +2103,7 @@
       </c>
       <c r="I37" s="6"/>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2125,7 +2130,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2150,7 +2155,7 @@
       </c>
       <c r="I39" s="6"/>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2179,7 +2184,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2204,7 +2209,7 @@
       </c>
       <c r="I41" s="6"/>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2229,7 +2234,7 @@
       </c>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2337,7 +2342,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2364,7 +2369,7 @@
       </c>
       <c r="I47" s="6"/>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2387,7 +2392,7 @@
       </c>
       <c r="I48" s="6"/>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2410,7 +2415,7 @@
       </c>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2439,7 +2444,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2466,7 +2471,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2581,11 +2586,13 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" s="3"/>
+      <c r="B56" s="3" t="s">
+        <v>153</v>
+      </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -2595,8 +2602,11 @@
         <v>144</v>
       </c>
       <c r="I56" s="6"/>
-    </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J56" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2611,7 +2621,7 @@
       </c>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2626,7 +2636,7 @@
       </c>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2641,7 +2651,7 @@
       </c>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2656,7 +2666,7 @@
       </c>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2671,7 +2681,7 @@
       </c>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -2686,7 +2696,7 @@
       </c>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2701,7 +2711,7 @@
       </c>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -2716,7 +2726,7 @@
       </c>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2731,7 +2741,7 @@
       </c>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -2746,7 +2756,7 @@
       </c>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -2761,7 +2771,7 @@
       </c>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -2776,7 +2786,7 @@
       </c>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -2791,7 +2801,7 @@
       </c>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -2806,7 +2816,7 @@
       </c>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2821,7 +2831,7 @@
       </c>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -2836,7 +2846,7 @@
       </c>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2851,7 +2861,7 @@
       </c>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -2866,7 +2876,7 @@
       </c>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2881,7 +2891,7 @@
       </c>
       <c r="I75" s="6"/>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -2896,7 +2906,7 @@
       </c>
       <c r="I76" s="6"/>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -2911,7 +2921,7 @@
       </c>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -2926,7 +2936,7 @@
       </c>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -2941,7 +2951,7 @@
       </c>
       <c r="I79" s="6"/>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -2956,7 +2966,7 @@
       </c>
       <c r="I80" s="6"/>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -2971,7 +2981,7 @@
       </c>
       <c r="I81" s="6"/>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -2986,7 +2996,7 @@
       </c>
       <c r="I82" s="6"/>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -3001,7 +3011,7 @@
       </c>
       <c r="I83" s="6"/>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -3016,7 +3026,7 @@
       </c>
       <c r="I84" s="6"/>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -3031,7 +3041,7 @@
       </c>
       <c r="I85" s="6"/>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -3046,7 +3056,7 @@
       </c>
       <c r="I86" s="6"/>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -3061,7 +3071,7 @@
       </c>
       <c r="I87" s="6"/>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -3076,7 +3086,7 @@
       </c>
       <c r="I88" s="6"/>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -3091,7 +3101,7 @@
       </c>
       <c r="I89" s="6"/>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -3106,7 +3116,7 @@
       </c>
       <c r="I90" s="6"/>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -3121,7 +3131,7 @@
       </c>
       <c r="I91" s="6"/>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -3137,19 +3147,14 @@
       <c r="I92" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}">
-    <filterColumn colId="7">
-      <filters>
-        <dateGroupItem year="2025" month="4" day="19" dateTimeGrouping="day"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}"/>
   <conditionalFormatting sqref="A1:I92">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$H1&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3461,13 +3466,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -3518,20 +3523,20 @@
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="22"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="20"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -3582,13 +3587,19 @@
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="22"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -3597,12 +3608,6 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B81F2E-6CDD-4282-B505-10E0DBE4273B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D12C26F-BB17-4BB5-B224-4B4388580F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="160">
   <si>
     <t>S No</t>
   </si>
@@ -505,6 +505,21 @@
   </si>
   <si>
     <t>C/o D.O</t>
+  </si>
+  <si>
+    <t>Qaiser</t>
+  </si>
+  <si>
+    <t>Inaya Fatima</t>
+  </si>
+  <si>
+    <t>Ijaz Ahmed</t>
+  </si>
+  <si>
+    <t>42501-6092987-5</t>
+  </si>
+  <si>
+    <t>c/o Miss Sajida</t>
   </si>
 </sst>
 </file>
@@ -758,12 +773,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -772,6 +781,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2610,7 +2625,9 @@
       <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" s="3"/>
+      <c r="B57" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -2625,7 +2642,9 @@
       <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" s="3"/>
+      <c r="B58" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -2640,16 +2659,33 @@
       <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I59" s="6"/>
+      <c r="B59" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F59" s="4">
+        <v>3075666019</v>
+      </c>
+      <c r="G59" s="5">
+        <v>45766</v>
+      </c>
+      <c r="H59" s="5">
+        <v>45770</v>
+      </c>
+      <c r="I59" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="J59" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
@@ -3466,13 +3502,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -3523,20 +3559,20 @@
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="22"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="20"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -3587,19 +3623,13 @@
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -3608,6 +3638,12 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D12C26F-BB17-4BB5-B224-4B4388580F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DE3468-10E3-481B-B8D9-F81CF6E359CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="165">
   <si>
     <t>S No</t>
   </si>
@@ -520,6 +520,21 @@
   </si>
   <si>
     <t>c/o Miss Sajida</t>
+  </si>
+  <si>
+    <t>Mustaqim Hussain</t>
+  </si>
+  <si>
+    <t>Zafar Hussain</t>
+  </si>
+  <si>
+    <t>43205-5592768-3</t>
+  </si>
+  <si>
+    <t>Muhammad Ramzan</t>
+  </si>
+  <si>
+    <t>42501-6420631-3</t>
   </si>
 </sst>
 </file>
@@ -1878,8 +1893,8 @@
       <c r="G28" s="5">
         <v>45755</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>144</v>
+      <c r="H28" s="5">
+        <v>45770</v>
       </c>
       <c r="I28" s="6"/>
     </row>
@@ -1905,8 +1920,8 @@
       <c r="G29" s="5">
         <v>45755</v>
       </c>
-      <c r="H29" s="5" t="s">
-        <v>144</v>
+      <c r="H29" s="5">
+        <v>45770</v>
       </c>
       <c r="I29" s="6"/>
     </row>
@@ -2595,7 +2610,7 @@
         <v>45764</v>
       </c>
       <c r="H55" s="5">
-        <v>45766</v>
+        <v>45771</v>
       </c>
       <c r="I55" s="6">
         <v>0.4375</v>
@@ -2691,31 +2706,59 @@
       <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I60" s="6"/>
+      <c r="B60" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F60" s="4">
+        <v>3146147223</v>
+      </c>
+      <c r="G60" s="5">
+        <v>45768</v>
+      </c>
+      <c r="H60" s="5">
+        <v>45770</v>
+      </c>
+      <c r="I60" s="6">
+        <v>0.39583333333333331</v>
+      </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I61" s="6"/>
+      <c r="B61" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F61" s="4">
+        <v>3012244916</v>
+      </c>
+      <c r="G61" s="5">
+        <v>45768</v>
+      </c>
+      <c r="H61" s="5">
+        <v>45770</v>
+      </c>
+      <c r="I61" s="6">
+        <v>0.39583333333333331</v>
+      </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2">

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DE3468-10E3-481B-B8D9-F81CF6E359CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05EC99F-02DE-4921-80FD-1374D36F7DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
-    <sheet name="Test Date" sheetId="2" r:id="rId2"/>
-    <sheet name="Test" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId4"/>
+    <sheet name="Admissions" sheetId="6" r:id="rId2"/>
+    <sheet name="Test Date" sheetId="2" r:id="rId3"/>
+    <sheet name="Test" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Registration!$A$1:$I$92</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="183">
   <si>
     <t>S No</t>
   </si>
@@ -535,6 +536,60 @@
   </si>
   <si>
     <t>42501-6420631-3</t>
+  </si>
+  <si>
+    <t>SR #</t>
+  </si>
+  <si>
+    <t>Semis Code</t>
+  </si>
+  <si>
+    <t>School Name</t>
+  </si>
+  <si>
+    <t>GR #</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Date of birth</t>
+  </si>
+  <si>
+    <t>Religion</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Admission Date</t>
+  </si>
+  <si>
+    <t>Father /Guardian CNIC</t>
+  </si>
+  <si>
+    <t>Contact Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siblings </t>
+  </si>
+  <si>
+    <t>GBPS Sindhi Jamaat</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>ECE (ROSE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Islam </t>
+  </si>
+  <si>
+    <t>SJCHS</t>
+  </si>
+  <si>
+    <t>STUDENT PROFILE 2025-2026</t>
   </si>
 </sst>
 </file>
@@ -545,7 +600,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -576,6 +631,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -591,7 +667,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -735,11 +811,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -788,6 +888,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,23 +903,72 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -3228,7 +3383,7 @@
   </sheetData>
   <autoFilter ref="A1:I92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}"/>
   <conditionalFormatting sqref="A1:I92">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$H1&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3238,6 +3393,1712 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACE4FB1-457D-4ABA-B740-EA58B1613A2C}">
+  <dimension ref="A1:O57"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="L2" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="29">
+        <v>1</v>
+      </c>
+      <c r="B3" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" s="30">
+        <v>910</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I3" s="33"/>
+      <c r="J3" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L3" s="35">
+        <v>45770</v>
+      </c>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="29">
+        <v>2</v>
+      </c>
+      <c r="B4" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="34"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I4" s="33"/>
+      <c r="J4" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K4" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L4" s="35"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="29">
+        <v>3</v>
+      </c>
+      <c r="B5" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="34"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I5" s="33"/>
+      <c r="J5" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L5" s="35"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="29">
+        <v>4</v>
+      </c>
+      <c r="B6" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D6" s="34"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L6" s="35"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="29">
+        <v>5</v>
+      </c>
+      <c r="B7" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" s="34"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I7" s="33"/>
+      <c r="J7" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L7" s="35"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="29">
+        <v>6</v>
+      </c>
+      <c r="B8" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="34"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L8" s="35"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="29">
+        <v>7</v>
+      </c>
+      <c r="B9" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" s="34"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I9" s="33"/>
+      <c r="J9" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L9" s="35"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+    </row>
+    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="29">
+        <v>8</v>
+      </c>
+      <c r="B10" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="34"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I10" s="33"/>
+      <c r="J10" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K10" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L10" s="35"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="29">
+        <v>9</v>
+      </c>
+      <c r="B11" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D11" s="34"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I11" s="33"/>
+      <c r="J11" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K11" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L11" s="35"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+    </row>
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="29">
+        <v>10</v>
+      </c>
+      <c r="B12" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="34"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I12" s="33"/>
+      <c r="J12" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K12" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L12" s="35"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="29">
+        <v>11</v>
+      </c>
+      <c r="B13" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="34"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I13" s="33"/>
+      <c r="J13" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K13" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L13" s="35"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="29">
+        <v>12</v>
+      </c>
+      <c r="B14" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" s="34"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I14" s="33"/>
+      <c r="J14" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L14" s="35"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+    </row>
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="29">
+        <v>13</v>
+      </c>
+      <c r="B15" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="34"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I15" s="33"/>
+      <c r="J15" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K15" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L15" s="35"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+    </row>
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="29">
+        <v>14</v>
+      </c>
+      <c r="B16" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" s="34"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K16" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L16" s="35"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+    </row>
+    <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="29">
+        <v>15</v>
+      </c>
+      <c r="B17" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" s="34"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I17" s="33"/>
+      <c r="J17" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K17" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L17" s="35"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="29">
+        <v>16</v>
+      </c>
+      <c r="B18" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="34"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I18" s="33"/>
+      <c r="J18" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K18" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L18" s="35"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="29">
+        <v>17</v>
+      </c>
+      <c r="B19" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="34"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I19" s="33"/>
+      <c r="J19" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K19" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L19" s="35"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="29">
+        <v>18</v>
+      </c>
+      <c r="B20" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I20" s="33"/>
+      <c r="J20" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K20" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L20" s="35"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+    </row>
+    <row r="21" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="29">
+        <v>19</v>
+      </c>
+      <c r="B21" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I21" s="33"/>
+      <c r="J21" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K21" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L21" s="35"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+    </row>
+    <row r="22" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="29">
+        <v>20</v>
+      </c>
+      <c r="B22" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" s="34"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I22" s="33"/>
+      <c r="J22" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K22" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L22" s="35"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="29">
+        <v>21</v>
+      </c>
+      <c r="B23" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D23" s="34"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I23" s="33"/>
+      <c r="J23" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K23" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L23" s="35"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="36"/>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="29">
+        <v>22</v>
+      </c>
+      <c r="B24" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D24" s="34"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I24" s="33"/>
+      <c r="J24" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K24" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L24" s="35"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="36"/>
+    </row>
+    <row r="25" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="29">
+        <v>23</v>
+      </c>
+      <c r="B25" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="34"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I25" s="33"/>
+      <c r="J25" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K25" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L25" s="35"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="36"/>
+    </row>
+    <row r="26" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="29">
+        <v>24</v>
+      </c>
+      <c r="B26" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D26" s="34"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I26" s="33"/>
+      <c r="J26" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K26" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L26" s="35"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="29">
+        <v>25</v>
+      </c>
+      <c r="B27" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="34"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I27" s="33"/>
+      <c r="J27" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K27" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L27" s="35"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="36"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="29">
+        <v>26</v>
+      </c>
+      <c r="B28" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D28" s="34"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I28" s="33"/>
+      <c r="J28" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K28" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L28" s="35"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
+    </row>
+    <row r="29" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="29">
+        <v>27</v>
+      </c>
+      <c r="B29" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D29" s="34"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I29" s="33"/>
+      <c r="J29" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K29" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L29" s="35"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="36"/>
+    </row>
+    <row r="30" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="29">
+        <v>28</v>
+      </c>
+      <c r="B30" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D30" s="34"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I30" s="33"/>
+      <c r="J30" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K30" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L30" s="35"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+    </row>
+    <row r="31" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="29">
+        <v>29</v>
+      </c>
+      <c r="B31" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" s="34"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I31" s="33"/>
+      <c r="J31" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K31" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L31" s="35"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="36"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="29">
+        <v>30</v>
+      </c>
+      <c r="B32" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D32" s="34"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I32" s="33"/>
+      <c r="J32" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K32" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L32" s="35"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="36"/>
+    </row>
+    <row r="33" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="29">
+        <v>31</v>
+      </c>
+      <c r="B33" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C33" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D33" s="34"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I33" s="33"/>
+      <c r="J33" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K33" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L33" s="35"/>
+      <c r="M33" s="36"/>
+      <c r="N33" s="36"/>
+      <c r="O33" s="36"/>
+    </row>
+    <row r="34" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="29">
+        <v>32</v>
+      </c>
+      <c r="B34" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C34" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D34" s="34"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I34" s="33"/>
+      <c r="J34" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K34" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L34" s="35"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="36"/>
+    </row>
+    <row r="35" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="29">
+        <v>33</v>
+      </c>
+      <c r="B35" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C35" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="34"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I35" s="33"/>
+      <c r="J35" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K35" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L35" s="35"/>
+      <c r="M35" s="36"/>
+      <c r="N35" s="36"/>
+      <c r="O35" s="36"/>
+    </row>
+    <row r="36" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="29">
+        <v>34</v>
+      </c>
+      <c r="B36" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C36" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" s="34"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I36" s="33"/>
+      <c r="J36" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K36" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L36" s="35"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="36"/>
+    </row>
+    <row r="37" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="29">
+        <v>35</v>
+      </c>
+      <c r="B37" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C37" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D37" s="34"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I37" s="33"/>
+      <c r="J37" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K37" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L37" s="35"/>
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="36"/>
+    </row>
+    <row r="38" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="29">
+        <v>36</v>
+      </c>
+      <c r="B38" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C38" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D38" s="34"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I38" s="33"/>
+      <c r="J38" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K38" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L38" s="35"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+    </row>
+    <row r="39" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="29">
+        <v>37</v>
+      </c>
+      <c r="B39" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C39" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D39" s="34"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I39" s="33"/>
+      <c r="J39" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K39" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L39" s="35"/>
+      <c r="M39" s="36"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="36"/>
+    </row>
+    <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="29">
+        <v>38</v>
+      </c>
+      <c r="B40" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C40" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D40" s="34"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I40" s="33"/>
+      <c r="J40" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K40" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L40" s="35"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="36"/>
+    </row>
+    <row r="41" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="29">
+        <v>39</v>
+      </c>
+      <c r="B41" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C41" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D41" s="34"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I41" s="33"/>
+      <c r="J41" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K41" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L41" s="35"/>
+      <c r="M41" s="36"/>
+      <c r="N41" s="36"/>
+      <c r="O41" s="36"/>
+    </row>
+    <row r="42" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="29">
+        <v>40</v>
+      </c>
+      <c r="B42" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C42" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D42" s="34"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I42" s="33"/>
+      <c r="J42" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K42" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L42" s="35"/>
+      <c r="M42" s="36"/>
+      <c r="N42" s="36"/>
+      <c r="O42" s="36"/>
+    </row>
+    <row r="43" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="29">
+        <v>41</v>
+      </c>
+      <c r="B43" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C43" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D43" s="34"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I43" s="33"/>
+      <c r="J43" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K43" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L43" s="35"/>
+      <c r="M43" s="36"/>
+      <c r="N43" s="36"/>
+      <c r="O43" s="36"/>
+    </row>
+    <row r="44" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="29">
+        <v>42</v>
+      </c>
+      <c r="B44" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C44" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D44" s="34"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I44" s="33"/>
+      <c r="J44" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K44" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L44" s="35"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="36"/>
+    </row>
+    <row r="45" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="29">
+        <v>43</v>
+      </c>
+      <c r="B45" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C45" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D45" s="34"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I45" s="33"/>
+      <c r="J45" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K45" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L45" s="35"/>
+      <c r="M45" s="36"/>
+      <c r="N45" s="36"/>
+      <c r="O45" s="36"/>
+    </row>
+    <row r="46" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="29">
+        <v>44</v>
+      </c>
+      <c r="B46" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C46" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D46" s="34"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I46" s="33"/>
+      <c r="J46" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K46" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L46" s="35"/>
+      <c r="M46" s="36"/>
+      <c r="N46" s="36"/>
+      <c r="O46" s="36"/>
+    </row>
+    <row r="47" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="29">
+        <v>45</v>
+      </c>
+      <c r="B47" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C47" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D47" s="34"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I47" s="33"/>
+      <c r="J47" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K47" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L47" s="35"/>
+      <c r="M47" s="36"/>
+      <c r="N47" s="36"/>
+      <c r="O47" s="36"/>
+    </row>
+    <row r="48" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="29">
+        <v>46</v>
+      </c>
+      <c r="B48" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C48" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D48" s="34"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I48" s="33"/>
+      <c r="J48" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K48" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L48" s="35"/>
+      <c r="M48" s="36"/>
+      <c r="N48" s="36"/>
+      <c r="O48" s="36"/>
+    </row>
+    <row r="49" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="29">
+        <v>47</v>
+      </c>
+      <c r="B49" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C49" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D49" s="34"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I49" s="33"/>
+      <c r="J49" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K49" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L49" s="35"/>
+      <c r="M49" s="36"/>
+      <c r="N49" s="36"/>
+      <c r="O49" s="36"/>
+    </row>
+    <row r="50" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="29">
+        <v>48</v>
+      </c>
+      <c r="B50" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C50" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D50" s="34"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I50" s="33"/>
+      <c r="J50" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K50" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L50" s="35"/>
+      <c r="M50" s="36"/>
+      <c r="N50" s="36"/>
+      <c r="O50" s="36"/>
+    </row>
+    <row r="51" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="29">
+        <v>49</v>
+      </c>
+      <c r="B51" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C51" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D51" s="34"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I51" s="33"/>
+      <c r="J51" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K51" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L51" s="35"/>
+      <c r="M51" s="36"/>
+      <c r="N51" s="36"/>
+      <c r="O51" s="36"/>
+    </row>
+    <row r="52" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="29">
+        <v>50</v>
+      </c>
+      <c r="B52" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C52" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" s="34"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I52" s="33"/>
+      <c r="J52" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K52" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L52" s="35"/>
+      <c r="M52" s="36"/>
+      <c r="N52" s="36"/>
+      <c r="O52" s="36"/>
+    </row>
+    <row r="53" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="29">
+        <v>51</v>
+      </c>
+      <c r="B53" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C53" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D53" s="34"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I53" s="33"/>
+      <c r="J53" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K53" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L53" s="35"/>
+      <c r="M53" s="36"/>
+      <c r="N53" s="36"/>
+      <c r="O53" s="36"/>
+    </row>
+    <row r="54" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="29">
+        <v>52</v>
+      </c>
+      <c r="B54" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C54" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D54" s="34"/>
+      <c r="E54" s="37"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I54" s="33"/>
+      <c r="J54" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K54" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L54" s="35"/>
+      <c r="M54" s="36"/>
+      <c r="N54" s="36"/>
+      <c r="O54" s="36"/>
+    </row>
+    <row r="55" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="29">
+        <v>53</v>
+      </c>
+      <c r="B55" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C55" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D55" s="34"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I55" s="33"/>
+      <c r="J55" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K55" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L55" s="35"/>
+      <c r="M55" s="36"/>
+      <c r="N55" s="36"/>
+      <c r="O55" s="36"/>
+    </row>
+    <row r="56" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="29">
+        <v>54</v>
+      </c>
+      <c r="B56" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C56" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D56" s="34"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I56" s="33"/>
+      <c r="J56" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K56" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L56" s="35"/>
+      <c r="M56" s="36"/>
+      <c r="N56" s="36"/>
+      <c r="O56" s="36"/>
+    </row>
+    <row r="57" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="29">
+        <v>55</v>
+      </c>
+      <c r="B57" s="29">
+        <v>408170153</v>
+      </c>
+      <c r="C57" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D57" s="34"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I57" s="33"/>
+      <c r="J57" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K57" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L57" s="35"/>
+      <c r="M57" s="36"/>
+      <c r="N57" s="36"/>
+      <c r="O57" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D1:D57">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1:M57">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1:N57">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8155FF31-57FB-40EF-86BA-1F383C661028}">
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3535,7 +5396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A255C02-D416-4376-BD1B-F40DA3AFB8AE}">
   <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3545,13 +5406,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -3602,20 +5463,20 @@
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="22"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="20"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -3666,13 +5527,19 @@
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="22"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -3681,18 +5548,12 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939DF1D5-8D30-40AA-BC5E-4A0C1B85C46B}">
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05EC99F-02DE-4921-80FD-1374D36F7DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E37C27-67D4-4B73-8763-2BAF4DBF4651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Test Date" sheetId="2" r:id="rId3"/>
     <sheet name="Test" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Registration!$A$1:$I$92</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="204">
   <si>
     <t>S No</t>
   </si>
@@ -590,6 +591,69 @@
   </si>
   <si>
     <t>STUDENT PROFILE 2025-2026</t>
+  </si>
+  <si>
+    <t>Zeeshan Ali</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>433029067105-3</t>
+  </si>
+  <si>
+    <t>Muhammad Qaiser</t>
+  </si>
+  <si>
+    <t>Muhammad Qasim Mugheri</t>
+  </si>
+  <si>
+    <t>43207-6937586-7</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>42501-5636670-9</t>
+  </si>
+  <si>
+    <t>42201-7552064-7</t>
+  </si>
+  <si>
+    <t>Sajid Jamali</t>
+  </si>
+  <si>
+    <t>Anabiya Tabassum</t>
+  </si>
+  <si>
+    <t>Ghulam Mujtaba</t>
+  </si>
+  <si>
+    <t>41409-1260569-1</t>
+  </si>
+  <si>
+    <t>Class-1</t>
+  </si>
+  <si>
+    <t>Mir Ghulam Mustafa Bhutto</t>
+  </si>
+  <si>
+    <t>Airah Alber</t>
+  </si>
+  <si>
+    <t>Abdul Alber</t>
+  </si>
+  <si>
+    <t>42501-0629176-5</t>
+  </si>
+  <si>
+    <t>Marwa Bibi</t>
+  </si>
+  <si>
+    <t>Muhammad Huzzaifa</t>
+  </si>
+  <si>
+    <t>Zain Ullah</t>
   </si>
 </sst>
 </file>
@@ -882,36 +946,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -934,11 +968,51 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3383,7 +3457,7 @@
   </sheetData>
   <autoFilter ref="A1:I92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}"/>
   <conditionalFormatting sqref="A1:I92">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$H1&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3401,8 +3475,8 @@
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -3415,23 +3489,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -3458,16 +3532,16 @@
       <c r="H2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="I2" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="17" t="s">
         <v>171</v>
       </c>
       <c r="K2" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="18" t="s">
         <v>173</v>
       </c>
       <c r="M2" s="14" t="s">
@@ -3481,1618 +3555,1904 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="29">
+      <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="19">
         <v>408170153</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D3" s="30">
+      <c r="D3" s="20">
         <v>910</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="29" t="s">
+      <c r="E3" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="33"/>
-      <c r="J3" s="34" t="s">
+      <c r="I3" s="23">
+        <v>43711</v>
+      </c>
+      <c r="J3" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K3" s="29" t="s">
+      <c r="K3" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L3" s="35">
+      <c r="L3" s="25">
         <v>45770</v>
       </c>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
+      <c r="M3" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="N3" s="26">
+        <v>3008912581</v>
+      </c>
+      <c r="O3" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="29">
+      <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="19">
         <v>408170153</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29" t="s">
+      <c r="D4" s="24">
+        <v>911</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="H4" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I4" s="33"/>
-      <c r="J4" s="34" t="s">
+      <c r="I4" s="23">
+        <v>44013</v>
+      </c>
+      <c r="J4" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L4" s="35"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
+      <c r="L4" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="N4" s="26">
+        <v>3408550574</v>
+      </c>
+      <c r="O4" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="29">
+      <c r="A5" s="19">
         <v>3</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="19">
         <v>408170153</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29" t="s">
+      <c r="D5" s="20">
+        <v>912</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I5" s="33"/>
-      <c r="J5" s="34" t="s">
+      <c r="I5" s="23">
+        <v>43832</v>
+      </c>
+      <c r="J5" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K5" s="29" t="s">
+      <c r="K5" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L5" s="35"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
+      <c r="L5" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="N5" s="26">
+        <v>3022345160</v>
+      </c>
+      <c r="O5" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="29">
+      <c r="A6" s="19">
         <v>4</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="19">
         <v>408170153</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29" t="s">
+      <c r="D6" s="24">
+        <v>913</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="H6" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34" t="s">
+      <c r="I6" s="23">
+        <v>43574</v>
+      </c>
+      <c r="J6" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K6" s="29" t="s">
+      <c r="K6" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L6" s="35"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
+      <c r="L6" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="N6" s="26">
+        <v>3152717911</v>
+      </c>
+      <c r="O6" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="29">
+      <c r="A7" s="19">
         <v>5</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="19">
         <v>408170153</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29" t="s">
+      <c r="D7" s="20">
+        <v>914</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I7" s="33"/>
-      <c r="J7" s="34" t="s">
+      <c r="I7" s="23">
+        <v>43879</v>
+      </c>
+      <c r="J7" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L7" s="35"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
+      <c r="L7" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M7" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="N7" s="26">
+        <v>3213522748</v>
+      </c>
+      <c r="O7" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="29">
+      <c r="A8" s="19">
         <v>6</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="19">
         <v>408170153</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29" t="s">
+      <c r="D8" s="24">
+        <v>915</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="H8" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I8" s="33"/>
-      <c r="J8" s="34" t="s">
+      <c r="I8" s="23">
+        <v>43471</v>
+      </c>
+      <c r="J8" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K8" s="29" t="s">
+      <c r="K8" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L8" s="35"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
+      <c r="L8" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M8" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="N8" s="26">
+        <v>3472586633</v>
+      </c>
+      <c r="O8" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="19">
         <v>7</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="19">
         <v>408170153</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29" t="s">
+      <c r="D9" s="20">
+        <v>916</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="H9" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I9" s="33"/>
-      <c r="J9" s="34" t="s">
+      <c r="I9" s="23">
+        <v>44143</v>
+      </c>
+      <c r="J9" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K9" s="29" t="s">
+      <c r="K9" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L9" s="35"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
+      <c r="L9" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M9" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="N9" s="26">
+        <v>3368603595</v>
+      </c>
+      <c r="O9" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="29">
+      <c r="A10" s="19">
         <v>8</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="19">
         <v>408170153</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29" t="s">
+      <c r="D10" s="24">
+        <v>917</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="H10" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I10" s="33"/>
-      <c r="J10" s="34" t="s">
+      <c r="I10" s="23">
+        <v>44096</v>
+      </c>
+      <c r="J10" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K10" s="29" t="s">
+      <c r="K10" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L10" s="35"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
+      <c r="L10" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M10" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="N10" s="26">
+        <v>3158719338</v>
+      </c>
+      <c r="O10" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="29">
+      <c r="A11" s="19">
         <v>9</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="19">
         <v>408170153</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D11" s="34"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29" t="s">
+      <c r="D11" s="20">
+        <v>918</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="I11" s="23">
+        <v>43088</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="L11" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M11" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>10</v>
+      </c>
+      <c r="B12" s="19">
+        <v>408170153</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="24">
+        <v>919</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="H12" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I11" s="33"/>
-      <c r="J11" s="34" t="s">
+      <c r="I12" s="23">
+        <v>44069</v>
+      </c>
+      <c r="J12" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K11" s="29" t="s">
+      <c r="K12" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L11" s="35"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="29">
+      <c r="L12" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M12" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="N12" s="26">
+        <v>3333115124</v>
+      </c>
+      <c r="O12" s="26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
+        <v>11</v>
+      </c>
+      <c r="B13" s="19">
+        <v>408170153</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="20">
+        <v>920</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="I13" s="23">
+        <v>43881</v>
+      </c>
+      <c r="J13" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="L13" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M13" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="N13" s="26">
+        <v>3412510302</v>
+      </c>
+      <c r="O13" s="26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
+        <v>12</v>
+      </c>
+      <c r="B14" s="19">
+        <v>408170153</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" s="24">
+        <v>921</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="I14" s="23">
+        <v>43936</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="L14" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M14" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="26">
+        <v>3471801620</v>
+      </c>
+      <c r="O14" s="26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
+        <v>13</v>
+      </c>
+      <c r="B15" s="19">
+        <v>408170153</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="20">
+        <v>922</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="I15" s="23">
+        <v>43871</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="L15" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M15" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="26">
+        <v>3471801620</v>
+      </c>
+      <c r="O15" s="26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
+        <v>14</v>
+      </c>
+      <c r="B16" s="19">
+        <v>408170153</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" s="24">
+        <v>923</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="I16" s="23">
+        <v>43936</v>
+      </c>
+      <c r="J16" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="L16" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M16" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="26">
+        <v>3471801620</v>
+      </c>
+      <c r="O16" s="26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
+        <v>15</v>
+      </c>
+      <c r="B17" s="19">
+        <v>408170153</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" s="20">
+        <v>924</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="I17" s="23">
+        <v>43723</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="L17" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M17" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="N17" s="26">
+        <v>3146147223</v>
+      </c>
+      <c r="O17" s="26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
+        <v>16</v>
+      </c>
+      <c r="B18" s="19">
+        <v>408170153</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="24">
+        <v>925</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="29">
+      <c r="G18" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="I18" s="23">
+        <v>43930</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="L18" s="25">
+        <v>45770</v>
+      </c>
+      <c r="M18" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="N18" s="26">
+        <v>3437668872</v>
+      </c>
+      <c r="O18" s="26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="19">
         <v>408170153</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C19" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D12" s="34"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29" t="s">
+      <c r="D19" s="20">
+        <v>926</v>
+      </c>
+      <c r="E19" s="27"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I12" s="33"/>
-      <c r="J12" s="34" t="s">
+      <c r="I19" s="23"/>
+      <c r="J19" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K12" s="29" t="s">
+      <c r="K19" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L12" s="35"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="29">
-        <v>11</v>
-      </c>
-      <c r="B13" s="29">
+      <c r="L19" s="25"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>18</v>
+      </c>
+      <c r="B20" s="19">
         <v>408170153</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C20" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="34"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29" t="s">
+      <c r="D20" s="24">
+        <v>927</v>
+      </c>
+      <c r="E20" s="27"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I13" s="33"/>
-      <c r="J13" s="34" t="s">
+      <c r="I20" s="23"/>
+      <c r="J20" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K13" s="29" t="s">
+      <c r="K20" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L13" s="35"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="29">
-        <v>12</v>
-      </c>
-      <c r="B14" s="29">
+      <c r="L20" s="25"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+    </row>
+    <row r="21" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
+        <v>19</v>
+      </c>
+      <c r="B21" s="19">
         <v>408170153</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C21" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D14" s="34"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29" t="s">
+      <c r="D21" s="20">
+        <v>928</v>
+      </c>
+      <c r="E21" s="27"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I14" s="33"/>
-      <c r="J14" s="34" t="s">
+      <c r="I21" s="23"/>
+      <c r="J21" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K14" s="29" t="s">
+      <c r="K21" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L14" s="35"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="29">
-        <v>13</v>
-      </c>
-      <c r="B15" s="29">
+      <c r="L21" s="25"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+    </row>
+    <row r="22" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
+        <v>20</v>
+      </c>
+      <c r="B22" s="19">
         <v>408170153</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C22" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D15" s="34"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29" t="s">
+      <c r="D22" s="24"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I15" s="33"/>
-      <c r="J15" s="34" t="s">
+      <c r="I22" s="23"/>
+      <c r="J22" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K15" s="29" t="s">
+      <c r="K22" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L15" s="35"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="29">
-        <v>14</v>
-      </c>
-      <c r="B16" s="29">
+      <c r="L22" s="25"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
+        <v>21</v>
+      </c>
+      <c r="B23" s="19">
         <v>408170153</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C23" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D16" s="34"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29" t="s">
+      <c r="D23" s="24"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I16" s="33"/>
-      <c r="J16" s="34" t="s">
+      <c r="I23" s="23"/>
+      <c r="J23" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K16" s="29" t="s">
+      <c r="K23" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L16" s="35"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-    </row>
-    <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="29">
-        <v>15</v>
-      </c>
-      <c r="B17" s="29">
+      <c r="L23" s="25"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="19">
+        <v>22</v>
+      </c>
+      <c r="B24" s="19">
         <v>408170153</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C24" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D17" s="34"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29" t="s">
+      <c r="D24" s="24"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I17" s="33"/>
-      <c r="J17" s="34" t="s">
+      <c r="I24" s="23"/>
+      <c r="J24" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K17" s="29" t="s">
+      <c r="K24" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L17" s="35"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-    </row>
-    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="29">
-        <v>16</v>
-      </c>
-      <c r="B18" s="29">
+      <c r="L24" s="25"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+    </row>
+    <row r="25" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
+        <v>23</v>
+      </c>
+      <c r="B25" s="19">
         <v>408170153</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C25" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D18" s="34"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29" t="s">
+      <c r="D25" s="24"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I18" s="33"/>
-      <c r="J18" s="34" t="s">
+      <c r="I25" s="23"/>
+      <c r="J25" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K25" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L18" s="35"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-    </row>
-    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="29">
-        <v>17</v>
-      </c>
-      <c r="B19" s="29">
+      <c r="L25" s="25"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+    </row>
+    <row r="26" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
+        <v>24</v>
+      </c>
+      <c r="B26" s="19">
         <v>408170153</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C26" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D19" s="34"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29" t="s">
+      <c r="D26" s="24"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I19" s="33"/>
-      <c r="J19" s="34" t="s">
+      <c r="I26" s="23"/>
+      <c r="J26" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K19" s="29" t="s">
+      <c r="K26" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L19" s="35"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-    </row>
-    <row r="20" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="29">
-        <v>18</v>
-      </c>
-      <c r="B20" s="29">
+      <c r="L26" s="25"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
+        <v>25</v>
+      </c>
+      <c r="B27" s="19">
         <v>408170153</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C27" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D20" s="34"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29" t="s">
+      <c r="D27" s="24"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I20" s="33"/>
-      <c r="J20" s="34" t="s">
+      <c r="I27" s="23"/>
+      <c r="J27" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K20" s="29" t="s">
+      <c r="K27" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L20" s="35"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-    </row>
-    <row r="21" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="29">
-        <v>19</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="L27" s="25"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
+        <v>26</v>
+      </c>
+      <c r="B28" s="19">
         <v>408170153</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C28" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29" t="s">
+      <c r="D28" s="24"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I21" s="33"/>
-      <c r="J21" s="34" t="s">
+      <c r="I28" s="23"/>
+      <c r="J28" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K21" s="29" t="s">
+      <c r="K28" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L21" s="35"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-    </row>
-    <row r="22" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="29">
-        <v>20</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="L28" s="25"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+    </row>
+    <row r="29" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="19">
+        <v>27</v>
+      </c>
+      <c r="B29" s="19">
         <v>408170153</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C29" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29" t="s">
+      <c r="D29" s="24"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I22" s="33"/>
-      <c r="J22" s="34" t="s">
+      <c r="I29" s="23"/>
+      <c r="J29" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K22" s="29" t="s">
+      <c r="K29" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L22" s="35"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-    </row>
-    <row r="23" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="29">
-        <v>21</v>
-      </c>
-      <c r="B23" s="29">
+      <c r="L29" s="25"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+    </row>
+    <row r="30" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="19">
+        <v>28</v>
+      </c>
+      <c r="B30" s="19">
         <v>408170153</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C30" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D23" s="34"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29" t="s">
+      <c r="D30" s="24"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I23" s="33"/>
-      <c r="J23" s="34" t="s">
+      <c r="I30" s="23"/>
+      <c r="J30" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K23" s="29" t="s">
+      <c r="K30" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L23" s="35"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-    </row>
-    <row r="24" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="29">
-        <v>22</v>
-      </c>
-      <c r="B24" s="29">
+      <c r="L30" s="25"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+    </row>
+    <row r="31" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="19">
+        <v>29</v>
+      </c>
+      <c r="B31" s="19">
         <v>408170153</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C31" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D24" s="34"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29" t="s">
+      <c r="D31" s="24"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I24" s="33"/>
-      <c r="J24" s="34" t="s">
+      <c r="I31" s="23"/>
+      <c r="J31" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K24" s="29" t="s">
+      <c r="K31" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L24" s="35"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="36"/>
-      <c r="O24" s="36"/>
-    </row>
-    <row r="25" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="29">
-        <v>23</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="L31" s="25"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="19">
+        <v>30</v>
+      </c>
+      <c r="B32" s="19">
         <v>408170153</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C32" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D25" s="34"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29" t="s">
+      <c r="D32" s="24"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I25" s="33"/>
-      <c r="J25" s="34" t="s">
+      <c r="I32" s="23"/>
+      <c r="J32" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K25" s="29" t="s">
+      <c r="K32" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L25" s="35"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="36"/>
-    </row>
-    <row r="26" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="29">
-        <v>24</v>
-      </c>
-      <c r="B26" s="29">
+      <c r="L32" s="25"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+    </row>
+    <row r="33" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="19">
+        <v>31</v>
+      </c>
+      <c r="B33" s="19">
         <v>408170153</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C33" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D26" s="34"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29" t="s">
+      <c r="D33" s="24"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I26" s="33"/>
-      <c r="J26" s="34" t="s">
+      <c r="I33" s="23"/>
+      <c r="J33" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K26" s="29" t="s">
+      <c r="K33" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L26" s="35"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-    </row>
-    <row r="27" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="29">
-        <v>25</v>
-      </c>
-      <c r="B27" s="29">
+      <c r="L33" s="25"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+    </row>
+    <row r="34" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="19">
+        <v>32</v>
+      </c>
+      <c r="B34" s="19">
         <v>408170153</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C34" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D27" s="34"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29" t="s">
+      <c r="D34" s="24"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I27" s="33"/>
-      <c r="J27" s="34" t="s">
+      <c r="I34" s="23"/>
+      <c r="J34" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K27" s="29" t="s">
+      <c r="K34" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L27" s="35"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="36"/>
-      <c r="O27" s="36"/>
-    </row>
-    <row r="28" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="29">
-        <v>26</v>
-      </c>
-      <c r="B28" s="29">
+      <c r="L34" s="25"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+    </row>
+    <row r="35" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="19">
+        <v>33</v>
+      </c>
+      <c r="B35" s="19">
         <v>408170153</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C35" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D28" s="34"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29" t="s">
+      <c r="D35" s="24"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I28" s="33"/>
-      <c r="J28" s="34" t="s">
+      <c r="I35" s="23"/>
+      <c r="J35" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K28" s="29" t="s">
+      <c r="K35" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L28" s="35"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="36"/>
-      <c r="O28" s="36"/>
-    </row>
-    <row r="29" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="29">
-        <v>27</v>
-      </c>
-      <c r="B29" s="29">
+      <c r="L35" s="25"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+    </row>
+    <row r="36" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="19">
+        <v>34</v>
+      </c>
+      <c r="B36" s="19">
         <v>408170153</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C36" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D29" s="34"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29" t="s">
+      <c r="D36" s="24"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I29" s="33"/>
-      <c r="J29" s="34" t="s">
+      <c r="I36" s="23"/>
+      <c r="J36" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K29" s="29" t="s">
+      <c r="K36" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L29" s="35"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="36"/>
-      <c r="O29" s="36"/>
-    </row>
-    <row r="30" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="29">
-        <v>28</v>
-      </c>
-      <c r="B30" s="29">
+      <c r="L36" s="25"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+    </row>
+    <row r="37" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="19">
+        <v>35</v>
+      </c>
+      <c r="B37" s="19">
         <v>408170153</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C37" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D30" s="34"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29" t="s">
+      <c r="D37" s="24"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I30" s="33"/>
-      <c r="J30" s="34" t="s">
+      <c r="I37" s="23"/>
+      <c r="J37" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K30" s="29" t="s">
+      <c r="K37" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L30" s="35"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="36"/>
-      <c r="O30" s="36"/>
-    </row>
-    <row r="31" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="29">
-        <v>29</v>
-      </c>
-      <c r="B31" s="29">
+      <c r="L37" s="25"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+    </row>
+    <row r="38" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="19">
+        <v>36</v>
+      </c>
+      <c r="B38" s="19">
         <v>408170153</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C38" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D31" s="34"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29" t="s">
+      <c r="D38" s="24"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I31" s="33"/>
-      <c r="J31" s="34" t="s">
+      <c r="I38" s="23"/>
+      <c r="J38" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K31" s="29" t="s">
+      <c r="K38" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L31" s="35"/>
-      <c r="M31" s="36"/>
-      <c r="N31" s="36"/>
-      <c r="O31" s="36"/>
-    </row>
-    <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="29">
-        <v>30</v>
-      </c>
-      <c r="B32" s="29">
+      <c r="L38" s="25"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+    </row>
+    <row r="39" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="19">
+        <v>37</v>
+      </c>
+      <c r="B39" s="19">
         <v>408170153</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C39" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29" t="s">
+      <c r="D39" s="24"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I32" s="33"/>
-      <c r="J32" s="34" t="s">
+      <c r="I39" s="23"/>
+      <c r="J39" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K32" s="29" t="s">
+      <c r="K39" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L32" s="35"/>
-      <c r="M32" s="36"/>
-      <c r="N32" s="36"/>
-      <c r="O32" s="36"/>
-    </row>
-    <row r="33" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="29">
-        <v>31</v>
-      </c>
-      <c r="B33" s="29">
+      <c r="L39" s="25"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+    </row>
+    <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="19">
+        <v>38</v>
+      </c>
+      <c r="B40" s="19">
         <v>408170153</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C40" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D33" s="34"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29" t="s">
+      <c r="D40" s="24"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I33" s="33"/>
-      <c r="J33" s="34" t="s">
+      <c r="I40" s="23"/>
+      <c r="J40" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K33" s="29" t="s">
+      <c r="K40" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L33" s="35"/>
-      <c r="M33" s="36"/>
-      <c r="N33" s="36"/>
-      <c r="O33" s="36"/>
-    </row>
-    <row r="34" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="29">
-        <v>32</v>
-      </c>
-      <c r="B34" s="29">
+      <c r="L40" s="25"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
+    </row>
+    <row r="41" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="19">
+        <v>39</v>
+      </c>
+      <c r="B41" s="19">
         <v>408170153</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C41" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D34" s="34"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29" t="s">
+      <c r="D41" s="24"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I34" s="33"/>
-      <c r="J34" s="34" t="s">
+      <c r="I41" s="23"/>
+      <c r="J41" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K34" s="29" t="s">
+      <c r="K41" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L34" s="35"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-    </row>
-    <row r="35" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="29">
-        <v>33</v>
-      </c>
-      <c r="B35" s="29">
+      <c r="L41" s="25"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
+    </row>
+    <row r="42" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="19">
+        <v>40</v>
+      </c>
+      <c r="B42" s="19">
         <v>408170153</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C42" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D35" s="34"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29" t="s">
+      <c r="D42" s="24"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I35" s="33"/>
-      <c r="J35" s="34" t="s">
+      <c r="I42" s="23"/>
+      <c r="J42" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K35" s="29" t="s">
+      <c r="K42" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L35" s="35"/>
-      <c r="M35" s="36"/>
-      <c r="N35" s="36"/>
-      <c r="O35" s="36"/>
-    </row>
-    <row r="36" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="29">
-        <v>34</v>
-      </c>
-      <c r="B36" s="29">
+      <c r="L42" s="25"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+    </row>
+    <row r="43" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="19">
+        <v>41</v>
+      </c>
+      <c r="B43" s="19">
         <v>408170153</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C43" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="34"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29" t="s">
+      <c r="D43" s="24"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I36" s="33"/>
-      <c r="J36" s="34" t="s">
+      <c r="I43" s="23"/>
+      <c r="J43" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K36" s="29" t="s">
+      <c r="K43" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L36" s="35"/>
-      <c r="M36" s="36"/>
-      <c r="N36" s="36"/>
-      <c r="O36" s="36"/>
-    </row>
-    <row r="37" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="29">
-        <v>35</v>
-      </c>
-      <c r="B37" s="29">
+      <c r="L43" s="25"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="26"/>
+      <c r="O43" s="26"/>
+    </row>
+    <row r="44" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="19">
+        <v>42</v>
+      </c>
+      <c r="B44" s="19">
         <v>408170153</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C44" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D37" s="34"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29" t="s">
+      <c r="D44" s="24"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I37" s="33"/>
-      <c r="J37" s="34" t="s">
+      <c r="I44" s="23"/>
+      <c r="J44" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K37" s="29" t="s">
+      <c r="K44" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L37" s="35"/>
-      <c r="M37" s="36"/>
-      <c r="N37" s="36"/>
-      <c r="O37" s="36"/>
-    </row>
-    <row r="38" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="29">
-        <v>36</v>
-      </c>
-      <c r="B38" s="29">
+      <c r="L44" s="25"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="26"/>
+      <c r="O44" s="26"/>
+    </row>
+    <row r="45" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="19">
+        <v>43</v>
+      </c>
+      <c r="B45" s="19">
         <v>408170153</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C45" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D38" s="34"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29" t="s">
+      <c r="D45" s="24"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I38" s="33"/>
-      <c r="J38" s="34" t="s">
+      <c r="I45" s="23"/>
+      <c r="J45" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K38" s="29" t="s">
+      <c r="K45" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L38" s="35"/>
-      <c r="M38" s="36"/>
-      <c r="N38" s="36"/>
-      <c r="O38" s="36"/>
-    </row>
-    <row r="39" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="29">
-        <v>37</v>
-      </c>
-      <c r="B39" s="29">
+      <c r="L45" s="25"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="26"/>
+      <c r="O45" s="26"/>
+    </row>
+    <row r="46" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="19">
+        <v>44</v>
+      </c>
+      <c r="B46" s="19">
         <v>408170153</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C46" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D39" s="34"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29" t="s">
+      <c r="D46" s="24"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I39" s="33"/>
-      <c r="J39" s="34" t="s">
+      <c r="I46" s="23"/>
+      <c r="J46" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K39" s="29" t="s">
+      <c r="K46" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L39" s="35"/>
-      <c r="M39" s="36"/>
-      <c r="N39" s="36"/>
-      <c r="O39" s="36"/>
-    </row>
-    <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="29">
-        <v>38</v>
-      </c>
-      <c r="B40" s="29">
+      <c r="L46" s="25"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="26"/>
+      <c r="O46" s="26"/>
+    </row>
+    <row r="47" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="19">
+        <v>45</v>
+      </c>
+      <c r="B47" s="19">
         <v>408170153</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C47" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D40" s="34"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29" t="s">
+      <c r="D47" s="24"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I40" s="33"/>
-      <c r="J40" s="34" t="s">
+      <c r="I47" s="23"/>
+      <c r="J47" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K40" s="29" t="s">
+      <c r="K47" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L40" s="35"/>
-      <c r="M40" s="36"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="36"/>
-    </row>
-    <row r="41" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="29">
-        <v>39</v>
-      </c>
-      <c r="B41" s="29">
+      <c r="L47" s="25"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="26"/>
+      <c r="O47" s="26"/>
+    </row>
+    <row r="48" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="19">
+        <v>46</v>
+      </c>
+      <c r="B48" s="19">
         <v>408170153</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C48" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D41" s="34"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29" t="s">
+      <c r="D48" s="24"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I41" s="33"/>
-      <c r="J41" s="34" t="s">
+      <c r="I48" s="23"/>
+      <c r="J48" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K41" s="29" t="s">
+      <c r="K48" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L41" s="35"/>
-      <c r="M41" s="36"/>
-      <c r="N41" s="36"/>
-      <c r="O41" s="36"/>
-    </row>
-    <row r="42" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="29">
-        <v>40</v>
-      </c>
-      <c r="B42" s="29">
+      <c r="L48" s="25"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
+    </row>
+    <row r="49" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="19">
+        <v>47</v>
+      </c>
+      <c r="B49" s="19">
         <v>408170153</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C49" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D42" s="34"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29" t="s">
+      <c r="D49" s="24"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I42" s="33"/>
-      <c r="J42" s="34" t="s">
+      <c r="I49" s="23"/>
+      <c r="J49" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K42" s="29" t="s">
+      <c r="K49" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L42" s="35"/>
-      <c r="M42" s="36"/>
-      <c r="N42" s="36"/>
-      <c r="O42" s="36"/>
-    </row>
-    <row r="43" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="29">
-        <v>41</v>
-      </c>
-      <c r="B43" s="29">
+      <c r="L49" s="25"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="26"/>
+      <c r="O49" s="26"/>
+    </row>
+    <row r="50" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="19">
+        <v>48</v>
+      </c>
+      <c r="B50" s="19">
         <v>408170153</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C50" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D43" s="34"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29" t="s">
+      <c r="D50" s="24"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I43" s="33"/>
-      <c r="J43" s="34" t="s">
+      <c r="I50" s="23"/>
+      <c r="J50" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K43" s="29" t="s">
+      <c r="K50" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L43" s="35"/>
-      <c r="M43" s="36"/>
-      <c r="N43" s="36"/>
-      <c r="O43" s="36"/>
-    </row>
-    <row r="44" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="29">
-        <v>42</v>
-      </c>
-      <c r="B44" s="29">
+      <c r="L50" s="25"/>
+      <c r="M50" s="26"/>
+      <c r="N50" s="26"/>
+      <c r="O50" s="26"/>
+    </row>
+    <row r="51" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="19">
+        <v>49</v>
+      </c>
+      <c r="B51" s="19">
         <v>408170153</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C51" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D44" s="34"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29" t="s">
+      <c r="D51" s="24"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I44" s="33"/>
-      <c r="J44" s="34" t="s">
+      <c r="I51" s="23"/>
+      <c r="J51" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K44" s="29" t="s">
+      <c r="K51" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L44" s="35"/>
-      <c r="M44" s="36"/>
-      <c r="N44" s="36"/>
-      <c r="O44" s="36"/>
-    </row>
-    <row r="45" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="29">
-        <v>43</v>
-      </c>
-      <c r="B45" s="29">
+      <c r="L51" s="25"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="26"/>
+      <c r="O51" s="26"/>
+    </row>
+    <row r="52" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="19">
+        <v>50</v>
+      </c>
+      <c r="B52" s="19">
         <v>408170153</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C52" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="34"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29" t="s">
+      <c r="D52" s="24"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I45" s="33"/>
-      <c r="J45" s="34" t="s">
+      <c r="I52" s="23"/>
+      <c r="J52" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K45" s="29" t="s">
+      <c r="K52" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L45" s="35"/>
-      <c r="M45" s="36"/>
-      <c r="N45" s="36"/>
-      <c r="O45" s="36"/>
-    </row>
-    <row r="46" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="29">
-        <v>44</v>
-      </c>
-      <c r="B46" s="29">
+      <c r="L52" s="25"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="26"/>
+      <c r="O52" s="26"/>
+    </row>
+    <row r="53" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="19">
+        <v>51</v>
+      </c>
+      <c r="B53" s="19">
         <v>408170153</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C53" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D46" s="34"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29" t="s">
+      <c r="D53" s="24"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I46" s="33"/>
-      <c r="J46" s="34" t="s">
+      <c r="I53" s="23"/>
+      <c r="J53" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K46" s="29" t="s">
+      <c r="K53" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L46" s="35"/>
-      <c r="M46" s="36"/>
-      <c r="N46" s="36"/>
-      <c r="O46" s="36"/>
-    </row>
-    <row r="47" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="29">
-        <v>45</v>
-      </c>
-      <c r="B47" s="29">
+      <c r="L53" s="25"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="26"/>
+      <c r="O53" s="26"/>
+    </row>
+    <row r="54" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="19">
+        <v>52</v>
+      </c>
+      <c r="B54" s="19">
         <v>408170153</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C54" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D47" s="34"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29" t="s">
+      <c r="D54" s="24"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I47" s="33"/>
-      <c r="J47" s="34" t="s">
+      <c r="I54" s="23"/>
+      <c r="J54" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K47" s="29" t="s">
+      <c r="K54" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L47" s="35"/>
-      <c r="M47" s="36"/>
-      <c r="N47" s="36"/>
-      <c r="O47" s="36"/>
-    </row>
-    <row r="48" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="29">
-        <v>46</v>
-      </c>
-      <c r="B48" s="29">
+      <c r="L54" s="25"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="26"/>
+      <c r="O54" s="26"/>
+    </row>
+    <row r="55" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="19">
+        <v>53</v>
+      </c>
+      <c r="B55" s="19">
         <v>408170153</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C55" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D48" s="34"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29" t="s">
+      <c r="D55" s="24"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="19"/>
+      <c r="H55" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I48" s="33"/>
-      <c r="J48" s="34" t="s">
+      <c r="I55" s="23"/>
+      <c r="J55" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K48" s="29" t="s">
+      <c r="K55" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L48" s="35"/>
-      <c r="M48" s="36"/>
-      <c r="N48" s="36"/>
-      <c r="O48" s="36"/>
-    </row>
-    <row r="49" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="29">
-        <v>47</v>
-      </c>
-      <c r="B49" s="29">
+      <c r="L55" s="25"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="26"/>
+      <c r="O55" s="26"/>
+    </row>
+    <row r="56" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="19">
+        <v>54</v>
+      </c>
+      <c r="B56" s="19">
         <v>408170153</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C56" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D49" s="34"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29" t="s">
+      <c r="D56" s="24"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I49" s="33"/>
-      <c r="J49" s="34" t="s">
+      <c r="I56" s="23"/>
+      <c r="J56" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K49" s="29" t="s">
+      <c r="K56" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L49" s="35"/>
-      <c r="M49" s="36"/>
-      <c r="N49" s="36"/>
-      <c r="O49" s="36"/>
-    </row>
-    <row r="50" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="29">
-        <v>48</v>
-      </c>
-      <c r="B50" s="29">
+      <c r="L56" s="25"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="26"/>
+      <c r="O56" s="26"/>
+    </row>
+    <row r="57" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="19">
+        <v>55</v>
+      </c>
+      <c r="B57" s="19">
         <v>408170153</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C57" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D50" s="34"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29" t="s">
+      <c r="D57" s="24"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I50" s="33"/>
-      <c r="J50" s="34" t="s">
+      <c r="I57" s="23"/>
+      <c r="J57" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K50" s="29" t="s">
+      <c r="K57" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L50" s="35"/>
-      <c r="M50" s="36"/>
-      <c r="N50" s="36"/>
-      <c r="O50" s="36"/>
-    </row>
-    <row r="51" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="29">
-        <v>49</v>
-      </c>
-      <c r="B51" s="29">
-        <v>408170153</v>
-      </c>
-      <c r="C51" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="D51" s="34"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I51" s="33"/>
-      <c r="J51" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="K51" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="L51" s="35"/>
-      <c r="M51" s="36"/>
-      <c r="N51" s="36"/>
-      <c r="O51" s="36"/>
-    </row>
-    <row r="52" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="29">
-        <v>50</v>
-      </c>
-      <c r="B52" s="29">
-        <v>408170153</v>
-      </c>
-      <c r="C52" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="D52" s="34"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I52" s="33"/>
-      <c r="J52" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="K52" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="L52" s="35"/>
-      <c r="M52" s="36"/>
-      <c r="N52" s="36"/>
-      <c r="O52" s="36"/>
-    </row>
-    <row r="53" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="29">
-        <v>51</v>
-      </c>
-      <c r="B53" s="29">
-        <v>408170153</v>
-      </c>
-      <c r="C53" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="D53" s="34"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="29"/>
-      <c r="H53" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I53" s="33"/>
-      <c r="J53" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="K53" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="L53" s="35"/>
-      <c r="M53" s="36"/>
-      <c r="N53" s="36"/>
-      <c r="O53" s="36"/>
-    </row>
-    <row r="54" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="29">
-        <v>52</v>
-      </c>
-      <c r="B54" s="29">
-        <v>408170153</v>
-      </c>
-      <c r="C54" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="D54" s="34"/>
-      <c r="E54" s="37"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I54" s="33"/>
-      <c r="J54" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="K54" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="L54" s="35"/>
-      <c r="M54" s="36"/>
-      <c r="N54" s="36"/>
-      <c r="O54" s="36"/>
-    </row>
-    <row r="55" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="29">
-        <v>53</v>
-      </c>
-      <c r="B55" s="29">
-        <v>408170153</v>
-      </c>
-      <c r="C55" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="D55" s="34"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I55" s="33"/>
-      <c r="J55" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="K55" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="L55" s="35"/>
-      <c r="M55" s="36"/>
-      <c r="N55" s="36"/>
-      <c r="O55" s="36"/>
-    </row>
-    <row r="56" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="29">
-        <v>54</v>
-      </c>
-      <c r="B56" s="29">
-        <v>408170153</v>
-      </c>
-      <c r="C56" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="D56" s="34"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I56" s="33"/>
-      <c r="J56" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="K56" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="L56" s="35"/>
-      <c r="M56" s="36"/>
-      <c r="N56" s="36"/>
-      <c r="O56" s="36"/>
-    </row>
-    <row r="57" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="29">
-        <v>55</v>
-      </c>
-      <c r="B57" s="29">
-        <v>408170153</v>
-      </c>
-      <c r="C57" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="D57" s="34"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I57" s="33"/>
-      <c r="J57" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="K57" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="L57" s="35"/>
-      <c r="M57" s="36"/>
-      <c r="N57" s="36"/>
-      <c r="O57" s="36"/>
+      <c r="L57" s="25"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="26"/>
+      <c r="O57" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D57">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M57">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N57">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5406,140 +5766,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="17"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
     </row>
     <row r="3" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
     </row>
     <row r="4" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
     </row>
     <row r="5" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="17"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="30"/>
     </row>
     <row r="6" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="35"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="22"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="33"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="17"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="30"/>
     </row>
     <row r="23" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="17"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="30"/>
     </row>
     <row r="24" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="17"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="30"/>
     </row>
     <row r="25" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="17"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="30"/>
     </row>
     <row r="26" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="17"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="30"/>
     </row>
     <row r="27" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -5548,6 +5902,12 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5567,24 +5927,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -5725,4 +6085,372 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5533C39B-C0F4-4BD5-B15B-A199B6086086}">
+  <dimension ref="A1:A92"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="3"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:A92">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$H1&lt;TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E37C27-67D4-4B73-8763-2BAF4DBF4651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7322F24B-7234-48C8-B924-242F4955585F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Test Date" sheetId="2" r:id="rId3"/>
     <sheet name="Test" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Registration!$A$1:$I$92</definedName>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="213">
   <si>
     <t>S No</t>
   </si>
@@ -654,6 +654,33 @@
   </si>
   <si>
     <t>Zain Ullah</t>
+  </si>
+  <si>
+    <t>Aon Ali</t>
+  </si>
+  <si>
+    <t>Imran Ali</t>
+  </si>
+  <si>
+    <t>Hafsa</t>
+  </si>
+  <si>
+    <t>Muhammad Fahad</t>
+  </si>
+  <si>
+    <t>Aiza</t>
+  </si>
+  <si>
+    <t>Irshad Ul Haq</t>
+  </si>
+  <si>
+    <t>Muhammad Hamza</t>
+  </si>
+  <si>
+    <t>Abdul Nafay</t>
+  </si>
+  <si>
+    <t>Abdul Rafay</t>
   </si>
 </sst>
 </file>
@@ -903,7 +930,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -977,6 +1004,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -986,33 +1019,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3457,7 +3488,7 @@
   </sheetData>
   <autoFilter ref="A1:I92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}"/>
   <conditionalFormatting sqref="A1:I92">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$H1&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4305,35 +4336,41 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
+      <c r="A19" s="38">
         <v>17</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="38">
         <v>408170153</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="39">
         <v>926</v>
       </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19" t="s">
+      <c r="E19" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H19" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="I19" s="23"/>
-      <c r="J19" s="24" t="s">
+      <c r="I19" s="42"/>
+      <c r="J19" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="K19" s="19" t="s">
+      <c r="K19" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="L19" s="25"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="45"/>
     </row>
     <row r="20" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
@@ -5446,13 +5483,13 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D57">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M57">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N57">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5766,13 +5803,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -5823,20 +5860,20 @@
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="35"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -5887,13 +5924,19 @@
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="35"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -5902,12 +5945,6 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6088,369 +6125,59 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5533C39B-C0F4-4BD5-B15B-A199B6086086}">
-  <dimension ref="A1:A92"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9775AE0A-527C-4FA9-ACE5-FDDEF858F8F4}">
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="3"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="3"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="3"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="3"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="3"/>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="3"/>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B6" t="s">
+        <v>209</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A92">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$H1&lt;TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7322F24B-7234-48C8-B924-242F4955585F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327F039D-E996-49F7-851D-342246FEA002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="218">
   <si>
     <t>S No</t>
   </si>
@@ -681,6 +681,21 @@
   </si>
   <si>
     <t>Abdul Rafay</t>
+  </si>
+  <si>
+    <t>Muhammad Umar</t>
+  </si>
+  <si>
+    <t>Irfan Ali</t>
+  </si>
+  <si>
+    <t>Level-III</t>
+  </si>
+  <si>
+    <t>42501-9394340-7</t>
+  </si>
+  <si>
+    <t>Rashid Hussain</t>
   </si>
 </sst>
 </file>
@@ -995,6 +1010,20 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1025,20 +1054,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1488,10 +1503,12 @@
       <c r="G3" s="5">
         <v>45755</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I3" s="6"/>
+      <c r="H3" s="5">
+        <v>45766</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0.4375</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -2544,10 +2561,12 @@
       <c r="G43" s="5">
         <v>45761</v>
       </c>
-      <c r="H43" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I43" s="6"/>
+      <c r="H43" s="5">
+        <v>45773</v>
+      </c>
+      <c r="I43" s="6">
+        <v>0.39583333333333331</v>
+      </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
@@ -3024,16 +3043,30 @@
       <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I62" s="6"/>
+      <c r="B62" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F62" s="4">
+        <v>3030439230</v>
+      </c>
+      <c r="G62" s="5">
+        <v>45771</v>
+      </c>
+      <c r="H62" s="5">
+        <v>45773</v>
+      </c>
+      <c r="I62" s="6">
+        <v>0.39583333333333331</v>
+      </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
@@ -3520,23 +3553,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -4336,41 +4369,41 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="38">
+      <c r="A19" s="28">
         <v>17</v>
       </c>
-      <c r="B19" s="38">
+      <c r="B19" s="28">
         <v>408170153</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="29">
         <v>926</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="F19" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="H19" s="38" t="s">
+      <c r="H19" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="I19" s="42"/>
-      <c r="J19" s="43" t="s">
+      <c r="I19" s="32"/>
+      <c r="J19" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="K19" s="38" t="s">
+      <c r="K19" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="L19" s="44"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
     </row>
     <row r="20" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
@@ -4385,23 +4418,39 @@
       <c r="D20" s="24">
         <v>927</v>
       </c>
-      <c r="E20" s="27"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="19"/>
+      <c r="E20" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>178</v>
+      </c>
       <c r="H20" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I20" s="23"/>
+      <c r="I20" s="23">
+        <v>43830</v>
+      </c>
       <c r="J20" s="24" t="s">
         <v>180</v>
       </c>
       <c r="K20" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L20" s="25"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="26"/>
+      <c r="L20" s="25">
+        <v>45771</v>
+      </c>
+      <c r="M20" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="N20" s="26">
+        <v>3018250207</v>
+      </c>
+      <c r="O20" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="21" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
@@ -4416,23 +4465,39 @@
       <c r="D21" s="20">
         <v>928</v>
       </c>
-      <c r="E21" s="27"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="19"/>
+      <c r="E21" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>184</v>
+      </c>
       <c r="H21" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I21" s="23"/>
+      <c r="I21" s="23">
+        <v>43626</v>
+      </c>
       <c r="J21" s="24" t="s">
         <v>180</v>
       </c>
       <c r="K21" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L21" s="25"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
+      <c r="L21" s="25">
+        <v>45771</v>
+      </c>
+      <c r="M21" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="N21" s="26">
+        <v>3012244916</v>
+      </c>
+      <c r="O21" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="22" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
@@ -4444,7 +4509,9 @@
       <c r="C22" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D22" s="24"/>
+      <c r="D22" s="24">
+        <v>929</v>
+      </c>
       <c r="E22" s="27"/>
       <c r="F22" s="22"/>
       <c r="G22" s="19"/>
@@ -4473,7 +4540,9 @@
       <c r="C23" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D23" s="24"/>
+      <c r="D23" s="20">
+        <v>930</v>
+      </c>
       <c r="E23" s="27"/>
       <c r="F23" s="22"/>
       <c r="G23" s="19"/>
@@ -4502,7 +4571,9 @@
       <c r="C24" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D24" s="24"/>
+      <c r="D24" s="24">
+        <v>931</v>
+      </c>
       <c r="E24" s="27"/>
       <c r="F24" s="22"/>
       <c r="G24" s="19"/>
@@ -4531,7 +4602,9 @@
       <c r="C25" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D25" s="24"/>
+      <c r="D25" s="20">
+        <v>932</v>
+      </c>
       <c r="E25" s="27"/>
       <c r="F25" s="22"/>
       <c r="G25" s="19"/>
@@ -4560,7 +4633,9 @@
       <c r="C26" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D26" s="24"/>
+      <c r="D26" s="24">
+        <v>933</v>
+      </c>
       <c r="E26" s="27"/>
       <c r="F26" s="22"/>
       <c r="G26" s="19"/>
@@ -4589,7 +4664,9 @@
       <c r="C27" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D27" s="24"/>
+      <c r="D27" s="20">
+        <v>934</v>
+      </c>
       <c r="E27" s="27"/>
       <c r="F27" s="22"/>
       <c r="G27" s="19"/>
@@ -4618,7 +4695,9 @@
       <c r="C28" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D28" s="24"/>
+      <c r="D28" s="24">
+        <v>935</v>
+      </c>
       <c r="E28" s="27"/>
       <c r="F28" s="22"/>
       <c r="G28" s="19"/>
@@ -4647,7 +4726,9 @@
       <c r="C29" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D29" s="24"/>
+      <c r="D29" s="20">
+        <v>936</v>
+      </c>
       <c r="E29" s="27"/>
       <c r="F29" s="22"/>
       <c r="G29" s="19"/>
@@ -4676,7 +4757,9 @@
       <c r="C30" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D30" s="24"/>
+      <c r="D30" s="24">
+        <v>937</v>
+      </c>
       <c r="E30" s="27"/>
       <c r="F30" s="22"/>
       <c r="G30" s="19"/>
@@ -4705,7 +4788,9 @@
       <c r="C31" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D31" s="24"/>
+      <c r="D31" s="20">
+        <v>938</v>
+      </c>
       <c r="E31" s="27"/>
       <c r="F31" s="22"/>
       <c r="G31" s="19"/>
@@ -4734,7 +4819,9 @@
       <c r="C32" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D32" s="24"/>
+      <c r="D32" s="24">
+        <v>939</v>
+      </c>
       <c r="E32" s="27"/>
       <c r="F32" s="22"/>
       <c r="G32" s="19"/>
@@ -4763,7 +4850,9 @@
       <c r="C33" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D33" s="24"/>
+      <c r="D33" s="20">
+        <v>940</v>
+      </c>
       <c r="E33" s="27"/>
       <c r="F33" s="22"/>
       <c r="G33" s="19"/>
@@ -4792,7 +4881,9 @@
       <c r="C34" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D34" s="24"/>
+      <c r="D34" s="24">
+        <v>941</v>
+      </c>
       <c r="E34" s="27"/>
       <c r="F34" s="22"/>
       <c r="G34" s="19"/>
@@ -4821,7 +4912,9 @@
       <c r="C35" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D35" s="24"/>
+      <c r="D35" s="20">
+        <v>942</v>
+      </c>
       <c r="E35" s="27"/>
       <c r="F35" s="22"/>
       <c r="G35" s="19"/>
@@ -4850,7 +4943,9 @@
       <c r="C36" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="24"/>
+      <c r="D36" s="24">
+        <v>943</v>
+      </c>
       <c r="E36" s="27"/>
       <c r="F36" s="22"/>
       <c r="G36" s="19"/>
@@ -4879,7 +4974,9 @@
       <c r="C37" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D37" s="24"/>
+      <c r="D37" s="20">
+        <v>944</v>
+      </c>
       <c r="E37" s="27"/>
       <c r="F37" s="22"/>
       <c r="G37" s="19"/>
@@ -4908,7 +5005,9 @@
       <c r="C38" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D38" s="24"/>
+      <c r="D38" s="24">
+        <v>945</v>
+      </c>
       <c r="E38" s="27"/>
       <c r="F38" s="22"/>
       <c r="G38" s="19"/>
@@ -5803,131 +5902,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="3" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="38"/>
     </row>
     <row r="4" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="38"/>
     </row>
     <row r="5" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="30"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="38"/>
     </row>
     <row r="6" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="30"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="38"/>
     </row>
     <row r="7" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="32"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="40"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="43"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="38"/>
     </row>
     <row r="23" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="38"/>
     </row>
     <row r="24" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="30"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="38"/>
     </row>
     <row r="25" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="30"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="38"/>
     </row>
     <row r="26" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="30"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="38"/>
     </row>
     <row r="27" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="32"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -5964,24 +6063,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
     </row>
     <row r="2" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -6128,6 +6227,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9775AE0A-527C-4FA9-ACE5-FDDEF858F8F4}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327F039D-E996-49F7-851D-342246FEA002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B7BE9E-1666-48C5-B5EB-65918E0DE69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -1033,12 +1033,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1047,6 +1041,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5902,13 +5902,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="41"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -5959,20 +5959,20 @@
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="40"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="43"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="43"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="41"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -6023,19 +6023,13 @@
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="40"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -6044,6 +6038,12 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B7BE9E-1666-48C5-B5EB-65918E0DE69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BB661F-1E63-4C86-BA6A-C7C16A3C5E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="226">
   <si>
     <t>S No</t>
   </si>
@@ -696,6 +696,30 @@
   </si>
   <si>
     <t>Rashid Hussain</t>
+  </si>
+  <si>
+    <t>3 years 6 months</t>
+  </si>
+  <si>
+    <t>4 years, 1 month, 1 week, 4 days</t>
+  </si>
+  <si>
+    <t>Momin Ali</t>
+  </si>
+  <si>
+    <t>Muhammad Waseem</t>
+  </si>
+  <si>
+    <t>43205-0147299-5</t>
+  </si>
+  <si>
+    <t>Muhammad Siddiq</t>
+  </si>
+  <si>
+    <t>Ghulam Nabi</t>
+  </si>
+  <si>
+    <t>43102-5528880-1</t>
   </si>
 </sst>
 </file>
@@ -1033,6 +1057,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1041,12 +1071,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1421,9 +1445,10 @@
     <col min="7" max="7" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1452,7 +1477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1481,7 +1506,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1510,7 +1535,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1539,7 +1564,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1568,7 +1593,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1594,8 +1619,11 @@
         <v>144</v>
       </c>
       <c r="I6" s="6"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1622,7 +1650,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1649,7 +1677,7 @@
       </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1676,7 +1704,7 @@
       </c>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1701,7 +1729,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1728,7 +1756,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1753,7 +1781,7 @@
       </c>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1782,7 +1810,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1809,7 +1837,7 @@
       </c>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1834,7 +1862,7 @@
       </c>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2281,7 +2309,7 @@
       </c>
       <c r="I32" s="6"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2310,7 +2338,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2336,8 +2364,11 @@
         <v>144</v>
       </c>
       <c r="I34" s="6"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2362,7 +2393,7 @@
       </c>
       <c r="I35" s="6"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2385,7 +2416,7 @@
       </c>
       <c r="I36" s="6"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2410,7 +2441,7 @@
       </c>
       <c r="I37" s="6"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2437,7 +2468,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2462,7 +2493,7 @@
       </c>
       <c r="I39" s="6"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2491,7 +2522,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2516,7 +2547,7 @@
       </c>
       <c r="I41" s="6"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2541,7 +2572,7 @@
       </c>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2568,7 +2599,7 @@
         <v>0.39583333333333331</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2597,7 +2628,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2624,7 +2655,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2651,7 +2682,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2678,7 +2709,7 @@
       </c>
       <c r="I47" s="6"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -3072,31 +3103,59 @@
       <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I63" s="6"/>
+      <c r="B63" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F63" s="4">
+        <v>3151184877</v>
+      </c>
+      <c r="G63" s="5">
+        <v>45772</v>
+      </c>
+      <c r="H63" s="5">
+        <v>45773</v>
+      </c>
+      <c r="I63" s="6">
+        <v>0.39583333333333331</v>
+      </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I64" s="6"/>
+      <c r="B64" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F64" s="4">
+        <v>3178789685</v>
+      </c>
+      <c r="G64" s="5">
+        <v>45772</v>
+      </c>
+      <c r="H64" s="5">
+        <v>45773</v>
+      </c>
+      <c r="I64" s="6">
+        <v>0.39583333333333331</v>
+      </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
@@ -3519,7 +3578,6 @@
       <c r="I92" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}"/>
   <conditionalFormatting sqref="A1:I92">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$H1&lt;TODAY()</formula>
@@ -5902,13 +5960,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -5959,20 +6017,20 @@
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="43"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="40"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="41"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="43"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -6023,13 +6081,19 @@
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="43"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -6038,12 +6102,6 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BB661F-1E63-4C86-BA6A-C7C16A3C5E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987FC71C-BC08-4B21-85A1-451B1AD857BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="228">
   <si>
     <t>S No</t>
   </si>
@@ -720,6 +720,12 @@
   </si>
   <si>
     <t>43102-5528880-1</t>
+  </si>
+  <si>
+    <t>Level-I</t>
+  </si>
+  <si>
+    <t>42401-9632491-3</t>
   </si>
 </sst>
 </file>
@@ -1057,12 +1063,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1071,6 +1071,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3598,7 +3604,7 @@
     <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -4570,23 +4576,37 @@
       <c r="D22" s="24">
         <v>929</v>
       </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="19"/>
+      <c r="E22" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>184</v>
+      </c>
       <c r="H22" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="I22" s="23"/>
+        <v>226</v>
+      </c>
+      <c r="I22" s="23">
+        <v>42853</v>
+      </c>
       <c r="J22" s="24" t="s">
         <v>180</v>
       </c>
       <c r="K22" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L22" s="25"/>
-      <c r="M22" s="26"/>
+      <c r="L22" s="25">
+        <v>45775</v>
+      </c>
+      <c r="M22" s="26" t="s">
+        <v>227</v>
+      </c>
       <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
+      <c r="O22" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="23" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="19">
@@ -5960,13 +5980,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="41"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -6017,20 +6037,20 @@
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="40"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="43"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="43"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="41"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -6081,19 +6101,13 @@
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="40"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -6102,6 +6116,12 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987FC71C-BC08-4B21-85A1-451B1AD857BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44DBB85-FA63-452E-8123-DBB41945840C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="228">
   <si>
     <t>S No</t>
   </si>
@@ -1063,6 +1063,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1071,12 +1077,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1088,7 +1088,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3128,7 +3138,7 @@
         <v>45772</v>
       </c>
       <c r="H63" s="5">
-        <v>45773</v>
+        <v>45780</v>
       </c>
       <c r="I63" s="6">
         <v>0.39583333333333331</v>
@@ -3585,7 +3595,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I92">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$H1&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4621,23 +4631,39 @@
       <c r="D23" s="20">
         <v>930</v>
       </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="19"/>
+      <c r="E23" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>184</v>
+      </c>
       <c r="H23" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="I23" s="23"/>
+        <v>215</v>
+      </c>
+      <c r="I23" s="23">
+        <v>42956</v>
+      </c>
       <c r="J23" s="24" t="s">
         <v>180</v>
       </c>
       <c r="K23" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L23" s="25"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
+      <c r="L23" s="25">
+        <v>45776</v>
+      </c>
+      <c r="M23" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="N23" s="26">
+        <v>3030439230</v>
+      </c>
+      <c r="O23" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="24" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
@@ -5660,13 +5686,18 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D57">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M57">
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1:N57">
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N57">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="E23:F23">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$H23&lt;TODAY()</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5980,13 +6011,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -6037,20 +6068,20 @@
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="43"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="40"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="41"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="43"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -6101,13 +6132,19 @@
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="43"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -6116,12 +6153,6 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44DBB85-FA63-452E-8123-DBB41945840C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556355FA-4CB7-4E12-A44E-CE10F4D3F690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="229">
   <si>
     <t>S No</t>
   </si>
@@ -726,6 +726,9 @@
   </si>
   <si>
     <t>42401-9632491-3</t>
+  </si>
+  <si>
+    <t>Arwa Fatima</t>
   </si>
 </sst>
 </file>
@@ -1091,16 +1094,6 @@
   <dxfs count="5">
     <dxf>
       <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1116,6 +1109,16 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2027,10 +2030,12 @@
       <c r="G21" s="5">
         <v>45755</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I21" s="6"/>
+      <c r="H21" s="5">
+        <v>45780</v>
+      </c>
+      <c r="I21" s="6">
+        <v>0.39583333333333331</v>
+      </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -4678,23 +4683,37 @@
       <c r="D24" s="24">
         <v>931</v>
       </c>
-      <c r="E24" s="27"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="19"/>
+      <c r="E24" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>178</v>
+      </c>
       <c r="H24" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I24" s="23"/>
+      <c r="I24" s="23">
+        <v>44419</v>
+      </c>
       <c r="J24" s="24" t="s">
         <v>180</v>
       </c>
       <c r="K24" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L24" s="25"/>
-      <c r="M24" s="26"/>
+      <c r="L24" s="25">
+        <v>45776</v>
+      </c>
+      <c r="M24" s="26" t="s">
+        <v>149</v>
+      </c>
       <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
+      <c r="O24" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="25" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="19">
@@ -5688,16 +5707,16 @@
   <conditionalFormatting sqref="D1:D57">
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E23:F23">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>$H23&lt;TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M1:M57">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N57">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E23:F23">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$H23&lt;TODAY()</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556355FA-4CB7-4E12-A44E-CE10F4D3F690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C30DF9-765D-407F-B503-611648A14D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,10 @@
     <sheet name="Test Date" sheetId="2" r:id="rId3"/>
     <sheet name="Test" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId6"/>
+    <sheet name="Drop Out" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Registration!$A$1:$I$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Registration!$A$1:$J$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="240">
   <si>
     <t>S No</t>
   </si>
@@ -729,6 +729,39 @@
   </si>
   <si>
     <t>Arwa Fatima</t>
+  </si>
+  <si>
+    <t>Mantasha Fatima</t>
+  </si>
+  <si>
+    <t>Almas Hussain Shah</t>
+  </si>
+  <si>
+    <t>45104-9914165-1</t>
+  </si>
+  <si>
+    <t>Level-II</t>
+  </si>
+  <si>
+    <t>Aqib</t>
+  </si>
+  <si>
+    <t>Muhammad Aqib</t>
+  </si>
+  <si>
+    <t>Ghulam Sarwar</t>
+  </si>
+  <si>
+    <t>42501-2744658-8</t>
+  </si>
+  <si>
+    <t>Maryam Magsi</t>
+  </si>
+  <si>
+    <t>c/o miss naila</t>
+  </si>
+  <si>
+    <t>c/o sir shunail</t>
   </si>
 </sst>
 </file>
@@ -978,7 +1011,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1087,6 +1120,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1452,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}">
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
@@ -3178,67 +3212,129 @@
         <v>0.39583333333333331</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I65" s="6"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B65" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F65" s="4">
+        <v>3323425295</v>
+      </c>
+      <c r="G65" s="5">
+        <v>45779</v>
+      </c>
+      <c r="H65" s="5">
+        <v>45782</v>
+      </c>
+      <c r="I65" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="J65" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
-      <c r="B66" s="3"/>
+      <c r="B66" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
+      <c r="D66" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="E66" s="3"/>
       <c r="F66" s="4"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I66" s="6"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G66" s="5">
+        <v>45779</v>
+      </c>
+      <c r="H66" s="5">
+        <v>45780</v>
+      </c>
+      <c r="I66" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I67" s="6"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B67" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F67" s="4">
+        <v>3360576896</v>
+      </c>
+      <c r="G67" s="5">
+        <v>45779</v>
+      </c>
+      <c r="H67" s="5">
+        <v>45782</v>
+      </c>
+      <c r="I67" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="J67" s="46">
+        <v>43949</v>
+      </c>
+      <c r="K67" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I68" s="6"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B68" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F68" s="4">
+        <v>3360576896</v>
+      </c>
+      <c r="G68" s="5">
+        <v>45779</v>
+      </c>
+      <c r="H68" s="5">
+        <v>45782</v>
+      </c>
+      <c r="I68" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="J68" s="46">
+        <v>42958</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3253,7 +3349,7 @@
       </c>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -3268,7 +3364,7 @@
       </c>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -3283,7 +3379,7 @@
       </c>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -3298,7 +3394,7 @@
       </c>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -3313,7 +3409,7 @@
       </c>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -3328,7 +3424,7 @@
       </c>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -3343,7 +3439,7 @@
       </c>
       <c r="I75" s="6"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -3358,7 +3454,7 @@
       </c>
       <c r="I76" s="6"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -3373,7 +3469,7 @@
       </c>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -3388,7 +3484,7 @@
       </c>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -3403,7 +3499,7 @@
       </c>
       <c r="I79" s="6"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -3599,6 +3695,7 @@
       <c r="I92" s="6"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}"/>
   <conditionalFormatting sqref="A1:I92">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>$H1&lt;TODAY()</formula>
@@ -4728,23 +4825,39 @@
       <c r="D25" s="20">
         <v>932</v>
       </c>
-      <c r="E25" s="27"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="19"/>
+      <c r="E25" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>184</v>
+      </c>
       <c r="H25" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I25" s="23"/>
+      <c r="I25" s="23">
+        <v>43419</v>
+      </c>
       <c r="J25" s="24" t="s">
         <v>180</v>
       </c>
       <c r="K25" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L25" s="25"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="26"/>
+      <c r="L25" s="25">
+        <v>45779</v>
+      </c>
+      <c r="M25" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="N25" s="26">
+        <v>3178789685</v>
+      </c>
+      <c r="O25" s="26" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="26" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="19">

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C30DF9-765D-407F-B503-611648A14D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17743CD-BD49-494C-ACB8-40A3939C219D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -1090,6 +1090,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1120,7 +1121,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3295,7 +3295,7 @@
       <c r="I67" s="6">
         <v>0.39583333333333331</v>
       </c>
-      <c r="J67" s="46">
+      <c r="J67" s="36">
         <v>43949</v>
       </c>
       <c r="K67" t="s">
@@ -3330,7 +3330,7 @@
       <c r="I68" s="6">
         <v>0.39583333333333331</v>
       </c>
-      <c r="J68" s="46">
+      <c r="J68" s="36">
         <v>42958</v>
       </c>
     </row>
@@ -3729,23 +3729,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -6143,131 +6143,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="44"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39"/>
     </row>
     <row r="3" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="39"/>
     </row>
     <row r="4" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="39"/>
     </row>
     <row r="5" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="39"/>
     </row>
     <row r="6" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="38"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="39"/>
     </row>
     <row r="7" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="40"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="41"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="44"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="38"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="39"/>
     </row>
     <row r="23" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="39"/>
     </row>
     <row r="24" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="38"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="39"/>
     </row>
     <row r="25" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="38"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="39"/>
     </row>
     <row r="26" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="38"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="39"/>
     </row>
     <row r="27" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="40"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -6304,24 +6304,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17743CD-BD49-494C-ACB8-40A3939C219D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105C6BB7-09D2-4F4C-9819-6C091660ADE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="242">
   <si>
     <t>S No</t>
   </si>
@@ -762,6 +762,12 @@
   </si>
   <si>
     <t>c/o sir shunail</t>
+  </si>
+  <si>
+    <t>Ismail</t>
+  </si>
+  <si>
+    <t>Zara Fatima</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1017,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1065,7 +1071,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1091,6 +1096,8 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1125,7 +1132,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1143,6 +1150,36 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3295,7 +3332,7 @@
       <c r="I67" s="6">
         <v>0.39583333333333331</v>
       </c>
-      <c r="J67" s="36">
+      <c r="J67" s="35">
         <v>43949</v>
       </c>
       <c r="K67" t="s">
@@ -3330,7 +3367,7 @@
       <c r="I68" s="6">
         <v>0.39583333333333331</v>
       </c>
-      <c r="J68" s="36">
+      <c r="J68" s="35">
         <v>42958</v>
       </c>
     </row>
@@ -3697,7 +3734,7 @@
   </sheetData>
   <autoFilter ref="A1:J92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}"/>
   <conditionalFormatting sqref="A1:I92">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>$H1&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3708,6 +3745,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACE4FB1-457D-4ABA-B740-EA58B1613A2C}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:O57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3729,23 +3769,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -3794,332 +3834,332 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="19">
+    <row r="3" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="27">
         <v>1</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="27">
         <v>408170153</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="28">
         <v>910</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="31">
         <v>43711</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="33">
         <v>45770</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="M3" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="34">
         <v>3008912581</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="O3" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="19">
+    <row r="4" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="27">
         <v>2</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="27">
         <v>408170153</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="32">
         <v>911</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="31">
         <v>44013</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J4" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L4" s="33">
         <v>45770</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="M4" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="N4" s="26">
+      <c r="N4" s="34">
         <v>3408550574</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="O4" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
+    <row r="5" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="27">
         <v>3</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="27">
         <v>408170153</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="28">
         <v>912</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="31">
         <v>43832</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="J5" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L5" s="25">
+      <c r="L5" s="33">
         <v>45770</v>
       </c>
-      <c r="M5" s="26" t="s">
+      <c r="M5" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="N5" s="26">
+      <c r="N5" s="34">
         <v>3022345160</v>
       </c>
-      <c r="O5" s="26" t="s">
+      <c r="O5" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+    <row r="6" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="27">
         <v>4</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="27">
         <v>408170153</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="32">
         <v>913</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="31">
         <v>43574</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="J6" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="33">
         <v>45770</v>
       </c>
-      <c r="M6" s="26" t="s">
+      <c r="M6" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="N6" s="26">
+      <c r="N6" s="34">
         <v>3152717911</v>
       </c>
-      <c r="O6" s="26" t="s">
+      <c r="O6" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
+    <row r="7" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
         <v>5</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="27">
         <v>408170153</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="28">
         <v>914</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="31">
         <v>43879</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="J7" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L7" s="25">
+      <c r="L7" s="33">
         <v>45770</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="M7" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="34">
         <v>3213522748</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="O7" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="19">
+    <row r="8" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="27">
         <v>6</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="27">
         <v>408170153</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="32">
         <v>915</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="31">
         <v>43471</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="33">
         <v>45770</v>
       </c>
-      <c r="M8" s="26" t="s">
+      <c r="M8" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="34">
         <v>3472586633</v>
       </c>
-      <c r="O8" s="26" t="s">
+      <c r="O8" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="19">
+    <row r="9" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
         <v>7</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="27">
         <v>408170153</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="28">
         <v>916</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="31">
         <v>44143</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="J9" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L9" s="25">
+      <c r="L9" s="33">
         <v>45770</v>
       </c>
-      <c r="M9" s="26" t="s">
+      <c r="M9" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="34">
         <v>3368603595</v>
       </c>
-      <c r="O9" s="26" t="s">
+      <c r="O9" s="34" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4133,13 +4173,13 @@
       <c r="C10" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="23">
         <v>917</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="21" t="s">
         <v>194</v>
       </c>
       <c r="G10" s="19" t="s">
@@ -4148,25 +4188,25 @@
       <c r="H10" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="22">
         <v>44096</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K10" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L10" s="25">
+      <c r="L10" s="24">
         <v>45770</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="25">
         <v>3158719338</v>
       </c>
-      <c r="O10" s="26" t="s">
+      <c r="O10" s="25" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4183,10 +4223,10 @@
       <c r="D11" s="20">
         <v>918</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="21" t="s">
         <v>103</v>
       </c>
       <c r="G11" s="19" t="s">
@@ -4195,483 +4235,483 @@
       <c r="H11" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="22">
         <v>43088</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K11" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L11" s="25">
+      <c r="L11" s="24">
         <v>45770</v>
       </c>
-      <c r="M11" s="26" t="s">
+      <c r="M11" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26" t="s">
+      <c r="N11" s="25"/>
+      <c r="O11" s="25" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
+    <row r="12" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="27">
         <v>10</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="27">
         <v>408170153</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="32">
         <v>919</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="31">
         <v>44069</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L12" s="25">
+      <c r="L12" s="33">
         <v>45770</v>
       </c>
-      <c r="M12" s="26" t="s">
+      <c r="M12" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="34">
         <v>3333115124</v>
       </c>
-      <c r="O12" s="26" t="s">
+      <c r="O12" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
+    <row r="13" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
         <v>11</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="27">
         <v>408170153</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="28">
         <v>920</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="31">
         <v>43881</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="K13" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="33">
         <v>45770</v>
       </c>
-      <c r="M13" s="26" t="s">
+      <c r="M13" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="34">
         <v>3412510302</v>
       </c>
-      <c r="O13" s="26" t="s">
+      <c r="O13" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
+    <row r="14" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
         <v>12</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="27">
         <v>408170153</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="32">
         <v>921</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="31">
         <v>43936</v>
       </c>
-      <c r="J14" s="24" t="s">
+      <c r="J14" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K14" s="19" t="s">
+      <c r="K14" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="33">
         <v>45770</v>
       </c>
-      <c r="M14" s="26" t="s">
+      <c r="M14" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="34">
         <v>3471801620</v>
       </c>
-      <c r="O14" s="26" t="s">
+      <c r="O14" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
+    <row r="15" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
         <v>13</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="27">
         <v>408170153</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="28">
         <v>922</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="31">
         <v>43871</v>
       </c>
-      <c r="J15" s="24" t="s">
+      <c r="J15" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K15" s="19" t="s">
+      <c r="K15" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L15" s="25">
+      <c r="L15" s="33">
         <v>45770</v>
       </c>
-      <c r="M15" s="26" t="s">
+      <c r="M15" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="34">
         <v>3471801620</v>
       </c>
-      <c r="O15" s="26" t="s">
+      <c r="O15" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
+    <row r="16" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
         <v>14</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="27">
         <v>408170153</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="32">
         <v>923</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="31">
         <v>43936</v>
       </c>
-      <c r="J16" s="24" t="s">
+      <c r="J16" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K16" s="19" t="s">
+      <c r="K16" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L16" s="25">
+      <c r="L16" s="33">
         <v>45770</v>
       </c>
-      <c r="M16" s="26" t="s">
+      <c r="M16" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="N16" s="26">
+      <c r="N16" s="34">
         <v>3471801620</v>
       </c>
-      <c r="O16" s="26" t="s">
+      <c r="O16" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
+    <row r="17" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
         <v>15</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="27">
         <v>408170153</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="28">
         <v>924</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="H17" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="31">
         <v>43723</v>
       </c>
-      <c r="J17" s="24" t="s">
+      <c r="J17" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K17" s="19" t="s">
+      <c r="K17" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L17" s="25">
+      <c r="L17" s="33">
         <v>45770</v>
       </c>
-      <c r="M17" s="26" t="s">
+      <c r="M17" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="N17" s="26">
+      <c r="N17" s="34">
         <v>3146147223</v>
       </c>
-      <c r="O17" s="26" t="s">
+      <c r="O17" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
+    <row r="18" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
         <v>16</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="27">
         <v>408170153</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="32">
         <v>925</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="31">
         <v>43930</v>
       </c>
-      <c r="J18" s="24" t="s">
+      <c r="J18" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K18" s="19" t="s">
+      <c r="K18" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L18" s="25">
+      <c r="L18" s="33">
         <v>45770</v>
       </c>
-      <c r="M18" s="26" t="s">
+      <c r="M18" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="N18" s="26">
+      <c r="N18" s="34">
         <v>3437668872</v>
       </c>
-      <c r="O18" s="26" t="s">
+      <c r="O18" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="28">
+    <row r="19" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
         <v>17</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="27">
         <v>408170153</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="28">
         <v>926</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="E19" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="G19" s="28" t="s">
+      <c r="G19" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="H19" s="28" t="s">
+      <c r="H19" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I19" s="32"/>
-      <c r="J19" s="33" t="s">
+      <c r="I19" s="31"/>
+      <c r="J19" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K19" s="28" t="s">
+      <c r="K19" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L19" s="34"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
-    </row>
-    <row r="20" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
+      <c r="L19" s="33"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+    </row>
+    <row r="20" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
         <v>18</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="27">
         <v>408170153</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="32">
         <v>927</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="H20" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="31">
         <v>43830</v>
       </c>
-      <c r="J20" s="24" t="s">
+      <c r="J20" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K20" s="19" t="s">
+      <c r="K20" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L20" s="25">
+      <c r="L20" s="33">
         <v>45771</v>
       </c>
-      <c r="M20" s="26" t="s">
+      <c r="M20" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="N20" s="26">
+      <c r="N20" s="34">
         <v>3018250207</v>
       </c>
-      <c r="O20" s="26" t="s">
+      <c r="O20" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="19">
+    <row r="21" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
         <v>19</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="27">
         <v>408170153</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="28">
         <v>928</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="H21" s="19" t="s">
+      <c r="H21" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="31">
         <v>43626</v>
       </c>
-      <c r="J21" s="24" t="s">
+      <c r="J21" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K21" s="19" t="s">
+      <c r="K21" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L21" s="25">
+      <c r="L21" s="33">
         <v>45771</v>
       </c>
-      <c r="M21" s="26" t="s">
+      <c r="M21" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="N21" s="26">
+      <c r="N21" s="34">
         <v>3012244916</v>
       </c>
-      <c r="O21" s="26" t="s">
+      <c r="O21" s="34" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4685,13 +4725,13 @@
       <c r="C22" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="23">
         <v>929</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="21" t="s">
         <v>108</v>
       </c>
       <c r="G22" s="19" t="s">
@@ -4700,23 +4740,23 @@
       <c r="H22" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="22">
         <v>42853</v>
       </c>
-      <c r="J22" s="24" t="s">
+      <c r="J22" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K22" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L22" s="25">
+      <c r="L22" s="24">
         <v>45775</v>
       </c>
-      <c r="M22" s="26" t="s">
+      <c r="M22" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26" t="s">
+      <c r="N22" s="25"/>
+      <c r="O22" s="25" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4745,367 +4785,395 @@
       <c r="H23" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="22">
         <v>42956</v>
       </c>
-      <c r="J23" s="24" t="s">
+      <c r="J23" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K23" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L23" s="25">
+      <c r="L23" s="24">
         <v>45776</v>
       </c>
-      <c r="M23" s="26" t="s">
+      <c r="M23" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="N23" s="26">
+      <c r="N23" s="25">
         <v>3030439230</v>
       </c>
-      <c r="O23" s="26" t="s">
+      <c r="O23" s="25" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="19">
+    <row r="24" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
         <v>22</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="27">
         <v>408170153</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="32">
         <v>931</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="31">
         <v>44419</v>
       </c>
-      <c r="J24" s="24" t="s">
+      <c r="J24" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K24" s="19" t="s">
+      <c r="K24" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L24" s="25">
+      <c r="L24" s="33">
         <v>45776</v>
       </c>
-      <c r="M24" s="26" t="s">
+      <c r="M24" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26" t="s">
+      <c r="N24" s="34"/>
+      <c r="O24" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="19">
+    <row r="25" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
         <v>23</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="27">
         <v>408170153</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="28">
         <v>932</v>
       </c>
-      <c r="E25" s="27" t="s">
+      <c r="E25" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="H25" s="19" t="s">
+      <c r="H25" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I25" s="23">
+      <c r="I25" s="31">
         <v>43419</v>
       </c>
-      <c r="J25" s="24" t="s">
+      <c r="J25" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K25" s="19" t="s">
+      <c r="K25" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L25" s="25">
+      <c r="L25" s="33">
         <v>45779</v>
       </c>
-      <c r="M25" s="26" t="s">
+      <c r="M25" s="34" t="s">
         <v>225</v>
       </c>
-      <c r="N25" s="26">
+      <c r="N25" s="34">
         <v>3178789685</v>
       </c>
-      <c r="O25" s="26" t="s">
+      <c r="O25" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="19">
+    <row r="26" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
         <v>24</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="27">
         <v>408170153</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="32">
         <v>933</v>
       </c>
-      <c r="E26" s="27"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19" t="s">
+      <c r="E26" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I26" s="23"/>
-      <c r="J26" s="24" t="s">
+      <c r="I26" s="31"/>
+      <c r="J26" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K26" s="19" t="s">
+      <c r="K26" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L26" s="25"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-    </row>
-    <row r="27" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="19">
+      <c r="L26" s="33"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+    </row>
+    <row r="27" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
         <v>25</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="27">
         <v>408170153</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="28">
         <v>934</v>
       </c>
-      <c r="E27" s="27"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19" t="s">
+      <c r="E27" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I27" s="23"/>
-      <c r="J27" s="24" t="s">
+      <c r="I27" s="31"/>
+      <c r="J27" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K27" s="19" t="s">
+      <c r="K27" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L27" s="25"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-    </row>
-    <row r="28" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="19">
+      <c r="L27" s="33"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+    </row>
+    <row r="28" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
         <v>26</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="27">
         <v>408170153</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="32">
         <v>935</v>
       </c>
-      <c r="E28" s="27"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19" t="s">
+      <c r="E28" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I28" s="23"/>
-      <c r="J28" s="24" t="s">
+      <c r="I28" s="31"/>
+      <c r="J28" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K28" s="19" t="s">
+      <c r="K28" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L28" s="25"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-    </row>
-    <row r="29" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="19">
+      <c r="L28" s="33"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+    </row>
+    <row r="29" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
         <v>27</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="27">
         <v>408170153</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="28">
         <v>936</v>
       </c>
-      <c r="E29" s="27"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19" t="s">
+      <c r="E29" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="F29" s="30"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I29" s="23"/>
-      <c r="J29" s="24" t="s">
+      <c r="I29" s="31"/>
+      <c r="J29" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K29" s="19" t="s">
+      <c r="K29" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L29" s="25"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-    </row>
-    <row r="30" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="19">
+      <c r="L29" s="33"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="34"/>
+    </row>
+    <row r="30" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
         <v>28</v>
       </c>
-      <c r="B30" s="19">
+      <c r="B30" s="27">
         <v>408170153</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="32">
         <v>937</v>
       </c>
-      <c r="E30" s="27"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19" t="s">
+      <c r="E30" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="F30" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I30" s="23"/>
-      <c r="J30" s="24" t="s">
+      <c r="I30" s="31"/>
+      <c r="J30" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K30" s="19" t="s">
+      <c r="K30" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L30" s="25"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
-    </row>
-    <row r="31" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="19">
+      <c r="L30" s="33"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
+    </row>
+    <row r="31" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
         <v>29</v>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="27">
         <v>408170153</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="28">
         <v>938</v>
       </c>
-      <c r="E31" s="27"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19" t="s">
+      <c r="E31" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I31" s="23"/>
-      <c r="J31" s="24" t="s">
+      <c r="I31" s="31"/>
+      <c r="J31" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K31" s="19" t="s">
+      <c r="K31" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L31" s="25"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-    </row>
-    <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="19">
+      <c r="L31" s="33"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+    </row>
+    <row r="32" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
         <v>30</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="27">
         <v>408170153</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="32">
         <v>939</v>
       </c>
-      <c r="E32" s="27"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19" t="s">
+      <c r="E32" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I32" s="23"/>
-      <c r="J32" s="24" t="s">
+      <c r="I32" s="31"/>
+      <c r="J32" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K32" s="19" t="s">
+      <c r="K32" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L32" s="25"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-    </row>
-    <row r="33" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="19">
+      <c r="L32" s="33"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
+      <c r="O32" s="34"/>
+    </row>
+    <row r="33" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
         <v>31</v>
       </c>
-      <c r="B33" s="19">
+      <c r="B33" s="27">
         <v>408170153</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="28">
         <v>940</v>
       </c>
-      <c r="E33" s="27"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19" t="s">
+      <c r="E33" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="F33" s="30"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="I33" s="23"/>
-      <c r="J33" s="24" t="s">
+      <c r="I33" s="31"/>
+      <c r="J33" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="K33" s="19" t="s">
+      <c r="K33" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L33" s="25"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
     </row>
     <row r="34" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
@@ -5117,26 +5185,26 @@
       <c r="C34" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="23">
         <v>941</v>
       </c>
-      <c r="E34" s="27"/>
-      <c r="F34" s="22"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="21"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I34" s="23"/>
-      <c r="J34" s="24" t="s">
+      <c r="I34" s="22"/>
+      <c r="J34" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K34" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L34" s="25"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
     </row>
     <row r="35" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="19">
@@ -5151,23 +5219,23 @@
       <c r="D35" s="20">
         <v>942</v>
       </c>
-      <c r="E35" s="27"/>
-      <c r="F35" s="22"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="21"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I35" s="23"/>
-      <c r="J35" s="24" t="s">
+      <c r="I35" s="22"/>
+      <c r="J35" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K35" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L35" s="25"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="26"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="25"/>
     </row>
     <row r="36" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
@@ -5179,26 +5247,26 @@
       <c r="C36" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="23">
         <v>943</v>
       </c>
-      <c r="E36" s="27"/>
-      <c r="F36" s="22"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="21"/>
       <c r="G36" s="19"/>
       <c r="H36" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I36" s="23"/>
-      <c r="J36" s="24" t="s">
+      <c r="I36" s="22"/>
+      <c r="J36" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K36" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L36" s="25"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="25"/>
+      <c r="N36" s="25"/>
+      <c r="O36" s="25"/>
     </row>
     <row r="37" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="19">
@@ -5213,23 +5281,23 @@
       <c r="D37" s="20">
         <v>944</v>
       </c>
-      <c r="E37" s="27"/>
-      <c r="F37" s="22"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="21"/>
       <c r="G37" s="19"/>
       <c r="H37" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I37" s="23"/>
-      <c r="J37" s="24" t="s">
+      <c r="I37" s="22"/>
+      <c r="J37" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K37" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L37" s="25"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="25"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="25"/>
     </row>
     <row r="38" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
@@ -5241,26 +5309,26 @@
       <c r="C38" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="23">
         <v>945</v>
       </c>
-      <c r="E38" s="27"/>
-      <c r="F38" s="22"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="21"/>
       <c r="G38" s="19"/>
       <c r="H38" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I38" s="23"/>
-      <c r="J38" s="24" t="s">
+      <c r="I38" s="22"/>
+      <c r="J38" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K38" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L38" s="25"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="25"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="25"/>
     </row>
     <row r="39" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="19">
@@ -5272,24 +5340,24 @@
       <c r="C39" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="22"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="21"/>
       <c r="G39" s="19"/>
       <c r="H39" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I39" s="23"/>
-      <c r="J39" s="24" t="s">
+      <c r="I39" s="22"/>
+      <c r="J39" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K39" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L39" s="25"/>
-      <c r="M39" s="26"/>
-      <c r="N39" s="26"/>
-      <c r="O39" s="26"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="25"/>
+      <c r="N39" s="25"/>
+      <c r="O39" s="25"/>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
@@ -5301,24 +5369,24 @@
       <c r="C40" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D40" s="24"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="22"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="21"/>
       <c r="G40" s="19"/>
       <c r="H40" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I40" s="23"/>
-      <c r="J40" s="24" t="s">
+      <c r="I40" s="22"/>
+      <c r="J40" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K40" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L40" s="25"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="26"/>
-      <c r="O40" s="26"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="25"/>
+      <c r="N40" s="25"/>
+      <c r="O40" s="25"/>
     </row>
     <row r="41" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="19">
@@ -5330,24 +5398,24 @@
       <c r="C41" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D41" s="24"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="22"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="21"/>
       <c r="G41" s="19"/>
       <c r="H41" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I41" s="23"/>
-      <c r="J41" s="24" t="s">
+      <c r="I41" s="22"/>
+      <c r="J41" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K41" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L41" s="25"/>
-      <c r="M41" s="26"/>
-      <c r="N41" s="26"/>
-      <c r="O41" s="26"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="25"/>
+      <c r="N41" s="25"/>
+      <c r="O41" s="25"/>
     </row>
     <row r="42" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
@@ -5359,24 +5427,24 @@
       <c r="C42" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D42" s="24"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="22"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="21"/>
       <c r="G42" s="19"/>
       <c r="H42" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I42" s="23"/>
-      <c r="J42" s="24" t="s">
+      <c r="I42" s="22"/>
+      <c r="J42" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K42" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L42" s="25"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="25"/>
+      <c r="N42" s="25"/>
+      <c r="O42" s="25"/>
     </row>
     <row r="43" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="19">
@@ -5388,24 +5456,24 @@
       <c r="C43" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D43" s="24"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="22"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="21"/>
       <c r="G43" s="19"/>
       <c r="H43" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I43" s="23"/>
-      <c r="J43" s="24" t="s">
+      <c r="I43" s="22"/>
+      <c r="J43" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K43" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L43" s="25"/>
-      <c r="M43" s="26"/>
-      <c r="N43" s="26"/>
-      <c r="O43" s="26"/>
+      <c r="L43" s="24"/>
+      <c r="M43" s="25"/>
+      <c r="N43" s="25"/>
+      <c r="O43" s="25"/>
     </row>
     <row r="44" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
@@ -5417,24 +5485,24 @@
       <c r="C44" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D44" s="24"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="22"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="21"/>
       <c r="G44" s="19"/>
       <c r="H44" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I44" s="23"/>
-      <c r="J44" s="24" t="s">
+      <c r="I44" s="22"/>
+      <c r="J44" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K44" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L44" s="25"/>
-      <c r="M44" s="26"/>
-      <c r="N44" s="26"/>
-      <c r="O44" s="26"/>
+      <c r="L44" s="24"/>
+      <c r="M44" s="25"/>
+      <c r="N44" s="25"/>
+      <c r="O44" s="25"/>
     </row>
     <row r="45" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="19">
@@ -5446,24 +5514,24 @@
       <c r="C45" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="22"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="21"/>
       <c r="G45" s="19"/>
       <c r="H45" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I45" s="23"/>
-      <c r="J45" s="24" t="s">
+      <c r="I45" s="22"/>
+      <c r="J45" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K45" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L45" s="25"/>
-      <c r="M45" s="26"/>
-      <c r="N45" s="26"/>
-      <c r="O45" s="26"/>
+      <c r="L45" s="24"/>
+      <c r="M45" s="25"/>
+      <c r="N45" s="25"/>
+      <c r="O45" s="25"/>
     </row>
     <row r="46" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="19">
@@ -5475,24 +5543,24 @@
       <c r="C46" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D46" s="24"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="22"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="21"/>
       <c r="G46" s="19"/>
       <c r="H46" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I46" s="23"/>
-      <c r="J46" s="24" t="s">
+      <c r="I46" s="22"/>
+      <c r="J46" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K46" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L46" s="25"/>
-      <c r="M46" s="26"/>
-      <c r="N46" s="26"/>
-      <c r="O46" s="26"/>
+      <c r="L46" s="24"/>
+      <c r="M46" s="25"/>
+      <c r="N46" s="25"/>
+      <c r="O46" s="25"/>
     </row>
     <row r="47" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="19">
@@ -5504,24 +5572,24 @@
       <c r="C47" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D47" s="24"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="22"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="21"/>
       <c r="G47" s="19"/>
       <c r="H47" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I47" s="23"/>
-      <c r="J47" s="24" t="s">
+      <c r="I47" s="22"/>
+      <c r="J47" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K47" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L47" s="25"/>
-      <c r="M47" s="26"/>
-      <c r="N47" s="26"/>
-      <c r="O47" s="26"/>
+      <c r="L47" s="24"/>
+      <c r="M47" s="25"/>
+      <c r="N47" s="25"/>
+      <c r="O47" s="25"/>
     </row>
     <row r="48" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
@@ -5533,24 +5601,24 @@
       <c r="C48" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D48" s="24"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="22"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="21"/>
       <c r="G48" s="19"/>
       <c r="H48" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I48" s="23"/>
-      <c r="J48" s="24" t="s">
+      <c r="I48" s="22"/>
+      <c r="J48" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K48" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L48" s="25"/>
-      <c r="M48" s="26"/>
-      <c r="N48" s="26"/>
-      <c r="O48" s="26"/>
+      <c r="L48" s="24"/>
+      <c r="M48" s="25"/>
+      <c r="N48" s="25"/>
+      <c r="O48" s="25"/>
     </row>
     <row r="49" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="19">
@@ -5562,24 +5630,24 @@
       <c r="C49" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="22"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="21"/>
       <c r="G49" s="19"/>
       <c r="H49" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I49" s="23"/>
-      <c r="J49" s="24" t="s">
+      <c r="I49" s="22"/>
+      <c r="J49" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K49" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L49" s="25"/>
-      <c r="M49" s="26"/>
-      <c r="N49" s="26"/>
-      <c r="O49" s="26"/>
+      <c r="L49" s="24"/>
+      <c r="M49" s="25"/>
+      <c r="N49" s="25"/>
+      <c r="O49" s="25"/>
     </row>
     <row r="50" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
@@ -5591,24 +5659,24 @@
       <c r="C50" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D50" s="24"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="22"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="21"/>
       <c r="G50" s="19"/>
       <c r="H50" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I50" s="23"/>
-      <c r="J50" s="24" t="s">
+      <c r="I50" s="22"/>
+      <c r="J50" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K50" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L50" s="25"/>
-      <c r="M50" s="26"/>
-      <c r="N50" s="26"/>
-      <c r="O50" s="26"/>
+      <c r="L50" s="24"/>
+      <c r="M50" s="25"/>
+      <c r="N50" s="25"/>
+      <c r="O50" s="25"/>
     </row>
     <row r="51" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="19">
@@ -5620,24 +5688,24 @@
       <c r="C51" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D51" s="24"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="22"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="21"/>
       <c r="G51" s="19"/>
       <c r="H51" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I51" s="23"/>
-      <c r="J51" s="24" t="s">
+      <c r="I51" s="22"/>
+      <c r="J51" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K51" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L51" s="25"/>
-      <c r="M51" s="26"/>
-      <c r="N51" s="26"/>
-      <c r="O51" s="26"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="25"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="25"/>
     </row>
     <row r="52" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
@@ -5649,24 +5717,24 @@
       <c r="C52" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D52" s="24"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="22"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="21"/>
       <c r="G52" s="19"/>
       <c r="H52" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I52" s="23"/>
-      <c r="J52" s="24" t="s">
+      <c r="I52" s="22"/>
+      <c r="J52" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K52" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L52" s="25"/>
-      <c r="M52" s="26"/>
-      <c r="N52" s="26"/>
-      <c r="O52" s="26"/>
+      <c r="L52" s="24"/>
+      <c r="M52" s="25"/>
+      <c r="N52" s="25"/>
+      <c r="O52" s="25"/>
     </row>
     <row r="53" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="19">
@@ -5678,24 +5746,24 @@
       <c r="C53" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D53" s="24"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="22"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="21"/>
       <c r="G53" s="19"/>
       <c r="H53" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I53" s="23"/>
-      <c r="J53" s="24" t="s">
+      <c r="I53" s="22"/>
+      <c r="J53" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K53" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L53" s="25"/>
-      <c r="M53" s="26"/>
-      <c r="N53" s="26"/>
-      <c r="O53" s="26"/>
+      <c r="L53" s="24"/>
+      <c r="M53" s="25"/>
+      <c r="N53" s="25"/>
+      <c r="O53" s="25"/>
     </row>
     <row r="54" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
@@ -5707,24 +5775,24 @@
       <c r="C54" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D54" s="24"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="22"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="21"/>
       <c r="G54" s="19"/>
       <c r="H54" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I54" s="23"/>
-      <c r="J54" s="24" t="s">
+      <c r="I54" s="22"/>
+      <c r="J54" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K54" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L54" s="25"/>
-      <c r="M54" s="26"/>
-      <c r="N54" s="26"/>
-      <c r="O54" s="26"/>
+      <c r="L54" s="24"/>
+      <c r="M54" s="25"/>
+      <c r="N54" s="25"/>
+      <c r="O54" s="25"/>
     </row>
     <row r="55" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="19">
@@ -5736,24 +5804,24 @@
       <c r="C55" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D55" s="24"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="22"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="21"/>
       <c r="G55" s="19"/>
       <c r="H55" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I55" s="23"/>
-      <c r="J55" s="24" t="s">
+      <c r="I55" s="22"/>
+      <c r="J55" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K55" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L55" s="25"/>
-      <c r="M55" s="26"/>
-      <c r="N55" s="26"/>
-      <c r="O55" s="26"/>
+      <c r="L55" s="24"/>
+      <c r="M55" s="25"/>
+      <c r="N55" s="25"/>
+      <c r="O55" s="25"/>
     </row>
     <row r="56" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
@@ -5765,24 +5833,24 @@
       <c r="C56" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D56" s="24"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="22"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="21"/>
       <c r="G56" s="19"/>
       <c r="H56" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I56" s="23"/>
-      <c r="J56" s="24" t="s">
+      <c r="I56" s="22"/>
+      <c r="J56" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K56" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L56" s="25"/>
-      <c r="M56" s="26"/>
-      <c r="N56" s="26"/>
-      <c r="O56" s="26"/>
+      <c r="L56" s="24"/>
+      <c r="M56" s="25"/>
+      <c r="N56" s="25"/>
+      <c r="O56" s="25"/>
     </row>
     <row r="57" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="19">
@@ -5794,44 +5862,60 @@
       <c r="C57" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D57" s="24"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="22"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="21"/>
       <c r="G57" s="19"/>
       <c r="H57" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I57" s="23"/>
-      <c r="J57" s="24" t="s">
+      <c r="I57" s="22"/>
+      <c r="J57" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K57" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L57" s="25"/>
-      <c r="M57" s="26"/>
-      <c r="N57" s="26"/>
-      <c r="O57" s="26"/>
+      <c r="L57" s="24"/>
+      <c r="M57" s="25"/>
+      <c r="N57" s="25"/>
+      <c r="O57" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D57">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>$H29&lt;TODAY()</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23:F23">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>$H23&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E26:F28">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$H26&lt;TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31:F32">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>$H31&lt;TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M1:M57">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N57">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6143,131 +6227,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="44"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="45"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="40"/>
     </row>
     <row r="3" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="40"/>
     </row>
     <row r="4" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="40"/>
     </row>
     <row r="5" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="39"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="40"/>
     </row>
     <row r="6" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="39"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="40"/>
     </row>
     <row r="7" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="41"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="42"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="42" t="s">
+      <c r="A21" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="44"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="45"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="39"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="40"/>
     </row>
     <row r="23" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="39"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="40"/>
     </row>
     <row r="24" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="39"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="40"/>
     </row>
     <row r="25" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="39"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="40"/>
     </row>
     <row r="26" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="39"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="40"/>
     </row>
     <row r="27" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="41"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -6304,24 +6388,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
     </row>
     <row r="2" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105C6BB7-09D2-4F4C-9819-6C091660ADE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E00AA8-D189-436B-82C3-478017051463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="243">
   <si>
     <t>S No</t>
   </si>
@@ -768,6 +768,9 @@
   </si>
   <si>
     <t>Zara Fatima</t>
+  </si>
+  <si>
+    <t>ECE (Daffodils)</t>
   </si>
 </sst>
 </file>
@@ -1107,12 +1110,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1121,6 +1118,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1132,7 +1135,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3734,7 +3747,7 @@
   </sheetData>
   <autoFilter ref="A1:J92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}"/>
   <conditionalFormatting sqref="A1:I92">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$H1&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3758,7 +3771,7 @@
     <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -4918,7 +4931,9 @@
       <c r="F26" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="G26" s="27"/>
+      <c r="G26" s="27" t="s">
+        <v>184</v>
+      </c>
       <c r="H26" s="27" t="s">
         <v>179</v>
       </c>
@@ -4953,7 +4968,9 @@
       <c r="F27" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="G27" s="27"/>
+      <c r="G27" s="27" t="s">
+        <v>184</v>
+      </c>
       <c r="H27" s="27" t="s">
         <v>179</v>
       </c>
@@ -4988,7 +5005,9 @@
       <c r="F28" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="G28" s="27"/>
+      <c r="G28" s="27" t="s">
+        <v>178</v>
+      </c>
       <c r="H28" s="27" t="s">
         <v>179</v>
       </c>
@@ -5021,7 +5040,9 @@
         <v>233</v>
       </c>
       <c r="F29" s="30"/>
-      <c r="G29" s="27"/>
+      <c r="G29" s="27" t="s">
+        <v>184</v>
+      </c>
       <c r="H29" s="27" t="s">
         <v>179</v>
       </c>
@@ -5056,7 +5077,9 @@
       <c r="F30" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="27" t="s">
+        <v>184</v>
+      </c>
       <c r="H30" s="27" t="s">
         <v>179</v>
       </c>
@@ -5091,7 +5114,9 @@
       <c r="F31" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="27" t="s">
+        <v>178</v>
+      </c>
       <c r="H31" s="27" t="s">
         <v>179</v>
       </c>
@@ -5126,7 +5151,9 @@
       <c r="F32" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="27" t="s">
+        <v>178</v>
+      </c>
       <c r="H32" s="27" t="s">
         <v>179</v>
       </c>
@@ -5159,7 +5186,9 @@
         <v>241</v>
       </c>
       <c r="F33" s="30"/>
-      <c r="G33" s="27"/>
+      <c r="G33" s="27" t="s">
+        <v>178</v>
+      </c>
       <c r="H33" s="27" t="s">
         <v>179</v>
       </c>
@@ -5188,11 +5217,17 @@
       <c r="D34" s="23">
         <v>941</v>
       </c>
-      <c r="E34" s="26"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="19"/>
+      <c r="E34" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G34" s="27" t="s">
+        <v>178</v>
+      </c>
       <c r="H34" s="19" t="s">
-        <v>179</v>
+        <v>242</v>
       </c>
       <c r="I34" s="22"/>
       <c r="J34" s="23" t="s">
@@ -5201,7 +5236,9 @@
       <c r="K34" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L34" s="24"/>
+      <c r="L34" s="24">
+        <v>45800</v>
+      </c>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
       <c r="O34" s="25"/>
@@ -5220,7 +5257,10 @@
         <v>942</v>
       </c>
       <c r="E35" s="26"/>
-      <c r="F35" s="21"/>
+      <c r="F35" s="21">
+        <f>COUNTIF($G$3:$G$33,"Male")</f>
+        <v>16</v>
+      </c>
       <c r="G35" s="19"/>
       <c r="H35" s="19" t="s">
         <v>179</v>
@@ -5251,7 +5291,10 @@
         <v>943</v>
       </c>
       <c r="E36" s="26"/>
-      <c r="F36" s="21"/>
+      <c r="F36" s="21">
+        <f>COUNTIF($G$3:$G$33,"Female")</f>
+        <v>15</v>
+      </c>
       <c r="G36" s="19"/>
       <c r="H36" s="19" t="s">
         <v>179</v>
@@ -5886,33 +5929,38 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D57">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>$H29&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23:F23">
-    <cfRule type="expression" dxfId="4" priority="7">
+    <cfRule type="expression" dxfId="5" priority="8">
       <formula>$H23&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:F28">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$H26&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:F32">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>$H31&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M57">
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1:N57">
     <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N57">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  <conditionalFormatting sqref="E34:F34">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$H34&lt;TODAY()</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -6227,13 +6275,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="45"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -6284,20 +6332,20 @@
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="42"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="45"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="45"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="43"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -6348,19 +6396,13 @@
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="42"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -6369,6 +6411,12 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E00AA8-D189-436B-82C3-478017051463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0357D3-2788-42A5-BA84-9F44B9D57D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="250">
   <si>
     <t>S No</t>
   </si>
@@ -771,6 +771,27 @@
   </si>
   <si>
     <t>ECE (Daffodils)</t>
+  </si>
+  <si>
+    <t>Noor Fajar Manzil</t>
+  </si>
+  <si>
+    <t>Ashiq Ali</t>
+  </si>
+  <si>
+    <t>45402-8515435-1</t>
+  </si>
+  <si>
+    <t>Yashba Dharejo</t>
+  </si>
+  <si>
+    <t>Class-I</t>
+  </si>
+  <si>
+    <t>Mahnoor Manzil</t>
+  </si>
+  <si>
+    <t>Class-II</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1041,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1110,6 +1131,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1119,33 +1146,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1163,6 +1175,16 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5223,7 +5245,7 @@
       <c r="F34" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G34" s="27" t="s">
+      <c r="G34" s="48" t="s">
         <v>178</v>
       </c>
       <c r="H34" s="19" t="s">
@@ -5256,25 +5278,36 @@
       <c r="D35" s="20">
         <v>942</v>
       </c>
-      <c r="E35" s="26"/>
-      <c r="F35" s="21">
-        <f>COUNTIF($G$3:$G$33,"Male")</f>
-        <v>16</v>
-      </c>
-      <c r="G35" s="19"/>
+      <c r="E35" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>178</v>
+      </c>
       <c r="H35" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="I35" s="22"/>
+      <c r="I35" s="22">
+        <v>44427</v>
+      </c>
       <c r="J35" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K35" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L35" s="24"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
+      <c r="L35" s="24">
+        <v>45801</v>
+      </c>
+      <c r="M35" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="N35" s="25">
+        <v>3083905874</v>
+      </c>
       <c r="O35" s="25"/>
     </row>
     <row r="36" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -5290,25 +5323,36 @@
       <c r="D36" s="23">
         <v>943</v>
       </c>
-      <c r="E36" s="26"/>
-      <c r="F36" s="21">
-        <f>COUNTIF($G$3:$G$33,"Female")</f>
-        <v>15</v>
-      </c>
-      <c r="G36" s="19"/>
+      <c r="E36" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>178</v>
+      </c>
       <c r="H36" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="I36" s="22"/>
+        <v>247</v>
+      </c>
+      <c r="I36" s="22">
+        <v>43906</v>
+      </c>
       <c r="J36" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K36" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L36" s="24"/>
-      <c r="M36" s="25"/>
-      <c r="N36" s="25"/>
+      <c r="L36" s="24">
+        <v>45801</v>
+      </c>
+      <c r="M36" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="N36" s="25">
+        <v>3083905874</v>
+      </c>
       <c r="O36" s="25"/>
     </row>
     <row r="37" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -5324,22 +5368,36 @@
       <c r="D37" s="20">
         <v>944</v>
       </c>
-      <c r="E37" s="26"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="19"/>
+      <c r="E37" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>178</v>
+      </c>
       <c r="H37" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="I37" s="22"/>
+        <v>249</v>
+      </c>
+      <c r="I37" s="22">
+        <v>43516</v>
+      </c>
       <c r="J37" s="23" t="s">
         <v>180</v>
       </c>
       <c r="K37" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="L37" s="24"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
+      <c r="L37" s="24">
+        <v>45801</v>
+      </c>
+      <c r="M37" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="N37" s="25">
+        <v>3083905874</v>
+      </c>
       <c r="O37" s="25"/>
     </row>
     <row r="38" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -5352,22 +5410,14 @@
       <c r="C38" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D38" s="23">
-        <v>945</v>
-      </c>
+      <c r="D38" s="23"/>
       <c r="E38" s="26"/>
       <c r="F38" s="21"/>
       <c r="G38" s="19"/>
-      <c r="H38" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H38" s="19"/>
       <c r="I38" s="22"/>
-      <c r="J38" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K38" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J38" s="23"/>
+      <c r="K38" s="19"/>
       <c r="L38" s="24"/>
       <c r="M38" s="25"/>
       <c r="N38" s="25"/>
@@ -5387,16 +5437,10 @@
       <c r="E39" s="26"/>
       <c r="F39" s="21"/>
       <c r="G39" s="19"/>
-      <c r="H39" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H39" s="19"/>
       <c r="I39" s="22"/>
-      <c r="J39" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K39" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J39" s="23"/>
+      <c r="K39" s="19"/>
       <c r="L39" s="24"/>
       <c r="M39" s="25"/>
       <c r="N39" s="25"/>
@@ -5416,16 +5460,10 @@
       <c r="E40" s="26"/>
       <c r="F40" s="21"/>
       <c r="G40" s="19"/>
-      <c r="H40" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H40" s="19"/>
       <c r="I40" s="22"/>
-      <c r="J40" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K40" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J40" s="23"/>
+      <c r="K40" s="19"/>
       <c r="L40" s="24"/>
       <c r="M40" s="25"/>
       <c r="N40" s="25"/>
@@ -5445,16 +5483,10 @@
       <c r="E41" s="26"/>
       <c r="F41" s="21"/>
       <c r="G41" s="19"/>
-      <c r="H41" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H41" s="19"/>
       <c r="I41" s="22"/>
-      <c r="J41" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K41" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J41" s="23"/>
+      <c r="K41" s="19"/>
       <c r="L41" s="24"/>
       <c r="M41" s="25"/>
       <c r="N41" s="25"/>
@@ -5474,16 +5506,10 @@
       <c r="E42" s="26"/>
       <c r="F42" s="21"/>
       <c r="G42" s="19"/>
-      <c r="H42" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H42" s="19"/>
       <c r="I42" s="22"/>
-      <c r="J42" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K42" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J42" s="23"/>
+      <c r="K42" s="19"/>
       <c r="L42" s="24"/>
       <c r="M42" s="25"/>
       <c r="N42" s="25"/>
@@ -5503,16 +5529,10 @@
       <c r="E43" s="26"/>
       <c r="F43" s="21"/>
       <c r="G43" s="19"/>
-      <c r="H43" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H43" s="19"/>
       <c r="I43" s="22"/>
-      <c r="J43" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K43" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J43" s="23"/>
+      <c r="K43" s="19"/>
       <c r="L43" s="24"/>
       <c r="M43" s="25"/>
       <c r="N43" s="25"/>
@@ -5532,16 +5552,10 @@
       <c r="E44" s="26"/>
       <c r="F44" s="21"/>
       <c r="G44" s="19"/>
-      <c r="H44" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H44" s="19"/>
       <c r="I44" s="22"/>
-      <c r="J44" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K44" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J44" s="23"/>
+      <c r="K44" s="19"/>
       <c r="L44" s="24"/>
       <c r="M44" s="25"/>
       <c r="N44" s="25"/>
@@ -5561,16 +5575,10 @@
       <c r="E45" s="26"/>
       <c r="F45" s="21"/>
       <c r="G45" s="19"/>
-      <c r="H45" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H45" s="19"/>
       <c r="I45" s="22"/>
-      <c r="J45" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K45" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J45" s="23"/>
+      <c r="K45" s="19"/>
       <c r="L45" s="24"/>
       <c r="M45" s="25"/>
       <c r="N45" s="25"/>
@@ -5590,16 +5598,10 @@
       <c r="E46" s="26"/>
       <c r="F46" s="21"/>
       <c r="G46" s="19"/>
-      <c r="H46" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H46" s="19"/>
       <c r="I46" s="22"/>
-      <c r="J46" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K46" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J46" s="23"/>
+      <c r="K46" s="19"/>
       <c r="L46" s="24"/>
       <c r="M46" s="25"/>
       <c r="N46" s="25"/>
@@ -5619,16 +5621,10 @@
       <c r="E47" s="26"/>
       <c r="F47" s="21"/>
       <c r="G47" s="19"/>
-      <c r="H47" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H47" s="19"/>
       <c r="I47" s="22"/>
-      <c r="J47" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K47" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J47" s="23"/>
+      <c r="K47" s="19"/>
       <c r="L47" s="24"/>
       <c r="M47" s="25"/>
       <c r="N47" s="25"/>
@@ -5648,16 +5644,10 @@
       <c r="E48" s="26"/>
       <c r="F48" s="21"/>
       <c r="G48" s="19"/>
-      <c r="H48" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H48" s="19"/>
       <c r="I48" s="22"/>
-      <c r="J48" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K48" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J48" s="23"/>
+      <c r="K48" s="19"/>
       <c r="L48" s="24"/>
       <c r="M48" s="25"/>
       <c r="N48" s="25"/>
@@ -5677,16 +5667,10 @@
       <c r="E49" s="26"/>
       <c r="F49" s="21"/>
       <c r="G49" s="19"/>
-      <c r="H49" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H49" s="19"/>
       <c r="I49" s="22"/>
-      <c r="J49" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K49" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J49" s="23"/>
+      <c r="K49" s="19"/>
       <c r="L49" s="24"/>
       <c r="M49" s="25"/>
       <c r="N49" s="25"/>
@@ -5706,16 +5690,10 @@
       <c r="E50" s="26"/>
       <c r="F50" s="21"/>
       <c r="G50" s="19"/>
-      <c r="H50" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H50" s="19"/>
       <c r="I50" s="22"/>
-      <c r="J50" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K50" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J50" s="23"/>
+      <c r="K50" s="19"/>
       <c r="L50" s="24"/>
       <c r="M50" s="25"/>
       <c r="N50" s="25"/>
@@ -5735,16 +5713,10 @@
       <c r="E51" s="26"/>
       <c r="F51" s="21"/>
       <c r="G51" s="19"/>
-      <c r="H51" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H51" s="19"/>
       <c r="I51" s="22"/>
-      <c r="J51" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K51" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J51" s="23"/>
+      <c r="K51" s="19"/>
       <c r="L51" s="24"/>
       <c r="M51" s="25"/>
       <c r="N51" s="25"/>
@@ -5764,16 +5736,10 @@
       <c r="E52" s="26"/>
       <c r="F52" s="21"/>
       <c r="G52" s="19"/>
-      <c r="H52" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H52" s="19"/>
       <c r="I52" s="22"/>
-      <c r="J52" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K52" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J52" s="23"/>
+      <c r="K52" s="19"/>
       <c r="L52" s="24"/>
       <c r="M52" s="25"/>
       <c r="N52" s="25"/>
@@ -5793,16 +5759,10 @@
       <c r="E53" s="26"/>
       <c r="F53" s="21"/>
       <c r="G53" s="19"/>
-      <c r="H53" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H53" s="19"/>
       <c r="I53" s="22"/>
-      <c r="J53" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K53" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J53" s="23"/>
+      <c r="K53" s="19"/>
       <c r="L53" s="24"/>
       <c r="M53" s="25"/>
       <c r="N53" s="25"/>
@@ -5822,16 +5782,10 @@
       <c r="E54" s="26"/>
       <c r="F54" s="21"/>
       <c r="G54" s="19"/>
-      <c r="H54" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H54" s="19"/>
       <c r="I54" s="22"/>
-      <c r="J54" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K54" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J54" s="23"/>
+      <c r="K54" s="19"/>
       <c r="L54" s="24"/>
       <c r="M54" s="25"/>
       <c r="N54" s="25"/>
@@ -5851,16 +5805,10 @@
       <c r="E55" s="26"/>
       <c r="F55" s="21"/>
       <c r="G55" s="19"/>
-      <c r="H55" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H55" s="19"/>
       <c r="I55" s="22"/>
-      <c r="J55" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K55" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J55" s="23"/>
+      <c r="K55" s="19"/>
       <c r="L55" s="24"/>
       <c r="M55" s="25"/>
       <c r="N55" s="25"/>
@@ -5880,16 +5828,10 @@
       <c r="E56" s="26"/>
       <c r="F56" s="21"/>
       <c r="G56" s="19"/>
-      <c r="H56" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H56" s="19"/>
       <c r="I56" s="22"/>
-      <c r="J56" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K56" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J56" s="23"/>
+      <c r="K56" s="19"/>
       <c r="L56" s="24"/>
       <c r="M56" s="25"/>
       <c r="N56" s="25"/>
@@ -5909,16 +5851,10 @@
       <c r="E57" s="26"/>
       <c r="F57" s="21"/>
       <c r="G57" s="19"/>
-      <c r="H57" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H57" s="19"/>
       <c r="I57" s="22"/>
-      <c r="J57" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K57" s="19" t="s">
-        <v>181</v>
-      </c>
+      <c r="J57" s="23"/>
+      <c r="K57" s="19"/>
       <c r="L57" s="24"/>
       <c r="M57" s="25"/>
       <c r="N57" s="25"/>
@@ -5951,16 +5887,16 @@
       <formula>$H31&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E34:F34">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>$H34&lt;TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M1:M57">
-    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N57">
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E34:F34">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$H34&lt;TODAY()</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -6275,13 +6211,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="45"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -6332,20 +6268,20 @@
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="45"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="42"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="43"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="45"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -6396,13 +6332,19 @@
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="45"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -6411,12 +6353,6 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0357D3-2788-42A5-BA84-9F44B9D57D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C634AD-E1F2-4F42-9516-904357842C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="254">
   <si>
     <t>S No</t>
   </si>
@@ -792,6 +792,18 @@
   </si>
   <si>
     <t>Class-II</t>
+  </si>
+  <si>
+    <t>Kinza</t>
+  </si>
+  <si>
+    <t>Sohail Khan</t>
+  </si>
+  <si>
+    <t>43205-3254253-5</t>
+  </si>
+  <si>
+    <t>B-Form, Photos, Birth Certificate, Blood Test, NIC</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1053,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1131,12 +1143,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1146,13 +1152,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3783,7 +3794,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
@@ -5191,7 +5202,7 @@
       <c r="N32" s="34"/>
       <c r="O32" s="34"/>
     </row>
-    <row r="33" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="27">
         <v>31</v>
       </c>
@@ -5226,7 +5237,7 @@
       <c r="N33" s="34"/>
       <c r="O33" s="34"/>
     </row>
-    <row r="34" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>32</v>
       </c>
@@ -5245,7 +5256,7 @@
       <c r="F34" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G34" s="48" t="s">
+      <c r="G34" s="19" t="s">
         <v>178</v>
       </c>
       <c r="H34" s="19" t="s">
@@ -5265,7 +5276,7 @@
       <c r="N34" s="25"/>
       <c r="O34" s="25"/>
     </row>
-    <row r="35" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="19">
         <v>33</v>
       </c>
@@ -5310,7 +5321,7 @@
       </c>
       <c r="O35" s="25"/>
     </row>
-    <row r="36" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>34</v>
       </c>
@@ -5355,7 +5366,7 @@
       </c>
       <c r="O36" s="25"/>
     </row>
-    <row r="37" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="19">
         <v>35</v>
       </c>
@@ -5400,7 +5411,7 @@
       </c>
       <c r="O37" s="25"/>
     </row>
-    <row r="38" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>36</v>
       </c>
@@ -5410,20 +5421,45 @@
       <c r="C38" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D38" s="23"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="25"/>
-      <c r="N38" s="25"/>
+      <c r="D38" s="23">
+        <v>945</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" s="22">
+        <v>43824</v>
+      </c>
+      <c r="J38" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="K38" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="L38" s="24">
+        <v>45806</v>
+      </c>
+      <c r="M38" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="N38" s="25">
+        <v>3331249111</v>
+      </c>
       <c r="O38" s="25"/>
-    </row>
-    <row r="39" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P38" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="19">
         <v>37</v>
       </c>
@@ -5446,7 +5482,7 @@
       <c r="N39" s="25"/>
       <c r="O39" s="25"/>
     </row>
-    <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>38</v>
       </c>
@@ -5469,7 +5505,7 @@
       <c r="N40" s="25"/>
       <c r="O40" s="25"/>
     </row>
-    <row r="41" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="19">
         <v>39</v>
       </c>
@@ -5492,7 +5528,7 @@
       <c r="N41" s="25"/>
       <c r="O41" s="25"/>
     </row>
-    <row r="42" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>40</v>
       </c>
@@ -5515,7 +5551,7 @@
       <c r="N42" s="25"/>
       <c r="O42" s="25"/>
     </row>
-    <row r="43" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="19">
         <v>41</v>
       </c>
@@ -5538,7 +5574,7 @@
       <c r="N43" s="25"/>
       <c r="O43" s="25"/>
     </row>
-    <row r="44" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>42</v>
       </c>
@@ -5561,7 +5597,7 @@
       <c r="N44" s="25"/>
       <c r="O44" s="25"/>
     </row>
-    <row r="45" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="19">
         <v>43</v>
       </c>
@@ -5584,7 +5620,7 @@
       <c r="N45" s="25"/>
       <c r="O45" s="25"/>
     </row>
-    <row r="46" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="19">
         <v>44</v>
       </c>
@@ -5607,7 +5643,7 @@
       <c r="N46" s="25"/>
       <c r="O46" s="25"/>
     </row>
-    <row r="47" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="19">
         <v>45</v>
       </c>
@@ -5630,7 +5666,7 @@
       <c r="N47" s="25"/>
       <c r="O47" s="25"/>
     </row>
-    <row r="48" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>46</v>
       </c>
@@ -6211,13 +6247,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="45"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -6268,20 +6304,20 @@
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="42"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="45"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="45"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="43"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -6332,19 +6368,13 @@
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="42"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B7:E7"/>
@@ -6353,6 +6383,12 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C634AD-E1F2-4F42-9516-904357842C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135903D0-10ED-41A2-AC57-E881B47C36C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,12 @@
     <sheet name="Test Date" sheetId="2" r:id="rId3"/>
     <sheet name="Test" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
-    <sheet name="Drop Out" sheetId="8" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId6"/>
+    <sheet name="Drop Out" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Registration!$A$1:$J$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Admissions!$A$2:$O$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Registration!$A$1:$J$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="279">
   <si>
     <t>S No</t>
   </si>
@@ -656,12 +658,6 @@
     <t>Zain Ullah</t>
   </si>
   <si>
-    <t>Aon Ali</t>
-  </si>
-  <si>
-    <t>Imran Ali</t>
-  </si>
-  <si>
     <t>Hafsa</t>
   </si>
   <si>
@@ -764,12 +760,6 @@
     <t>c/o sir shunail</t>
   </si>
   <si>
-    <t>Ismail</t>
-  </si>
-  <si>
-    <t>Zara Fatima</t>
-  </si>
-  <si>
     <t>ECE (Daffodils)</t>
   </si>
   <si>
@@ -785,15 +775,9 @@
     <t>Yashba Dharejo</t>
   </si>
   <si>
-    <t>Class-I</t>
-  </si>
-  <si>
     <t>Mahnoor Manzil</t>
   </si>
   <si>
-    <t>Class-II</t>
-  </si>
-  <si>
     <t>Kinza</t>
   </si>
   <si>
@@ -803,7 +787,100 @@
     <t>43205-3254253-5</t>
   </si>
   <si>
-    <t>B-Form, Photos, Birth Certificate, Blood Test, NIC</t>
+    <t>Class-3</t>
+  </si>
+  <si>
+    <t>Class-2</t>
+  </si>
+  <si>
+    <t>Boys</t>
+  </si>
+  <si>
+    <t>Girls</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>One</t>
+  </si>
+  <si>
+    <t>Two</t>
+  </si>
+  <si>
+    <t>Three</t>
+  </si>
+  <si>
+    <t>Four</t>
+  </si>
+  <si>
+    <t>Five</t>
+  </si>
+  <si>
+    <t>Six</t>
+  </si>
+  <si>
+    <t>Seven</t>
+  </si>
+  <si>
+    <t>Eight</t>
+  </si>
+  <si>
+    <t>Nine</t>
+  </si>
+  <si>
+    <t>Muhammad Awais</t>
+  </si>
+  <si>
+    <t>Abdul Aziz</t>
+  </si>
+  <si>
+    <t>42501-7115644-5</t>
+  </si>
+  <si>
+    <t>Qadir Bux</t>
+  </si>
+  <si>
+    <t>43402-0958608-4</t>
+  </si>
+  <si>
+    <t>Muhammad Shayan</t>
+  </si>
+  <si>
+    <t>Ansar Ahmed</t>
+  </si>
+  <si>
+    <t>45204-5217782-8</t>
+  </si>
+  <si>
+    <t>Shanzy Fatima</t>
+  </si>
+  <si>
+    <t>43402-0471187-3</t>
+  </si>
+  <si>
+    <t>45204-8108080-3</t>
+  </si>
+  <si>
+    <t>Aneeta</t>
+  </si>
+  <si>
+    <t>Naeem Ahmed</t>
+  </si>
+  <si>
+    <t>Class-4</t>
+  </si>
+  <si>
+    <t>45203-9721947-3</t>
+  </si>
+  <si>
+    <t>Anosha</t>
+  </si>
+  <si>
+    <t>Faheem</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1096,13 +1173,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1117,23 +1188,13 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1164,11 +1225,46 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1184,7 +1280,17 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -1196,56 +1302,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1569,7 +1625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}">
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
@@ -1756,7 +1812,7 @@
       </c>
       <c r="I6" s="6"/>
       <c r="J6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -2503,7 +2559,7 @@
       </c>
       <c r="I34" s="6"/>
       <c r="J34" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -3213,16 +3269,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="F62" s="4">
         <v>3030439230</v>
@@ -3242,16 +3298,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="F63" s="4">
         <v>3151184877</v>
@@ -3271,16 +3327,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="F64" s="4">
         <v>3178789685</v>
@@ -3300,16 +3356,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="F65" s="4">
         <v>3323425295</v>
@@ -3324,7 +3380,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="J65" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -3332,7 +3388,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3" t="s">
@@ -3355,16 +3411,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="F67" s="4">
         <v>3360576896</v>
@@ -3378,11 +3434,11 @@
       <c r="I67" s="6">
         <v>0.39583333333333331</v>
       </c>
-      <c r="J67" s="35">
+      <c r="J67" s="16">
         <v>43949</v>
       </c>
       <c r="K67" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -3390,16 +3446,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F68" s="4">
         <v>3360576896</v>
@@ -3413,7 +3469,7 @@
       <c r="I68" s="6">
         <v>0.39583333333333331</v>
       </c>
-      <c r="J68" s="35">
+      <c r="J68" s="16">
         <v>42958</v>
       </c>
     </row>
@@ -3421,61 +3477,117 @@
       <c r="A69" s="2">
         <v>68</v>
       </c>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I69" s="6"/>
+      <c r="B69" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F69" s="4">
+        <v>3013313553</v>
+      </c>
+      <c r="G69" s="5">
+        <v>45874</v>
+      </c>
+      <c r="H69" s="5">
+        <v>45876</v>
+      </c>
+      <c r="I69" s="6">
+        <v>0.39583333333333331</v>
+      </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I70" s="6"/>
+      <c r="B70" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F70" s="4">
+        <v>3363396753</v>
+      </c>
+      <c r="G70" s="5">
+        <v>45874</v>
+      </c>
+      <c r="H70" s="5">
+        <v>45876</v>
+      </c>
+      <c r="I70" s="6">
+        <v>0.39583333333333331</v>
+      </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I71" s="6"/>
+      <c r="B71" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F71" s="4">
+        <v>3337112133</v>
+      </c>
+      <c r="G71" s="5">
+        <v>45874</v>
+      </c>
+      <c r="H71" s="5">
+        <v>45876</v>
+      </c>
+      <c r="I71" s="6">
+        <v>0.39583333333333331</v>
+      </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I72" s="6"/>
+      <c r="B72" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F72" s="4">
+        <v>3337112133</v>
+      </c>
+      <c r="G72" s="5">
+        <v>45874</v>
+      </c>
+      <c r="H72" s="5">
+        <v>45876</v>
+      </c>
+      <c r="I72" s="6">
+        <v>0.39583333333333331</v>
+      </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
@@ -3762,25 +3874,9 @@
       </c>
       <c r="I91" s="6"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
-        <v>91</v>
-      </c>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="5"/>
-      <c r="H92" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I92" s="6"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J92" xr:uid="{1828FFCB-D8F5-4B91-AACC-9381EDE31E0A}"/>
-  <conditionalFormatting sqref="A1:I92">
-    <cfRule type="expression" dxfId="8" priority="1">
+  <conditionalFormatting sqref="A1:I68 A69 D69:I69 A70:I91">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>$H1&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3794,7 +3890,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
@@ -3815,23 +3911,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -3858,16 +3954,16 @@
       <c r="H2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="26" t="s">
         <v>171</v>
       </c>
       <c r="K2" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="27" t="s">
         <v>173</v>
       </c>
       <c r="M2" s="14" t="s">
@@ -3880,2059 +3976,1463 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="27">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="38">
         <v>1</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="38">
         <v>408170153</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D3" s="28">
-        <v>910</v>
-      </c>
-      <c r="E3" s="37" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H3" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="I3" s="42">
+        <v>43088</v>
+      </c>
+      <c r="J3" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K3" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L3" s="43">
+        <v>45770</v>
+      </c>
+      <c r="M3" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="38">
+        <v>2</v>
+      </c>
+      <c r="B4" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="21"/>
+      <c r="E4" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H4" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="I4" s="42">
+        <v>42853</v>
+      </c>
+      <c r="J4" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L4" s="43">
+        <v>45775</v>
+      </c>
+      <c r="M4" s="44" t="s">
+        <v>225</v>
+      </c>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="38">
+        <v>3</v>
+      </c>
+      <c r="B5" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="I5" s="42">
+        <v>43906</v>
+      </c>
+      <c r="J5" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L5" s="43">
+        <v>45801</v>
+      </c>
+      <c r="M5" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="N5" s="44">
+        <v>3083905874</v>
+      </c>
+      <c r="O5" s="44" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="38">
+        <v>4</v>
+      </c>
+      <c r="B6" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D6" s="39"/>
+      <c r="E6" s="40" t="s">
+        <v>269</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="I6" s="42">
+        <v>43267</v>
+      </c>
+      <c r="J6" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K6" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L6" s="43">
+        <v>45876</v>
+      </c>
+      <c r="M6" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="N6" s="44">
+        <v>3337112133</v>
+      </c>
+      <c r="O6" s="44" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="38">
+        <v>5</v>
+      </c>
+      <c r="B7" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" s="46"/>
+      <c r="E7" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="I7" s="42">
+        <v>43101</v>
+      </c>
+      <c r="J7" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K7" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L7" s="43">
+        <v>45757</v>
+      </c>
+      <c r="M7" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="N7" s="23">
+        <v>3080471611</v>
+      </c>
+      <c r="O7" s="44" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="38">
+        <v>6</v>
+      </c>
+      <c r="B8" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="39"/>
+      <c r="E8" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H8" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="I8" s="42">
+        <v>43466</v>
+      </c>
+      <c r="J8" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K8" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L8" s="43">
+        <v>45757</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="N8" s="23">
+        <v>3080471611</v>
+      </c>
+      <c r="O8" s="44" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="38">
+        <v>7</v>
+      </c>
+      <c r="B9" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" s="46"/>
+      <c r="E9" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H9" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="I9" s="42">
+        <v>43516</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K9" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L9" s="43">
+        <v>45801</v>
+      </c>
+      <c r="M9" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="N9" s="44">
+        <v>3083905874</v>
+      </c>
+      <c r="O9" s="44" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="38">
+        <v>8</v>
+      </c>
+      <c r="B10" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="39"/>
+      <c r="E10" s="49" t="s">
+        <v>211</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="I10" s="42">
+        <v>42956</v>
+      </c>
+      <c r="J10" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K10" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L10" s="43">
+        <v>45776</v>
+      </c>
+      <c r="M10" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="N10" s="44">
+        <v>3030439230</v>
+      </c>
+      <c r="O10" s="44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="38">
+        <v>9</v>
+      </c>
+      <c r="B11" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="I11" s="42">
+        <v>42424</v>
+      </c>
+      <c r="J11" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K11" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L11" s="43">
+        <v>45876</v>
+      </c>
+      <c r="M11" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="N11" s="44">
+        <v>3337112133</v>
+      </c>
+      <c r="O11" s="44" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="38">
+        <v>10</v>
+      </c>
+      <c r="B12" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="39"/>
+      <c r="E12" s="40" t="s">
+        <v>272</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H12" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="I12" s="42">
+        <v>42095</v>
+      </c>
+      <c r="J12" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K12" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L12" s="43">
+        <v>45757</v>
+      </c>
+      <c r="M12" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="N12" s="23">
+        <v>3080471611</v>
+      </c>
+      <c r="O12" s="44" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="38">
+        <v>11</v>
+      </c>
+      <c r="B13" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="21"/>
+      <c r="E13" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="I13" s="42">
+        <v>43824</v>
+      </c>
+      <c r="J13" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K13" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L13" s="43">
+        <v>45806</v>
+      </c>
+      <c r="M13" s="44" t="s">
+        <v>246</v>
+      </c>
+      <c r="N13" s="44">
+        <v>3331249111</v>
+      </c>
+      <c r="O13" s="44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="38">
+        <v>12</v>
+      </c>
+      <c r="B14" s="17">
+        <v>408170153</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F14" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G14" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H14" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="31">
+      <c r="I14" s="20">
         <v>43711</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J14" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K14" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L3" s="33">
+      <c r="L14" s="22">
         <v>45770</v>
       </c>
-      <c r="M3" s="34" t="s">
+      <c r="M14" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="N3" s="34">
+      <c r="N14" s="23">
         <v>3008912581</v>
       </c>
-      <c r="O3" s="34" t="s">
+      <c r="O14" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="27">
-        <v>2</v>
-      </c>
-      <c r="B4" s="27">
+    <row r="15" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="38">
+        <v>13</v>
+      </c>
+      <c r="B15" s="38">
         <v>408170153</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C15" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="32">
-        <v>911</v>
-      </c>
-      <c r="E4" s="29" t="s">
+      <c r="D15" s="39"/>
+      <c r="E15" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F15" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G15" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H15" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I15" s="42">
         <v>44013</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J15" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="K4" s="27" t="s">
+      <c r="K15" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L15" s="43">
         <v>45770</v>
       </c>
-      <c r="M4" s="34" t="s">
+      <c r="M15" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N15" s="44">
         <v>3408550574</v>
       </c>
-      <c r="O4" s="34" t="s">
+      <c r="O15" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="27">
-        <v>3</v>
-      </c>
-      <c r="B5" s="27">
+    <row r="16" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="38">
+        <v>14</v>
+      </c>
+      <c r="B16" s="38">
         <v>408170153</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C16" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D5" s="28">
-        <v>912</v>
-      </c>
-      <c r="E5" s="29" t="s">
+      <c r="D16" s="18"/>
+      <c r="E16" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F16" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G16" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H16" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="I5" s="31">
+      <c r="I16" s="42">
         <v>43832</v>
       </c>
-      <c r="J5" s="32" t="s">
+      <c r="J16" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="K16" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="L5" s="33">
+      <c r="L16" s="43">
         <v>45770</v>
       </c>
-      <c r="M5" s="34" t="s">
+      <c r="M16" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N16" s="44">
         <v>3022345160</v>
       </c>
-      <c r="O5" s="34" t="s">
+      <c r="O16" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="27">
-        <v>4</v>
-      </c>
-      <c r="B6" s="27">
+    <row r="17" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="38">
+        <v>15</v>
+      </c>
+      <c r="B17" s="38">
         <v>408170153</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C17" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D6" s="32">
-        <v>913</v>
-      </c>
-      <c r="E6" s="29" t="s">
+      <c r="D17" s="39"/>
+      <c r="E17" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F17" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G17" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H17" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I17" s="42">
         <v>43574</v>
       </c>
-      <c r="J6" s="32" t="s">
+      <c r="J17" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="K6" s="27" t="s">
+      <c r="K17" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="L6" s="33">
+      <c r="L17" s="43">
         <v>45770</v>
       </c>
-      <c r="M6" s="34" t="s">
+      <c r="M17" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N17" s="44">
         <v>3152717911</v>
       </c>
-      <c r="O6" s="34" t="s">
+      <c r="O17" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
-        <v>5</v>
-      </c>
-      <c r="B7" s="27">
+    <row r="18" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="38">
+        <v>16</v>
+      </c>
+      <c r="B18" s="38">
         <v>408170153</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C18" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="28">
-        <v>914</v>
-      </c>
-      <c r="E7" s="29" t="s">
+      <c r="D18" s="18"/>
+      <c r="E18" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F18" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G18" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H18" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I18" s="42">
         <v>43879</v>
       </c>
-      <c r="J7" s="32" t="s">
+      <c r="J18" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="K7" s="27" t="s">
+      <c r="K18" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="L7" s="33">
+      <c r="L18" s="43">
         <v>45770</v>
       </c>
-      <c r="M7" s="34" t="s">
+      <c r="M18" s="44" t="s">
         <v>190</v>
       </c>
-      <c r="N7" s="34">
+      <c r="N18" s="44">
         <v>3213522748</v>
       </c>
-      <c r="O7" s="34" t="s">
+      <c r="O18" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="27">
-        <v>6</v>
-      </c>
-      <c r="B8" s="27">
+    <row r="19" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="38">
+        <v>17</v>
+      </c>
+      <c r="B19" s="38">
         <v>408170153</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C19" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D8" s="32">
-        <v>915</v>
-      </c>
-      <c r="E8" s="29" t="s">
+      <c r="D19" s="39"/>
+      <c r="E19" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F19" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G19" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H19" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I19" s="42">
         <v>43471</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J19" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="K8" s="27" t="s">
+      <c r="K19" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="L8" s="33">
+      <c r="L19" s="43">
         <v>45770</v>
       </c>
-      <c r="M8" s="34" t="s">
+      <c r="M19" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="N8" s="34">
+      <c r="N19" s="44">
         <v>3472586633</v>
       </c>
-      <c r="O8" s="34" t="s">
+      <c r="O19" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
-        <v>7</v>
-      </c>
-      <c r="B9" s="27">
+    <row r="20" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="38">
+        <v>18</v>
+      </c>
+      <c r="B20" s="38">
         <v>408170153</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C20" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D9" s="28">
-        <v>916</v>
-      </c>
-      <c r="E9" s="29" t="s">
+      <c r="D20" s="18"/>
+      <c r="E20" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F20" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G20" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="H20" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I20" s="42">
         <v>44143</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J20" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="K9" s="27" t="s">
+      <c r="K20" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="L9" s="33">
+      <c r="L20" s="43">
         <v>45770</v>
       </c>
-      <c r="M9" s="34" t="s">
+      <c r="M20" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="N9" s="34">
+      <c r="N20" s="44">
         <v>3368603595</v>
       </c>
-      <c r="O9" s="34" t="s">
+      <c r="O20" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="19">
-        <v>8</v>
-      </c>
-      <c r="B10" s="19">
+    <row r="21" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="38">
+        <v>19</v>
+      </c>
+      <c r="B21" s="38">
         <v>408170153</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C21" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D10" s="23">
-        <v>917</v>
-      </c>
-      <c r="E10" s="26" t="s">
+      <c r="D21" s="39"/>
+      <c r="E21" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F21" s="48" t="s">
         <v>194</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G21" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H21" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I21" s="42">
         <v>44096</v>
       </c>
-      <c r="J10" s="23" t="s">
+      <c r="J21" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K21" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="L10" s="24">
+      <c r="L21" s="43">
         <v>45770</v>
       </c>
-      <c r="M10" s="25" t="s">
+      <c r="M21" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N21" s="44">
         <v>3158719338</v>
       </c>
-      <c r="O10" s="25" t="s">
+      <c r="O21" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
+    <row r="22" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="38">
+        <v>20</v>
+      </c>
+      <c r="B22" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" s="46"/>
+      <c r="E22" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="F22" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H22" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="I22" s="42">
+        <v>44069</v>
+      </c>
+      <c r="J22" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K22" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L22" s="43">
+        <v>45770</v>
+      </c>
+      <c r="M22" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="N22" s="44">
+        <v>3333115124</v>
+      </c>
+      <c r="O22" s="44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="38">
+        <v>21</v>
+      </c>
+      <c r="B23" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D23" s="21"/>
+      <c r="E23" s="40" t="s">
+        <v>198</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="I23" s="42">
+        <v>43881</v>
+      </c>
+      <c r="J23" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K23" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L23" s="43">
+        <v>45770</v>
+      </c>
+      <c r="M23" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="N23" s="44">
+        <v>3412510302</v>
+      </c>
+      <c r="O23" s="44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="38">
+        <v>22</v>
+      </c>
+      <c r="B24" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D24" s="46"/>
+      <c r="E24" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="I24" s="42">
+        <v>43936</v>
+      </c>
+      <c r="J24" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K24" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L24" s="43">
+        <v>45770</v>
+      </c>
+      <c r="M24" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="44">
+        <v>3471801620</v>
+      </c>
+      <c r="O24" s="44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="38">
+        <v>23</v>
+      </c>
+      <c r="B25" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="21"/>
+      <c r="E25" s="40" t="s">
+        <v>201</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H25" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="I25" s="42">
+        <v>43871</v>
+      </c>
+      <c r="J25" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K25" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L25" s="43">
+        <v>45770</v>
+      </c>
+      <c r="M25" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" s="44">
+        <v>3471801620</v>
+      </c>
+      <c r="O25" s="44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="38">
+        <v>24</v>
+      </c>
+      <c r="B26" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D26" s="46"/>
+      <c r="E26" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="F26" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="G26" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H26" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="I26" s="42">
+        <v>43936</v>
+      </c>
+      <c r="J26" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K26" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L26" s="43">
+        <v>45770</v>
+      </c>
+      <c r="M26" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" s="44">
+        <v>3471801620</v>
+      </c>
+      <c r="O26" s="44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="38">
+        <v>25</v>
+      </c>
+      <c r="B27" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="21"/>
+      <c r="E27" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H27" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="I27" s="42">
+        <v>43723</v>
+      </c>
+      <c r="J27" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K27" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L27" s="43">
+        <v>45770</v>
+      </c>
+      <c r="M27" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="N27" s="44">
+        <v>3146147223</v>
+      </c>
+      <c r="O27" s="44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="38">
+        <v>26</v>
+      </c>
+      <c r="B28" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D28" s="46"/>
+      <c r="E28" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="19">
+      <c r="F28" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H28" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="I28" s="42">
+        <v>43930</v>
+      </c>
+      <c r="J28" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K28" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L28" s="43">
+        <v>45770</v>
+      </c>
+      <c r="M28" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="N28" s="44">
+        <v>3437668872</v>
+      </c>
+      <c r="O28" s="44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="38">
+        <v>27</v>
+      </c>
+      <c r="B29" s="38">
         <v>408170153</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C29" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D11" s="20">
-        <v>918</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="G11" s="19" t="s">
+      <c r="D29" s="21"/>
+      <c r="E29" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="G29" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="H11" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="I11" s="22">
-        <v>43088</v>
-      </c>
-      <c r="J11" s="23" t="s">
+      <c r="H29" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="I29" s="42">
+        <v>43830</v>
+      </c>
+      <c r="J29" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="K11" s="19" t="s">
+      <c r="K29" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="L11" s="24">
-        <v>45770</v>
-      </c>
-      <c r="M11" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25" t="s">
+      <c r="L29" s="43">
+        <v>45771</v>
+      </c>
+      <c r="M29" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="N29" s="44">
+        <v>3018250207</v>
+      </c>
+      <c r="O29" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="27">
-        <v>10</v>
-      </c>
-      <c r="B12" s="27">
+    <row r="30" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="38">
+        <v>28</v>
+      </c>
+      <c r="B30" s="38">
         <v>408170153</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C30" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D12" s="32">
-        <v>919</v>
-      </c>
-      <c r="E12" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="G12" s="27" t="s">
+      <c r="D30" s="46"/>
+      <c r="E30" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="H12" s="27" t="s">
+      <c r="H30" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="I12" s="31">
-        <v>44069</v>
-      </c>
-      <c r="J12" s="32" t="s">
+      <c r="I30" s="42">
+        <v>43626</v>
+      </c>
+      <c r="J30" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="K12" s="27" t="s">
+      <c r="K30" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="L12" s="33">
-        <v>45770</v>
-      </c>
-      <c r="M12" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="N12" s="34">
-        <v>3333115124</v>
-      </c>
-      <c r="O12" s="34" t="s">
+      <c r="L30" s="43">
+        <v>45771</v>
+      </c>
+      <c r="M30" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="N30" s="44">
+        <v>3012244916</v>
+      </c>
+      <c r="O30" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="27">
-        <v>11</v>
-      </c>
-      <c r="B13" s="27">
+    <row r="31" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="38">
+        <v>29</v>
+      </c>
+      <c r="B31" s="38">
         <v>408170153</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C31" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="28">
-        <v>920</v>
-      </c>
-      <c r="E13" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="G13" s="27" t="s">
+      <c r="D31" s="18"/>
+      <c r="E31" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="F31" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="G31" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="H13" s="27" t="s">
+      <c r="H31" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="I13" s="31">
-        <v>43881</v>
-      </c>
-      <c r="J13" s="32" t="s">
+      <c r="I31" s="42">
+        <v>44419</v>
+      </c>
+      <c r="J31" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="K13" s="27" t="s">
+      <c r="K31" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="L13" s="33">
-        <v>45770</v>
-      </c>
-      <c r="M13" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="N13" s="34">
-        <v>3412510302</v>
-      </c>
-      <c r="O13" s="34" t="s">
+      <c r="L31" s="43">
+        <v>45776</v>
+      </c>
+      <c r="M31" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="N31" s="44"/>
+      <c r="O31" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="27">
-        <v>12</v>
-      </c>
-      <c r="B14" s="27">
+    <row r="32" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="38">
+        <v>30</v>
+      </c>
+      <c r="B32" s="38">
         <v>408170153</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C32" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D14" s="32">
-        <v>921</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="27" t="s">
+      <c r="D32" s="39"/>
+      <c r="E32" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="F32" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="G32" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H32" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="I32" s="42">
+        <v>43419</v>
+      </c>
+      <c r="J32" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K32" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L32" s="43">
+        <v>45779</v>
+      </c>
+      <c r="M32" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="N32" s="44">
+        <v>3178789685</v>
+      </c>
+      <c r="O32" s="44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="38">
+        <v>31</v>
+      </c>
+      <c r="B33" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D33" s="39"/>
+      <c r="E33" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="F33" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="G33" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="H14" s="27" t="s">
+      <c r="H33" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="I14" s="31">
-        <v>43936</v>
-      </c>
-      <c r="J14" s="32" t="s">
+      <c r="I33" s="42">
+        <v>44427</v>
+      </c>
+      <c r="J33" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="K14" s="27" t="s">
+      <c r="K33" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="L14" s="33">
-        <v>45770</v>
-      </c>
-      <c r="M14" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="N14" s="34">
-        <v>3471801620</v>
-      </c>
-      <c r="O14" s="34" t="s">
+      <c r="L33" s="43">
+        <v>45801</v>
+      </c>
+      <c r="M33" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="N33" s="44">
+        <v>3083905874</v>
+      </c>
+      <c r="O33" s="44" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="38">
+        <v>32</v>
+      </c>
+      <c r="B34" s="38">
+        <v>408170153</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D34" s="39"/>
+      <c r="E34" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="G34" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H34" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="I34" s="42">
+        <v>44159</v>
+      </c>
+      <c r="J34" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="K34" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L34" s="43">
+        <v>45876</v>
+      </c>
+      <c r="M34" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="N34" s="44">
+        <v>3363396753</v>
+      </c>
+      <c r="O34" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="27">
-        <v>13</v>
-      </c>
-      <c r="B15" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D15" s="28">
-        <v>922</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="F15" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="H15" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I15" s="31">
-        <v>43871</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K15" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L15" s="33">
-        <v>45770</v>
-      </c>
-      <c r="M15" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="34">
-        <v>3471801620</v>
-      </c>
-      <c r="O15" s="34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="27">
-        <v>14</v>
-      </c>
-      <c r="B16" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D16" s="32">
-        <v>923</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="F16" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="H16" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I16" s="31">
-        <v>43936</v>
-      </c>
-      <c r="J16" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K16" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L16" s="33">
-        <v>45770</v>
-      </c>
-      <c r="M16" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="N16" s="34">
-        <v>3471801620</v>
-      </c>
-      <c r="O16" s="34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="27">
-        <v>15</v>
-      </c>
-      <c r="B17" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D17" s="28">
-        <v>924</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="F17" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="H17" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I17" s="31">
-        <v>43723</v>
-      </c>
-      <c r="J17" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L17" s="33">
-        <v>45770</v>
-      </c>
-      <c r="M17" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="N17" s="34">
-        <v>3146147223</v>
-      </c>
-      <c r="O17" s="34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="27">
-        <v>16</v>
-      </c>
-      <c r="B18" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D18" s="32">
-        <v>925</v>
-      </c>
-      <c r="E18" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="H18" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I18" s="31">
-        <v>43930</v>
-      </c>
-      <c r="J18" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K18" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L18" s="33">
-        <v>45770</v>
-      </c>
-      <c r="M18" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="N18" s="34">
-        <v>3437668872</v>
-      </c>
-      <c r="O18" s="34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="27">
-        <v>17</v>
-      </c>
-      <c r="B19" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D19" s="28">
-        <v>926</v>
-      </c>
-      <c r="E19" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="F19" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="G19" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="H19" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I19" s="31"/>
-      <c r="J19" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K19" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L19" s="33"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-    </row>
-    <row r="20" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="27">
-        <v>18</v>
-      </c>
-      <c r="B20" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D20" s="32">
-        <v>927</v>
-      </c>
-      <c r="E20" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="G20" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I20" s="31">
-        <v>43830</v>
-      </c>
-      <c r="J20" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K20" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L20" s="33">
-        <v>45771</v>
-      </c>
-      <c r="M20" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="N20" s="34">
-        <v>3018250207</v>
-      </c>
-      <c r="O20" s="34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="27">
-        <v>19</v>
-      </c>
-      <c r="B21" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D21" s="28">
-        <v>928</v>
-      </c>
-      <c r="E21" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="F21" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="H21" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I21" s="31">
-        <v>43626</v>
-      </c>
-      <c r="J21" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K21" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L21" s="33">
-        <v>45771</v>
-      </c>
-      <c r="M21" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="N21" s="34">
-        <v>3012244916</v>
-      </c>
-      <c r="O21" s="34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="19">
-        <v>20</v>
-      </c>
-      <c r="B22" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D22" s="23">
-        <v>929</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="I22" s="22">
-        <v>42853</v>
-      </c>
-      <c r="J22" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K22" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="L22" s="24">
-        <v>45775</v>
-      </c>
-      <c r="M22" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="N22" s="25"/>
-      <c r="O22" s="25" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="19">
-        <v>21</v>
-      </c>
-      <c r="B23" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D23" s="20">
-        <v>930</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="I23" s="22">
-        <v>42956</v>
-      </c>
-      <c r="J23" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K23" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="L23" s="24">
-        <v>45776</v>
-      </c>
-      <c r="M23" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="N23" s="25">
-        <v>3030439230</v>
-      </c>
-      <c r="O23" s="25" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="27">
-        <v>22</v>
-      </c>
-      <c r="B24" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C24" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D24" s="32">
-        <v>931</v>
-      </c>
-      <c r="E24" s="29" t="s">
-        <v>228</v>
-      </c>
-      <c r="F24" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="G24" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="H24" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I24" s="31">
-        <v>44419</v>
-      </c>
-      <c r="J24" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K24" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L24" s="33">
-        <v>45776</v>
-      </c>
-      <c r="M24" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
-        <v>23</v>
-      </c>
-      <c r="B25" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D25" s="28">
-        <v>932</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="F25" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="G25" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="H25" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I25" s="31">
-        <v>43419</v>
-      </c>
-      <c r="J25" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K25" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L25" s="33">
-        <v>45779</v>
-      </c>
-      <c r="M25" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="N25" s="34">
-        <v>3178789685</v>
-      </c>
-      <c r="O25" s="34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="27">
-        <v>24</v>
-      </c>
-      <c r="B26" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D26" s="32">
-        <v>933</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G26" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="H26" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I26" s="31"/>
-      <c r="J26" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K26" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L26" s="33"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="34"/>
-    </row>
-    <row r="27" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="27">
-        <v>25</v>
-      </c>
-      <c r="B27" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D27" s="28">
-        <v>934</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="G27" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="H27" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I27" s="31"/>
-      <c r="J27" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K27" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L27" s="33"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
-      <c r="O27" s="34"/>
-    </row>
-    <row r="28" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="27">
-        <v>26</v>
-      </c>
-      <c r="B28" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C28" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D28" s="32">
-        <v>935</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="G28" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="H28" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I28" s="31"/>
-      <c r="J28" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K28" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L28" s="33"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-    </row>
-    <row r="29" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="27">
-        <v>27</v>
-      </c>
-      <c r="B29" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D29" s="28">
-        <v>936</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="F29" s="30"/>
-      <c r="G29" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="H29" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I29" s="31"/>
-      <c r="J29" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K29" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L29" s="33"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
-      <c r="O29" s="34"/>
-    </row>
-    <row r="30" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="27">
-        <v>28</v>
-      </c>
-      <c r="B30" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C30" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D30" s="32">
-        <v>937</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="F30" s="30" t="s">
-        <v>240</v>
-      </c>
-      <c r="G30" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="H30" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I30" s="31"/>
-      <c r="J30" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K30" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L30" s="33"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
-    </row>
-    <row r="31" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="27">
-        <v>29</v>
-      </c>
-      <c r="B31" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C31" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D31" s="28">
-        <v>938</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G31" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="H31" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I31" s="31"/>
-      <c r="J31" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K31" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L31" s="33"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="34"/>
-    </row>
-    <row r="32" spans="1:15" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="27">
-        <v>30</v>
-      </c>
-      <c r="B32" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D32" s="32">
-        <v>939</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="H32" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I32" s="31"/>
-      <c r="J32" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K32" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L32" s="33"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="34"/>
-    </row>
-    <row r="33" spans="1:16" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="27">
-        <v>31</v>
-      </c>
-      <c r="B33" s="27">
-        <v>408170153</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D33" s="28">
-        <v>940</v>
-      </c>
-      <c r="E33" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="F33" s="30"/>
-      <c r="G33" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="H33" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I33" s="31"/>
-      <c r="J33" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="K33" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="L33" s="33"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-    </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="19">
-        <v>32</v>
-      </c>
-      <c r="B34" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D34" s="23">
-        <v>941</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="I34" s="22"/>
-      <c r="J34" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K34" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="L34" s="24">
-        <v>45800</v>
-      </c>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-    </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="19">
-        <v>33</v>
-      </c>
-      <c r="B35" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D35" s="20">
-        <v>942</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="G35" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="H35" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="I35" s="22">
-        <v>44427</v>
-      </c>
-      <c r="J35" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K35" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="L35" s="24">
-        <v>45801</v>
-      </c>
-      <c r="M35" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="N35" s="25">
-        <v>3083905874</v>
-      </c>
-      <c r="O35" s="25"/>
-    </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="19">
-        <v>34</v>
-      </c>
-      <c r="B36" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D36" s="23">
-        <v>943</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="F36" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="H36" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="I36" s="22">
-        <v>43906</v>
-      </c>
-      <c r="J36" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K36" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="L36" s="24">
-        <v>45801</v>
-      </c>
-      <c r="M36" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="N36" s="25">
-        <v>3083905874</v>
-      </c>
-      <c r="O36" s="25"/>
-    </row>
-    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="19">
-        <v>35</v>
-      </c>
-      <c r="B37" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D37" s="20">
-        <v>944</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="H37" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="I37" s="22">
-        <v>43516</v>
-      </c>
-      <c r="J37" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K37" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="L37" s="24">
-        <v>45801</v>
-      </c>
-      <c r="M37" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="N37" s="25">
-        <v>3083905874</v>
-      </c>
-      <c r="O37" s="25"/>
-    </row>
-    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="19">
-        <v>36</v>
-      </c>
-      <c r="B38" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D38" s="23">
-        <v>945</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="F38" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="H38" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="I38" s="22">
-        <v>43824</v>
-      </c>
-      <c r="J38" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K38" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="L38" s="24">
-        <v>45806</v>
-      </c>
-      <c r="M38" s="25" t="s">
-        <v>252</v>
-      </c>
-      <c r="N38" s="25">
-        <v>3331249111</v>
-      </c>
-      <c r="O38" s="25"/>
-      <c r="P38" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="19">
-        <v>37</v>
-      </c>
-      <c r="B39" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D39" s="23"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="25"/>
-      <c r="N39" s="25"/>
-      <c r="O39" s="25"/>
-    </row>
-    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="19">
-        <v>38</v>
-      </c>
-      <c r="B40" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D40" s="23"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="22"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="25"/>
-      <c r="N40" s="25"/>
-      <c r="O40" s="25"/>
-    </row>
-    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="19">
-        <v>39</v>
-      </c>
-      <c r="B41" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D41" s="23"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="25"/>
-      <c r="N41" s="25"/>
-      <c r="O41" s="25"/>
-    </row>
-    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="19">
-        <v>40</v>
-      </c>
-      <c r="B42" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="23"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="25"/>
-      <c r="N42" s="25"/>
-      <c r="O42" s="25"/>
-    </row>
-    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="19">
-        <v>41</v>
-      </c>
-      <c r="B43" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D43" s="23"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="25"/>
-      <c r="N43" s="25"/>
-      <c r="O43" s="25"/>
-    </row>
-    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="19">
-        <v>42</v>
-      </c>
-      <c r="B44" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D44" s="23"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="23"/>
-      <c r="K44" s="19"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="25"/>
-      <c r="N44" s="25"/>
-      <c r="O44" s="25"/>
-    </row>
-    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="19">
-        <v>43</v>
-      </c>
-      <c r="B45" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D45" s="23"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="23"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="24"/>
-      <c r="M45" s="25"/>
-      <c r="N45" s="25"/>
-      <c r="O45" s="25"/>
-    </row>
-    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="19">
-        <v>44</v>
-      </c>
-      <c r="B46" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D46" s="23"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="19"/>
-      <c r="L46" s="24"/>
-      <c r="M46" s="25"/>
-      <c r="N46" s="25"/>
-      <c r="O46" s="25"/>
-    </row>
-    <row r="47" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="19">
-        <v>45</v>
-      </c>
-      <c r="B47" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D47" s="23"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="23"/>
-      <c r="K47" s="19"/>
-      <c r="L47" s="24"/>
-      <c r="M47" s="25"/>
-      <c r="N47" s="25"/>
-      <c r="O47" s="25"/>
-    </row>
-    <row r="48" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="19">
-        <v>46</v>
-      </c>
-      <c r="B48" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D48" s="23"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="23"/>
-      <c r="K48" s="19"/>
-      <c r="L48" s="24"/>
-      <c r="M48" s="25"/>
-      <c r="N48" s="25"/>
-      <c r="O48" s="25"/>
-    </row>
-    <row r="49" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="19">
-        <v>47</v>
-      </c>
-      <c r="B49" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D49" s="23"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="22"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="19"/>
-      <c r="L49" s="24"/>
-      <c r="M49" s="25"/>
-      <c r="N49" s="25"/>
-      <c r="O49" s="25"/>
-    </row>
-    <row r="50" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="19">
-        <v>48</v>
-      </c>
-      <c r="B50" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D50" s="23"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="22"/>
-      <c r="J50" s="23"/>
-      <c r="K50" s="19"/>
-      <c r="L50" s="24"/>
-      <c r="M50" s="25"/>
-      <c r="N50" s="25"/>
-      <c r="O50" s="25"/>
-    </row>
-    <row r="51" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="19">
-        <v>49</v>
-      </c>
-      <c r="B51" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D51" s="23"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="22"/>
-      <c r="J51" s="23"/>
-      <c r="K51" s="19"/>
-      <c r="L51" s="24"/>
-      <c r="M51" s="25"/>
-      <c r="N51" s="25"/>
-      <c r="O51" s="25"/>
-    </row>
-    <row r="52" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="19">
-        <v>50</v>
-      </c>
-      <c r="B52" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D52" s="23"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="22"/>
-      <c r="J52" s="23"/>
-      <c r="K52" s="19"/>
-      <c r="L52" s="24"/>
-      <c r="M52" s="25"/>
-      <c r="N52" s="25"/>
-      <c r="O52" s="25"/>
-    </row>
-    <row r="53" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="19">
-        <v>51</v>
-      </c>
-      <c r="B53" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D53" s="23"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="22"/>
-      <c r="J53" s="23"/>
-      <c r="K53" s="19"/>
-      <c r="L53" s="24"/>
-      <c r="M53" s="25"/>
-      <c r="N53" s="25"/>
-      <c r="O53" s="25"/>
-    </row>
-    <row r="54" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="19">
-        <v>52</v>
-      </c>
-      <c r="B54" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D54" s="23"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="22"/>
-      <c r="J54" s="23"/>
-      <c r="K54" s="19"/>
-      <c r="L54" s="24"/>
-      <c r="M54" s="25"/>
-      <c r="N54" s="25"/>
-      <c r="O54" s="25"/>
-    </row>
-    <row r="55" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="19">
-        <v>53</v>
-      </c>
-      <c r="B55" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D55" s="23"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="22"/>
-      <c r="J55" s="23"/>
-      <c r="K55" s="19"/>
-      <c r="L55" s="24"/>
-      <c r="M55" s="25"/>
-      <c r="N55" s="25"/>
-      <c r="O55" s="25"/>
-    </row>
-    <row r="56" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="19">
-        <v>54</v>
-      </c>
-      <c r="B56" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D56" s="23"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="22"/>
-      <c r="J56" s="23"/>
-      <c r="K56" s="19"/>
-      <c r="L56" s="24"/>
-      <c r="M56" s="25"/>
-      <c r="N56" s="25"/>
-      <c r="O56" s="25"/>
-    </row>
-    <row r="57" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="19">
-        <v>55</v>
-      </c>
-      <c r="B57" s="19">
-        <v>408170153</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D57" s="23"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="22"/>
-      <c r="J57" s="23"/>
-      <c r="K57" s="19"/>
-      <c r="L57" s="24"/>
-      <c r="M57" s="25"/>
-      <c r="N57" s="25"/>
-      <c r="O57" s="25"/>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O34">
+    <sortCondition ref="H3:H34"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D1:D57">
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="6" priority="4">
-      <formula>$H29&lt;TODAY()</formula>
+  <conditionalFormatting sqref="E21:F21">
+    <cfRule type="expression" dxfId="4" priority="12">
+      <formula>$H21&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E23:F23">
-    <cfRule type="expression" dxfId="5" priority="8">
-      <formula>$H23&lt;TODAY()</formula>
-    </cfRule>
+  <conditionalFormatting sqref="N33:N34">
+    <cfRule type="duplicateValues" dxfId="3" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E26:F28">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>$H26&lt;TODAY()</formula>
-    </cfRule>
+  <conditionalFormatting sqref="N1:N32">
+    <cfRule type="duplicateValues" dxfId="2" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E31:F32">
-    <cfRule type="expression" dxfId="3" priority="2">
-      <formula>$H31&lt;TODAY()</formula>
-    </cfRule>
+  <conditionalFormatting sqref="D1:D34">
+    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E34:F34">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>$H34&lt;TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M57">
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N57">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  <conditionalFormatting sqref="M1:M34">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -6247,131 +5747,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="40"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
     </row>
     <row r="3" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="40"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
     </row>
     <row r="4" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="40"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
     </row>
     <row r="5" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="40"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="30"/>
     </row>
     <row r="6" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="40"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="45"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="35"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="43"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="33"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="40"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="30"/>
     </row>
     <row r="23" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="40"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="30"/>
     </row>
     <row r="24" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="40"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="30"/>
     </row>
     <row r="25" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="40"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="30"/>
     </row>
     <row r="26" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="40"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="30"/>
     </row>
     <row r="27" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="45"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -6408,24 +5908,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -6569,6 +6069,195 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C09A81-97BE-47C2-BB6D-F73DC0D1202E}">
+  <dimension ref="A2:E13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3">
+        <f>C3+D3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E12" si="0">C4+D4</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>256</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <f>SUM(E3:E12)</f>
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9775AE0A-527C-4FA9-ACE5-FDDEF858F8F4}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6579,10 +6268,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6590,39 +6279,39 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
+++ b/Sindhi Muslim/New Admissions 2025-2026/Student Registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\New Admissions 2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135903D0-10ED-41A2-AC57-E881B47C36C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02671956-1483-4753-9562-F905CFC68621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8EEF71F7-8EBE-4B4E-97F3-3DF7586E05F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="285">
   <si>
     <t>S No</t>
   </si>
@@ -881,6 +881,24 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Alina</t>
+  </si>
+  <si>
+    <t>Aqeel Ahmd Soomro</t>
+  </si>
+  <si>
+    <t>43205-8732569-3</t>
+  </si>
+  <si>
+    <t>Meesum Abbas</t>
+  </si>
+  <si>
+    <t>Mohsin Ali Sethar</t>
+  </si>
+  <si>
+    <t>42501-8572369-1</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1195,6 +1213,13 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1225,42 +1250,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -1280,8 +1280,18 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3593,31 +3603,65 @@
       <c r="A73" s="2">
         <v>72</v>
       </c>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I73" s="6"/>
+      <c r="B73" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F73" s="4">
+        <v>3022655366</v>
+      </c>
+      <c r="G73" s="5">
+        <v>45887</v>
+      </c>
+      <c r="H73" s="5">
+        <v>45890</v>
+      </c>
+      <c r="I73" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="J73" s="5">
+        <v>42917</v>
+      </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I74" s="6"/>
+      <c r="B74" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="F74" s="4">
+        <v>3310351080</v>
+      </c>
+      <c r="G74" s="5">
+        <v>45887</v>
+      </c>
+      <c r="H74" s="5">
+        <v>45890</v>
+      </c>
+      <c r="I74" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="J74" s="5">
+        <v>44071</v>
+      </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
@@ -3876,8 +3920,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I68 A69 D69:I69 A70:I91">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>$H1&lt;TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J73:J74">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>$H73&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3911,23 +3960,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -3977,498 +4026,498 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="38">
+      <c r="A3" s="17">
         <v>1</v>
       </c>
-      <c r="B3" s="38">
+      <c r="B3" s="17">
         <v>408170153</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D3" s="18"/>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="I3" s="42">
+      <c r="I3" s="20">
         <v>43088</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="J3" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L3" s="43">
+      <c r="L3" s="22">
         <v>45770</v>
       </c>
-      <c r="M3" s="44" t="s">
+      <c r="M3" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44" t="s">
+      <c r="N3" s="23"/>
+      <c r="O3" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="38">
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="17">
         <v>2</v>
       </c>
-      <c r="B4" s="38">
+      <c r="B4" s="17">
         <v>408170153</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D4" s="21"/>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H4" s="38" t="s">
+      <c r="H4" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="I4" s="42">
+      <c r="I4" s="20">
         <v>42853</v>
       </c>
-      <c r="J4" s="39" t="s">
+      <c r="J4" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K4" s="38" t="s">
+      <c r="K4" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L4" s="43">
+      <c r="L4" s="22">
         <v>45775</v>
       </c>
-      <c r="M4" s="44" t="s">
+      <c r="M4" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44" t="s">
+      <c r="N4" s="23"/>
+      <c r="O4" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="38">
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="17">
         <v>408170153</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D5" s="18"/>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="20">
         <v>43906</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="K5" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="22">
         <v>45801</v>
       </c>
-      <c r="M5" s="44" t="s">
+      <c r="M5" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="23">
         <v>3083905874</v>
       </c>
-      <c r="O5" s="44" t="s">
+      <c r="O5" s="23" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="38">
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="17">
         <v>408170153</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D6" s="39"/>
-      <c r="E6" s="40" t="s">
+      <c r="D6" s="21"/>
+      <c r="E6" s="24" t="s">
         <v>269</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="H6" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I6" s="42">
+      <c r="I6" s="20">
         <v>43267</v>
       </c>
-      <c r="J6" s="39" t="s">
+      <c r="J6" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K6" s="38" t="s">
+      <c r="K6" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="22">
         <v>45876</v>
       </c>
-      <c r="M6" s="44" t="s">
+      <c r="M6" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="N6" s="44">
+      <c r="N6" s="23">
         <v>3337112133</v>
       </c>
-      <c r="O6" s="44" t="s">
+      <c r="O6" s="23" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="38">
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="17">
         <v>5</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="17">
         <v>408170153</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="40" t="s">
+      <c r="D7" s="18"/>
+      <c r="E7" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H7" s="38" t="s">
+      <c r="H7" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="I7" s="42">
+      <c r="I7" s="20">
         <v>43101</v>
       </c>
-      <c r="J7" s="39" t="s">
+      <c r="J7" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K7" s="38" t="s">
+      <c r="K7" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L7" s="43">
+      <c r="L7" s="22">
         <v>45757</v>
       </c>
-      <c r="M7" s="44" t="s">
+      <c r="M7" s="23" t="s">
         <v>275</v>
       </c>
       <c r="N7" s="23">
         <v>3080471611</v>
       </c>
-      <c r="O7" s="44" t="s">
+      <c r="O7" s="23" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="38">
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
         <v>6</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="17">
         <v>408170153</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D8" s="39"/>
-      <c r="E8" s="40" t="s">
+      <c r="D8" s="21"/>
+      <c r="E8" s="24" t="s">
         <v>277</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H8" s="38" t="s">
+      <c r="H8" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="I8" s="42">
+      <c r="I8" s="20">
         <v>43466</v>
       </c>
-      <c r="J8" s="39" t="s">
+      <c r="J8" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K8" s="38" t="s">
+      <c r="K8" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L8" s="43">
+      <c r="L8" s="22">
         <v>45757</v>
       </c>
-      <c r="M8" s="44" t="s">
+      <c r="M8" s="23" t="s">
         <v>275</v>
       </c>
       <c r="N8" s="23">
         <v>3080471611</v>
       </c>
-      <c r="O8" s="44" t="s">
+      <c r="O8" s="23" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="38">
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
         <v>7</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="17">
         <v>408170153</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D9" s="46"/>
-      <c r="E9" s="40" t="s">
+      <c r="D9" s="18"/>
+      <c r="E9" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="F9" s="41" t="s">
+      <c r="F9" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="G9" s="38" t="s">
+      <c r="G9" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H9" s="38" t="s">
+      <c r="H9" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="I9" s="42">
+      <c r="I9" s="20">
         <v>43516</v>
       </c>
-      <c r="J9" s="39" t="s">
+      <c r="J9" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K9" s="38" t="s">
+      <c r="K9" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L9" s="43">
+      <c r="L9" s="22">
         <v>45801</v>
       </c>
-      <c r="M9" s="44" t="s">
+      <c r="M9" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="N9" s="44">
+      <c r="N9" s="23">
         <v>3083905874</v>
       </c>
-      <c r="O9" s="44" t="s">
+      <c r="O9" s="23" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="38">
+    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
         <v>8</v>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="17">
         <v>408170153</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D10" s="39"/>
-      <c r="E10" s="49" t="s">
+      <c r="D10" s="21"/>
+      <c r="E10" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H10" s="38" t="s">
+      <c r="H10" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="I10" s="42">
+      <c r="I10" s="20">
         <v>42956</v>
       </c>
-      <c r="J10" s="39" t="s">
+      <c r="J10" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K10" s="38" t="s">
+      <c r="K10" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L10" s="43">
+      <c r="L10" s="22">
         <v>45776</v>
       </c>
-      <c r="M10" s="44" t="s">
+      <c r="M10" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="N10" s="44">
+      <c r="N10" s="23">
         <v>3030439230</v>
       </c>
-      <c r="O10" s="44" t="s">
+      <c r="O10" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="38">
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
         <v>9</v>
       </c>
-      <c r="B11" s="38">
+      <c r="B11" s="17">
         <v>408170153</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D11" s="18"/>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="24" t="s">
         <v>266</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H11" s="47" t="s">
+      <c r="H11" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="I11" s="42">
+      <c r="I11" s="20">
         <v>42424</v>
       </c>
-      <c r="J11" s="39" t="s">
+      <c r="J11" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K11" s="38" t="s">
+      <c r="K11" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="22">
         <v>45876</v>
       </c>
-      <c r="M11" s="44" t="s">
+      <c r="M11" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="N11" s="44">
+      <c r="N11" s="23">
         <v>3337112133</v>
       </c>
-      <c r="O11" s="44" t="s">
+      <c r="O11" s="23" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="38">
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
         <v>10</v>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="17">
         <v>408170153</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D12" s="39"/>
-      <c r="E12" s="40" t="s">
+      <c r="D12" s="21"/>
+      <c r="E12" s="24" t="s">
         <v>272</v>
       </c>
-      <c r="F12" s="41" t="s">
+      <c r="F12" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H12" s="38" t="s">
+      <c r="H12" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="I12" s="42">
+      <c r="I12" s="20">
         <v>42095</v>
       </c>
-      <c r="J12" s="39" t="s">
+      <c r="J12" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K12" s="38" t="s">
+      <c r="K12" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L12" s="43">
+      <c r="L12" s="22">
         <v>45757</v>
       </c>
-      <c r="M12" s="44" t="s">
+      <c r="M12" s="23" t="s">
         <v>275</v>
       </c>
       <c r="N12" s="23">
         <v>3080471611</v>
       </c>
-      <c r="O12" s="44" t="s">
+      <c r="O12" s="23" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="38">
-        <v>11</v>
-      </c>
-      <c r="B13" s="38">
+    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>11</v>
+      </c>
+      <c r="B13" s="17">
         <v>408170153</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D13" s="21"/>
-      <c r="E13" s="40" t="s">
+      <c r="E13" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="F13" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="G13" s="38" t="s">
+      <c r="G13" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H13" s="38" t="s">
+      <c r="H13" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="I13" s="42">
+      <c r="I13" s="20">
         <v>43824</v>
       </c>
-      <c r="J13" s="39" t="s">
+      <c r="J13" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K13" s="38" t="s">
+      <c r="K13" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L13" s="43">
+      <c r="L13" s="22">
         <v>45806</v>
       </c>
-      <c r="M13" s="44" t="s">
+      <c r="M13" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="44">
+      <c r="N13" s="23">
         <v>3331249111</v>
       </c>
-      <c r="O13" s="44" t="s">
+      <c r="O13" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="38">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
         <v>12</v>
       </c>
       <c r="B14" s="17">
@@ -4512,901 +4561,901 @@
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="38">
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
         <v>13</v>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="17">
         <v>408170153</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="40" t="s">
+      <c r="D15" s="21"/>
+      <c r="E15" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="F15" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="38" t="s">
+      <c r="G15" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H15" s="38" t="s">
+      <c r="H15" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I15" s="42">
+      <c r="I15" s="20">
         <v>44013</v>
       </c>
-      <c r="J15" s="39" t="s">
+      <c r="J15" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K15" s="38" t="s">
+      <c r="K15" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L15" s="43">
+      <c r="L15" s="22">
         <v>45770</v>
       </c>
-      <c r="M15" s="44" t="s">
+      <c r="M15" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="N15" s="44">
+      <c r="N15" s="23">
         <v>3408550574</v>
       </c>
-      <c r="O15" s="44" t="s">
+      <c r="O15" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="38">
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
         <v>14</v>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="17">
         <v>408170153</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D16" s="18"/>
-      <c r="E16" s="40" t="s">
+      <c r="E16" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="F16" s="41" t="s">
+      <c r="F16" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="G16" s="38" t="s">
+      <c r="G16" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H16" s="38" t="s">
+      <c r="H16" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I16" s="42">
+      <c r="I16" s="20">
         <v>43832</v>
       </c>
-      <c r="J16" s="39" t="s">
+      <c r="J16" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K16" s="38" t="s">
+      <c r="K16" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L16" s="43">
+      <c r="L16" s="22">
         <v>45770</v>
       </c>
-      <c r="M16" s="44" t="s">
+      <c r="M16" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="N16" s="44">
+      <c r="N16" s="23">
         <v>3022345160</v>
       </c>
-      <c r="O16" s="44" t="s">
+      <c r="O16" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="38">
+    <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
         <v>15</v>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="17">
         <v>408170153</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40" t="s">
+      <c r="D17" s="21"/>
+      <c r="E17" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="G17" s="38" t="s">
+      <c r="G17" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H17" s="38" t="s">
+      <c r="H17" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I17" s="42">
+      <c r="I17" s="20">
         <v>43574</v>
       </c>
-      <c r="J17" s="39" t="s">
+      <c r="J17" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K17" s="38" t="s">
+      <c r="K17" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L17" s="43">
+      <c r="L17" s="22">
         <v>45770</v>
       </c>
-      <c r="M17" s="44" t="s">
+      <c r="M17" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="N17" s="44">
+      <c r="N17" s="23">
         <v>3152717911</v>
       </c>
-      <c r="O17" s="44" t="s">
+      <c r="O17" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="38">
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
         <v>16</v>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="17">
         <v>408170153</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D18" s="18"/>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G18" s="38" t="s">
+      <c r="G18" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H18" s="38" t="s">
+      <c r="H18" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I18" s="42">
+      <c r="I18" s="20">
         <v>43879</v>
       </c>
-      <c r="J18" s="39" t="s">
+      <c r="J18" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K18" s="38" t="s">
+      <c r="K18" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L18" s="43">
+      <c r="L18" s="22">
         <v>45770</v>
       </c>
-      <c r="M18" s="44" t="s">
+      <c r="M18" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="N18" s="44">
+      <c r="N18" s="23">
         <v>3213522748</v>
       </c>
-      <c r="O18" s="44" t="s">
+      <c r="O18" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="38">
+    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
         <v>17</v>
       </c>
-      <c r="B19" s="38">
+      <c r="B19" s="17">
         <v>408170153</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D19" s="39"/>
-      <c r="E19" s="40" t="s">
+      <c r="D19" s="21"/>
+      <c r="E19" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="F19" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H19" s="38" t="s">
+      <c r="H19" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I19" s="42">
+      <c r="I19" s="20">
         <v>43471</v>
       </c>
-      <c r="J19" s="39" t="s">
+      <c r="J19" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K19" s="38" t="s">
+      <c r="K19" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L19" s="43">
+      <c r="L19" s="22">
         <v>45770</v>
       </c>
-      <c r="M19" s="44" t="s">
+      <c r="M19" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="N19" s="44">
+      <c r="N19" s="23">
         <v>3472586633</v>
       </c>
-      <c r="O19" s="44" t="s">
+      <c r="O19" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="38">
+    <row r="20" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
         <v>18</v>
       </c>
-      <c r="B20" s="38">
+      <c r="B20" s="17">
         <v>408170153</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D20" s="18"/>
-      <c r="E20" s="40" t="s">
+      <c r="E20" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F20" s="41" t="s">
+      <c r="F20" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H20" s="38" t="s">
+      <c r="H20" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I20" s="42">
+      <c r="I20" s="20">
         <v>44143</v>
       </c>
-      <c r="J20" s="39" t="s">
+      <c r="J20" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K20" s="38" t="s">
+      <c r="K20" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L20" s="43">
+      <c r="L20" s="22">
         <v>45770</v>
       </c>
-      <c r="M20" s="44" t="s">
+      <c r="M20" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="N20" s="44">
+      <c r="N20" s="23">
         <v>3368603595</v>
       </c>
-      <c r="O20" s="44" t="s">
+      <c r="O20" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="21" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="38">
+    <row r="21" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
         <v>19</v>
       </c>
-      <c r="B21" s="38">
+      <c r="B21" s="17">
         <v>408170153</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D21" s="39"/>
-      <c r="E21" s="48" t="s">
+      <c r="D21" s="21"/>
+      <c r="E21" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="F21" s="48" t="s">
+      <c r="F21" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="G21" s="38" t="s">
+      <c r="G21" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H21" s="38" t="s">
+      <c r="H21" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I21" s="42">
+      <c r="I21" s="20">
         <v>44096</v>
       </c>
-      <c r="J21" s="39" t="s">
+      <c r="J21" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K21" s="38" t="s">
+      <c r="K21" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L21" s="43">
+      <c r="L21" s="22">
         <v>45770</v>
       </c>
-      <c r="M21" s="44" t="s">
+      <c r="M21" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="N21" s="44">
+      <c r="N21" s="23">
         <v>3158719338</v>
       </c>
-      <c r="O21" s="44" t="s">
+      <c r="O21" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="38">
+    <row r="22" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
         <v>20</v>
       </c>
-      <c r="B22" s="38">
+      <c r="B22" s="17">
         <v>408170153</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D22" s="46"/>
-      <c r="E22" s="40" t="s">
+      <c r="D22" s="18"/>
+      <c r="E22" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="F22" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="38" t="s">
+      <c r="G22" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H22" s="38" t="s">
+      <c r="H22" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I22" s="42">
+      <c r="I22" s="20">
         <v>44069</v>
       </c>
-      <c r="J22" s="39" t="s">
+      <c r="J22" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K22" s="38" t="s">
+      <c r="K22" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L22" s="43">
+      <c r="L22" s="22">
         <v>45770</v>
       </c>
-      <c r="M22" s="44" t="s">
+      <c r="M22" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="N22" s="44">
+      <c r="N22" s="23">
         <v>3333115124</v>
       </c>
-      <c r="O22" s="44" t="s">
+      <c r="O22" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="38">
+    <row r="23" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
         <v>21</v>
       </c>
-      <c r="B23" s="38">
+      <c r="B23" s="17">
         <v>408170153</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="C23" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D23" s="21"/>
-      <c r="E23" s="40" t="s">
+      <c r="E23" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="F23" s="41" t="s">
+      <c r="F23" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="G23" s="38" t="s">
+      <c r="G23" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H23" s="38" t="s">
+      <c r="H23" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I23" s="42">
+      <c r="I23" s="20">
         <v>43881</v>
       </c>
-      <c r="J23" s="39" t="s">
+      <c r="J23" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K23" s="38" t="s">
+      <c r="K23" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L23" s="43">
+      <c r="L23" s="22">
         <v>45770</v>
       </c>
-      <c r="M23" s="44" t="s">
+      <c r="M23" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="N23" s="44">
+      <c r="N23" s="23">
         <v>3412510302</v>
       </c>
-      <c r="O23" s="44" t="s">
+      <c r="O23" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="24" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="38">
+    <row r="24" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
         <v>22</v>
       </c>
-      <c r="B24" s="38">
+      <c r="B24" s="17">
         <v>408170153</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D24" s="46"/>
-      <c r="E24" s="40" t="s">
+      <c r="D24" s="18"/>
+      <c r="E24" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="F24" s="41" t="s">
+      <c r="F24" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="38" t="s">
+      <c r="G24" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H24" s="38" t="s">
+      <c r="H24" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I24" s="42">
+      <c r="I24" s="20">
         <v>43936</v>
       </c>
-      <c r="J24" s="39" t="s">
+      <c r="J24" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K24" s="38" t="s">
+      <c r="K24" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L24" s="43">
+      <c r="L24" s="22">
         <v>45770</v>
       </c>
-      <c r="M24" s="44" t="s">
+      <c r="M24" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="N24" s="44">
+      <c r="N24" s="23">
         <v>3471801620</v>
       </c>
-      <c r="O24" s="44" t="s">
+      <c r="O24" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="38">
+    <row r="25" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
         <v>23</v>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="17">
         <v>408170153</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D25" s="21"/>
-      <c r="E25" s="40" t="s">
+      <c r="E25" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="F25" s="41" t="s">
+      <c r="F25" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="38" t="s">
+      <c r="G25" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H25" s="38" t="s">
+      <c r="H25" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I25" s="42">
+      <c r="I25" s="20">
         <v>43871</v>
       </c>
-      <c r="J25" s="39" t="s">
+      <c r="J25" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K25" s="38" t="s">
+      <c r="K25" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L25" s="43">
+      <c r="L25" s="22">
         <v>45770</v>
       </c>
-      <c r="M25" s="44" t="s">
+      <c r="M25" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="N25" s="44">
+      <c r="N25" s="23">
         <v>3471801620</v>
       </c>
-      <c r="O25" s="44" t="s">
+      <c r="O25" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="26" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="38">
+    <row r="26" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
         <v>24</v>
       </c>
-      <c r="B26" s="38">
+      <c r="B26" s="17">
         <v>408170153</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D26" s="46"/>
-      <c r="E26" s="40" t="s">
+      <c r="D26" s="18"/>
+      <c r="E26" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="F26" s="41" t="s">
+      <c r="F26" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="G26" s="38" t="s">
+      <c r="G26" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H26" s="38" t="s">
+      <c r="H26" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I26" s="42">
+      <c r="I26" s="20">
         <v>43936</v>
       </c>
-      <c r="J26" s="39" t="s">
+      <c r="J26" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K26" s="38" t="s">
+      <c r="K26" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L26" s="43">
+      <c r="L26" s="22">
         <v>45770</v>
       </c>
-      <c r="M26" s="44" t="s">
+      <c r="M26" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="N26" s="44">
+      <c r="N26" s="23">
         <v>3471801620</v>
       </c>
-      <c r="O26" s="44" t="s">
+      <c r="O26" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="27" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="38">
+    <row r="27" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
         <v>25</v>
       </c>
-      <c r="B27" s="38">
+      <c r="B27" s="17">
         <v>408170153</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D27" s="21"/>
-      <c r="E27" s="40" t="s">
+      <c r="E27" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="F27" s="41" t="s">
+      <c r="F27" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="G27" s="38" t="s">
+      <c r="G27" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H27" s="38" t="s">
+      <c r="H27" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I27" s="42">
+      <c r="I27" s="20">
         <v>43723</v>
       </c>
-      <c r="J27" s="39" t="s">
+      <c r="J27" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K27" s="38" t="s">
+      <c r="K27" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L27" s="43">
+      <c r="L27" s="22">
         <v>45770</v>
       </c>
-      <c r="M27" s="44" t="s">
+      <c r="M27" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="N27" s="44">
+      <c r="N27" s="23">
         <v>3146147223</v>
       </c>
-      <c r="O27" s="44" t="s">
+      <c r="O27" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="38">
+    <row r="28" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
         <v>26</v>
       </c>
-      <c r="B28" s="38">
+      <c r="B28" s="17">
         <v>408170153</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D28" s="46"/>
-      <c r="E28" s="40" t="s">
+      <c r="D28" s="18"/>
+      <c r="E28" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="F28" s="41" t="s">
+      <c r="F28" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G28" s="38" t="s">
+      <c r="G28" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H28" s="38" t="s">
+      <c r="H28" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I28" s="42">
+      <c r="I28" s="20">
         <v>43930</v>
       </c>
-      <c r="J28" s="39" t="s">
+      <c r="J28" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K28" s="38" t="s">
+      <c r="K28" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L28" s="43">
+      <c r="L28" s="22">
         <v>45770</v>
       </c>
-      <c r="M28" s="44" t="s">
+      <c r="M28" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="N28" s="44">
+      <c r="N28" s="23">
         <v>3437668872</v>
       </c>
-      <c r="O28" s="44" t="s">
+      <c r="O28" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="38">
+    <row r="29" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
         <v>27</v>
       </c>
-      <c r="B29" s="38">
+      <c r="B29" s="17">
         <v>408170153</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D29" s="21"/>
-      <c r="E29" s="40" t="s">
+      <c r="E29" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F29" s="41" t="s">
+      <c r="F29" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="G29" s="38" t="s">
+      <c r="G29" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H29" s="38" t="s">
+      <c r="H29" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I29" s="42">
+      <c r="I29" s="20">
         <v>43830</v>
       </c>
-      <c r="J29" s="39" t="s">
+      <c r="J29" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K29" s="38" t="s">
+      <c r="K29" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L29" s="43">
+      <c r="L29" s="22">
         <v>45771</v>
       </c>
-      <c r="M29" s="44" t="s">
+      <c r="M29" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="N29" s="44">
+      <c r="N29" s="23">
         <v>3018250207</v>
       </c>
-      <c r="O29" s="44" t="s">
+      <c r="O29" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="30" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="38">
+    <row r="30" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="17">
         <v>28</v>
       </c>
-      <c r="B30" s="38">
+      <c r="B30" s="17">
         <v>408170153</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D30" s="46"/>
-      <c r="E30" s="40" t="s">
+      <c r="D30" s="18"/>
+      <c r="E30" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="F30" s="41" t="s">
+      <c r="F30" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G30" s="38" t="s">
+      <c r="G30" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H30" s="38" t="s">
+      <c r="H30" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I30" s="42">
+      <c r="I30" s="20">
         <v>43626</v>
       </c>
-      <c r="J30" s="39" t="s">
+      <c r="J30" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K30" s="38" t="s">
+      <c r="K30" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L30" s="43">
+      <c r="L30" s="22">
         <v>45771</v>
       </c>
-      <c r="M30" s="44" t="s">
+      <c r="M30" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="N30" s="44">
+      <c r="N30" s="23">
         <v>3012244916</v>
       </c>
-      <c r="O30" s="44" t="s">
+      <c r="O30" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="31" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="38">
+    <row r="31" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="17">
         <v>29</v>
       </c>
-      <c r="B31" s="38">
+      <c r="B31" s="17">
         <v>408170153</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="C31" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D31" s="18"/>
-      <c r="E31" s="40" t="s">
+      <c r="E31" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="F31" s="41" t="s">
+      <c r="F31" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="G31" s="38" t="s">
+      <c r="G31" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H31" s="38" t="s">
+      <c r="H31" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I31" s="42">
+      <c r="I31" s="20">
         <v>44419</v>
       </c>
-      <c r="J31" s="39" t="s">
+      <c r="J31" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K31" s="38" t="s">
+      <c r="K31" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L31" s="43">
+      <c r="L31" s="22">
         <v>45776</v>
       </c>
-      <c r="M31" s="44" t="s">
+      <c r="M31" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44" t="s">
+      <c r="N31" s="23"/>
+      <c r="O31" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="32" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="38">
+    <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="17">
         <v>30</v>
       </c>
-      <c r="B32" s="38">
+      <c r="B32" s="17">
         <v>408170153</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="40" t="s">
+      <c r="D32" s="21"/>
+      <c r="E32" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="G32" s="38" t="s">
+      <c r="G32" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H32" s="38" t="s">
+      <c r="H32" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I32" s="42">
+      <c r="I32" s="20">
         <v>43419</v>
       </c>
-      <c r="J32" s="39" t="s">
+      <c r="J32" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K32" s="38" t="s">
+      <c r="K32" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L32" s="43">
+      <c r="L32" s="22">
         <v>45779</v>
       </c>
-      <c r="M32" s="44" t="s">
+      <c r="M32" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="N32" s="44">
+      <c r="N32" s="23">
         <v>3178789685</v>
       </c>
-      <c r="O32" s="44" t="s">
+      <c r="O32" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="38">
+    <row r="33" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="17">
         <v>31</v>
       </c>
-      <c r="B33" s="38">
+      <c r="B33" s="17">
         <v>408170153</v>
       </c>
-      <c r="C33" s="38" t="s">
+      <c r="C33" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D33" s="39"/>
-      <c r="E33" s="40" t="s">
+      <c r="D33" s="21"/>
+      <c r="E33" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="F33" s="41" t="s">
+      <c r="F33" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="G33" s="38" t="s">
+      <c r="G33" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H33" s="38" t="s">
+      <c r="H33" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I33" s="42">
+      <c r="I33" s="20">
         <v>44427</v>
       </c>
-      <c r="J33" s="39" t="s">
+      <c r="J33" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K33" s="38" t="s">
+      <c r="K33" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L33" s="43">
+      <c r="L33" s="22">
         <v>45801</v>
       </c>
-      <c r="M33" s="44" t="s">
+      <c r="M33" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="N33" s="44">
+      <c r="N33" s="23">
         <v>3083905874</v>
       </c>
-      <c r="O33" s="44" t="s">
+      <c r="O33" s="23" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="38">
+    <row r="34" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="17">
         <v>32</v>
       </c>
-      <c r="B34" s="38">
+      <c r="B34" s="17">
         <v>408170153</v>
       </c>
-      <c r="C34" s="38" t="s">
+      <c r="C34" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D34" s="39"/>
-      <c r="E34" s="40" t="s">
+      <c r="D34" s="21"/>
+      <c r="E34" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="41" t="s">
+      <c r="F34" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="G34" s="38" t="s">
+      <c r="G34" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H34" s="47" t="s">
+      <c r="H34" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="I34" s="42">
+      <c r="I34" s="20">
         <v>44159</v>
       </c>
-      <c r="J34" s="39" t="s">
+      <c r="J34" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K34" s="38" t="s">
+      <c r="K34" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="L34" s="43">
+      <c r="L34" s="22">
         <v>45876</v>
       </c>
-      <c r="M34" s="44" t="s">
+      <c r="M34" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="N34" s="44">
+      <c r="N34" s="23">
         <v>3363396753</v>
       </c>
-      <c r="O34" s="44" t="s">
+      <c r="O34" s="23" t="s">
         <v>189</v>
       </c>
     </row>
@@ -5417,22 +5466,22 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
+  <conditionalFormatting sqref="D1:D34">
+    <cfRule type="duplicateValues" dxfId="4" priority="34"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E21:F21">
-    <cfRule type="expression" dxfId="4" priority="12">
+    <cfRule type="expression" dxfId="3" priority="12">
       <formula>$H21&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N33:N34">
-    <cfRule type="duplicateValues" dxfId="3" priority="25"/>
+  <conditionalFormatting sqref="M1:M34">
+    <cfRule type="duplicateValues" dxfId="2" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N32">
-    <cfRule type="duplicateValues" dxfId="2" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D34">
-    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M34">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  <conditionalFormatting sqref="N33:N34">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -5747,131 +5796,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="36"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
     </row>
     <row r="3" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
     </row>
     <row r="4" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="33"/>
     </row>
     <row r="5" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="30"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="33"/>
     </row>
     <row r="6" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="30"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="33"/>
     </row>
     <row r="7" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="35"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="38"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="36"/>
     </row>
     <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="33"/>
     </row>
     <row r="23" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="33"/>
     </row>
     <row r="24" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="30"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="33"/>
     </row>
     <row r="25" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="30"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="33"/>
     </row>
     <row r="26" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="30"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
     </row>
     <row r="27" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="35"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -5908,24 +5957,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="2" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
